--- a/database/event/3515/event_3515_evp_summary.xlsx
+++ b/database/event/3515/event_3515_evp_summary.xlsx
@@ -502,7 +502,7 @@
         <v>3.1939</v>
       </c>
       <c r="D2" t="n">
-        <v>2.5656</v>
+        <v>2.5018</v>
       </c>
       <c r="E2" t="n">
         <v>7.3939</v>
@@ -548,7 +548,7 @@
         <v>2.3944</v>
       </c>
       <c r="D3" t="n">
-        <v>1.8179</v>
+        <v>1.7644</v>
       </c>
       <c r="E3" t="n">
         <v>5.543</v>
@@ -594,7 +594,7 @@
         <v>2.0873</v>
       </c>
       <c r="D4" t="n">
-        <v>1.5307</v>
+        <v>1.4812</v>
       </c>
       <c r="E4" t="n">
         <v>4.8322</v>
@@ -640,7 +640,7 @@
         <v>1.8323</v>
       </c>
       <c r="D5" t="n">
-        <v>1.2922</v>
+        <v>1.246</v>
       </c>
       <c r="E5" t="n">
         <v>4.2418</v>
@@ -686,7 +686,7 @@
         <v>1.7181</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1854</v>
+        <v>1.1407</v>
       </c>
       <c r="E6" t="n">
         <v>3.9774</v>
@@ -732,7 +732,7 @@
         <v>1.597</v>
       </c>
       <c r="D7" t="n">
-        <v>1.0722</v>
+        <v>1.029</v>
       </c>
       <c r="E7" t="n">
         <v>3.6971</v>
@@ -778,7 +778,7 @@
         <v>1.5968</v>
       </c>
       <c r="D8" t="n">
-        <v>1.072</v>
+        <v>1.0288</v>
       </c>
       <c r="E8" t="n">
         <v>3.6966</v>
@@ -824,7 +824,7 @@
         <v>1.4676</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9510999999999999</v>
+        <v>0.9096</v>
       </c>
       <c r="E9" t="n">
         <v>3.3974</v>
@@ -870,7 +870,7 @@
         <v>1.4213</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9078000000000001</v>
+        <v>0.8669</v>
       </c>
       <c r="E10" t="n">
         <v>3.2903</v>
@@ -916,7 +916,7 @@
         <v>1.3666</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8567</v>
+        <v>0.8165</v>
       </c>
       <c r="E11" t="n">
         <v>3.1636</v>
@@ -962,7 +962,7 @@
         <v>1.16</v>
       </c>
       <c r="D12" t="n">
-        <v>0.6635</v>
+        <v>0.626</v>
       </c>
       <c r="E12" t="n">
         <v>2.6855</v>
@@ -1008,7 +1008,7 @@
         <v>1.0008</v>
       </c>
       <c r="D13" t="n">
-        <v>0.5145999999999999</v>
+        <v>0.4791</v>
       </c>
       <c r="E13" t="n">
         <v>2.3169</v>
@@ -1054,7 +1054,7 @@
         <v>0.9818</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4968</v>
+        <v>0.4616</v>
       </c>
       <c r="E14" t="n">
         <v>2.2729</v>
@@ -1100,7 +1100,7 @@
         <v>0.9311</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4495</v>
+        <v>0.4149</v>
       </c>
       <c r="E15" t="n">
         <v>2.1556</v>
@@ -1146,7 +1146,7 @@
         <v>0.6251</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1632</v>
+        <v>0.1326</v>
       </c>
       <c r="E16" t="n">
         <v>1.4471</v>
@@ -1192,7 +1192,7 @@
         <v>0.5869</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1275</v>
+        <v>0.0974</v>
       </c>
       <c r="E17" t="n">
         <v>1.3587</v>
@@ -1238,7 +1238,7 @@
         <v>0.5568</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0994</v>
+        <v>0.0696</v>
       </c>
       <c r="E18" t="n">
         <v>1.289</v>
@@ -1284,7 +1284,7 @@
         <v>0.5371</v>
       </c>
       <c r="D19" t="n">
-        <v>0.081</v>
+        <v>0.0515</v>
       </c>
       <c r="E19" t="n">
         <v>1.2435</v>
@@ -1330,7 +1330,7 @@
         <v>0.5145999999999999</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0599</v>
+        <v>0.0307</v>
       </c>
       <c r="E20" t="n">
         <v>1.1913</v>
@@ -1376,7 +1376,7 @@
         <v>0.4089</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.039</v>
+        <v>-0.0668</v>
       </c>
       <c r="E21" t="n">
         <v>0.9466</v>
@@ -1422,7 +1422,7 @@
         <v>0.2946</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1458</v>
+        <v>-0.1722</v>
       </c>
       <c r="E22" t="n">
         <v>0.6821</v>
@@ -1468,7 +1468,7 @@
         <v>0.1893</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.2443</v>
+        <v>-0.2693</v>
       </c>
       <c r="E23" t="n">
         <v>0.4382</v>
@@ -1514,7 +1514,7 @@
         <v>0.1437</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.287</v>
+        <v>-0.3114</v>
       </c>
       <c r="E24" t="n">
         <v>0.3327</v>
@@ -1560,7 +1560,7 @@
         <v>-0.0767</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.4931</v>
+        <v>-0.5147</v>
       </c>
       <c r="E25" t="n">
         <v>-0.1776</v>
@@ -1606,7 +1606,7 @@
         <v>-0.1034</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.518</v>
+        <v>-0.5392</v>
       </c>
       <c r="E26" t="n">
         <v>-0.2393</v>
@@ -1652,7 +1652,7 @@
         <v>-0.1057</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.5202</v>
+        <v>-0.5414</v>
       </c>
       <c r="E27" t="n">
         <v>-0.2447</v>
@@ -1698,7 +1698,7 @@
         <v>-0.1686</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.5790999999999999</v>
+        <v>-0.5994</v>
       </c>
       <c r="E28" t="n">
         <v>-0.3904</v>
@@ -1744,7 +1744,7 @@
         <v>-0.2917</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.6942</v>
+        <v>-0.713</v>
       </c>
       <c r="E29" t="n">
         <v>-0.6754</v>
@@ -1790,7 +1790,7 @@
         <v>-0.3255</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.7258</v>
+        <v>-0.7441</v>
       </c>
       <c r="E30" t="n">
         <v>-0.7534999999999999</v>
@@ -1836,7 +1836,7 @@
         <v>-0.3975</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.7931</v>
+        <v>-0.8106</v>
       </c>
       <c r="E31" t="n">
         <v>-0.9203</v>
@@ -1882,7 +1882,7 @@
         <v>-0.4092</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.8041</v>
+        <v>-0.8214</v>
       </c>
       <c r="E32" t="n">
         <v>-0.9474</v>
@@ -1928,7 +1928,7 @@
         <v>-0.46</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.8516</v>
+        <v>-0.8682</v>
       </c>
       <c r="E33" t="n">
         <v>-1.0649</v>
@@ -1974,7 +1974,7 @@
         <v>-0.5181</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.9059</v>
+        <v>-0.9218</v>
       </c>
       <c r="E34" t="n">
         <v>-1.1994</v>
@@ -2020,7 +2020,7 @@
         <v>-0.5668</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.9514</v>
+        <v>-0.9667</v>
       </c>
       <c r="E35" t="n">
         <v>-1.3121</v>
@@ -2066,7 +2066,7 @@
         <v>-0.5673</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9519</v>
+        <v>-0.9671999999999999</v>
       </c>
       <c r="E36" t="n">
         <v>-1.3134</v>
@@ -2112,7 +2112,7 @@
         <v>-0.6303</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.0108</v>
+        <v>-1.0253</v>
       </c>
       <c r="E37" t="n">
         <v>-1.4592</v>
@@ -2158,7 +2158,7 @@
         <v>-0.6458</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.0253</v>
+        <v>-1.0396</v>
       </c>
       <c r="E38" t="n">
         <v>-1.4951</v>
@@ -2204,7 +2204,7 @@
         <v>-0.66</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.0386</v>
+        <v>-1.0527</v>
       </c>
       <c r="E39" t="n">
         <v>-1.528</v>
@@ -2250,7 +2250,7 @@
         <v>-0.9154</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.2774</v>
+        <v>-1.2882</v>
       </c>
       <c r="E40" t="n">
         <v>-2.1191</v>
@@ -2296,7 +2296,7 @@
         <v>-1.5247</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.8473</v>
+        <v>-1.8501</v>
       </c>
       <c r="E41" t="n">
         <v>-3.5297</v>

--- a/database/event/3515/event_3515_evp_summary.xlsx
+++ b/database/event/3515/event_3515_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.3939</v>
+        <v>6.593</v>
       </c>
       <c r="C2" t="n">
-        <v>3.1939</v>
+        <v>2.8479</v>
       </c>
       <c r="D2" t="n">
-        <v>2.5018</v>
+        <v>2.3384</v>
       </c>
       <c r="E2" t="n">
-        <v>7.3939</v>
+        <v>6.593</v>
       </c>
       <c r="F2" t="n">
-        <v>4.4978</v>
+        <v>4.2303</v>
       </c>
       <c r="G2" t="n">
-        <v>2.8961</v>
+        <v>2.3627</v>
       </c>
       <c r="H2" t="n">
-        <v>5.5354</v>
+        <v>9.4185</v>
       </c>
       <c r="I2" t="n">
-        <v>4.4866</v>
+        <v>4.8972</v>
       </c>
       <c r="J2" t="n">
-        <v>2.8961</v>
+        <v>2.3627</v>
       </c>
       <c r="K2" t="n">
         <v>110</v>
@@ -529,7 +529,7 @@
         <v>102</v>
       </c>
       <c r="M2" t="n">
-        <v>7.3827</v>
+        <v>7.2599</v>
       </c>
       <c r="N2" t="n">
         <v>212</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.543</v>
+        <v>5.0273</v>
       </c>
       <c r="C3" t="n">
-        <v>2.3944</v>
+        <v>2.1716</v>
       </c>
       <c r="D3" t="n">
-        <v>1.7644</v>
+        <v>1.6316</v>
       </c>
       <c r="E3" t="n">
-        <v>5.543</v>
+        <v>5.0273</v>
       </c>
       <c r="F3" t="n">
-        <v>4.4804</v>
+        <v>4.1882</v>
       </c>
       <c r="G3" t="n">
-        <v>1.0626</v>
+        <v>0.8391</v>
       </c>
       <c r="H3" t="n">
-        <v>5.4652</v>
+        <v>9.2704</v>
       </c>
       <c r="I3" t="n">
-        <v>4.4297</v>
+        <v>4.8202</v>
       </c>
       <c r="J3" t="n">
-        <v>1.0626</v>
+        <v>0.8391</v>
       </c>
       <c r="K3" t="n">
         <v>152</v>
@@ -575,7 +575,7 @@
         <v>103</v>
       </c>
       <c r="M3" t="n">
-        <v>5.4923</v>
+        <v>5.6593</v>
       </c>
       <c r="N3" t="n">
         <v>255</v>
@@ -584,127 +584,127 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Twistzz</t>
+          <t>gla1ve</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.8322</v>
+        <v>4.4243</v>
       </c>
       <c r="C4" t="n">
-        <v>2.0873</v>
+        <v>1.9111</v>
       </c>
       <c r="D4" t="n">
-        <v>1.4812</v>
+        <v>1.3593</v>
       </c>
       <c r="E4" t="n">
-        <v>4.8322</v>
+        <v>4.4243</v>
       </c>
       <c r="F4" t="n">
-        <v>4.3694</v>
+        <v>2.3035</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4628</v>
+        <v>2.1208</v>
       </c>
       <c r="H4" t="n">
-        <v>5.0188</v>
+        <v>2.6297</v>
       </c>
       <c r="I4" t="n">
-        <v>4.0678</v>
+        <v>1.3673</v>
       </c>
       <c r="J4" t="n">
-        <v>0.4628</v>
+        <v>2.1208</v>
       </c>
       <c r="K4" t="n">
-        <v>152</v>
+        <v>110</v>
       </c>
       <c r="L4" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="M4" t="n">
-        <v>4.5306</v>
+        <v>3.4881</v>
       </c>
       <c r="N4" t="n">
-        <v>255</v>
+        <v>212</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>s1mple</t>
+          <t>Twistzz</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.2418</v>
+        <v>4.3494</v>
       </c>
       <c r="C5" t="n">
-        <v>1.8323</v>
+        <v>1.8788</v>
       </c>
       <c r="D5" t="n">
-        <v>1.246</v>
+        <v>1.3255</v>
       </c>
       <c r="E5" t="n">
-        <v>4.2418</v>
+        <v>4.3494</v>
       </c>
       <c r="F5" t="n">
-        <v>4.2253</v>
+        <v>4.1111</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0165</v>
+        <v>0.2383</v>
       </c>
       <c r="H5" t="n">
-        <v>4.4389</v>
+        <v>8.9985</v>
       </c>
       <c r="I5" t="n">
-        <v>3.5978</v>
+        <v>4.6788</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0165</v>
+        <v>0.2383</v>
       </c>
       <c r="K5" t="n">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="L5" t="n">
-        <v>54</v>
+        <v>103</v>
       </c>
       <c r="M5" t="n">
-        <v>3.6143</v>
+        <v>4.9171</v>
       </c>
       <c r="N5" t="n">
-        <v>214</v>
+        <v>255</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>gla1ve</t>
+          <t>dupreeh</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.9774</v>
+        <v>4.0162</v>
       </c>
       <c r="C6" t="n">
-        <v>1.7181</v>
+        <v>1.7349</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1407</v>
+        <v>1.1751</v>
       </c>
       <c r="E6" t="n">
-        <v>3.9774</v>
+        <v>4.0162</v>
       </c>
       <c r="F6" t="n">
-        <v>1.433</v>
+        <v>2.7472</v>
       </c>
       <c r="G6" t="n">
-        <v>2.5444</v>
+        <v>1.269</v>
       </c>
       <c r="H6" t="n">
-        <v>1.433</v>
+        <v>4.1933</v>
       </c>
       <c r="I6" t="n">
-        <v>1.1615</v>
+        <v>2.1803</v>
       </c>
       <c r="J6" t="n">
-        <v>2.5444</v>
+        <v>1.269</v>
       </c>
       <c r="K6" t="n">
         <v>110</v>
@@ -713,7 +713,7 @@
         <v>102</v>
       </c>
       <c r="M6" t="n">
-        <v>3.7059</v>
+        <v>3.4493</v>
       </c>
       <c r="N6" t="n">
         <v>212</v>
@@ -722,81 +722,81 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>dupreeh</t>
+          <t>nitr0</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.6971</v>
+        <v>3.7841</v>
       </c>
       <c r="C7" t="n">
-        <v>1.597</v>
+        <v>1.6346</v>
       </c>
       <c r="D7" t="n">
-        <v>1.029</v>
+        <v>1.0703</v>
       </c>
       <c r="E7" t="n">
-        <v>3.6971</v>
+        <v>3.7841</v>
       </c>
       <c r="F7" t="n">
-        <v>2.6055</v>
+        <v>2.7767</v>
       </c>
       <c r="G7" t="n">
-        <v>1.0916</v>
+        <v>1.0074</v>
       </c>
       <c r="H7" t="n">
-        <v>2.6055</v>
+        <v>4.2971</v>
       </c>
       <c r="I7" t="n">
-        <v>2.1119</v>
+        <v>2.2343</v>
       </c>
       <c r="J7" t="n">
-        <v>1.0916</v>
+        <v>1.0074</v>
       </c>
       <c r="K7" t="n">
-        <v>110</v>
+        <v>152</v>
       </c>
       <c r="L7" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="M7" t="n">
-        <v>3.2035</v>
+        <v>3.2417</v>
       </c>
       <c r="N7" t="n">
-        <v>212</v>
+        <v>255</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>electroNic</t>
+          <t>s1mple</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.6966</v>
+        <v>3.7222</v>
       </c>
       <c r="C8" t="n">
-        <v>1.5968</v>
+        <v>1.6079</v>
       </c>
       <c r="D8" t="n">
-        <v>1.0288</v>
+        <v>1.0424</v>
       </c>
       <c r="E8" t="n">
-        <v>3.6966</v>
+        <v>3.7222</v>
       </c>
       <c r="F8" t="n">
-        <v>3.5903</v>
+        <v>3.5643</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1063</v>
+        <v>0.1579</v>
       </c>
       <c r="H8" t="n">
-        <v>3.5903</v>
+        <v>7.072</v>
       </c>
       <c r="I8" t="n">
-        <v>2.91</v>
+        <v>3.6771</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1063</v>
+        <v>0.1579</v>
       </c>
       <c r="K8" t="n">
         <v>160</v>
@@ -805,7 +805,7 @@
         <v>54</v>
       </c>
       <c r="M8" t="n">
-        <v>3.0163</v>
+        <v>3.835</v>
       </c>
       <c r="N8" t="n">
         <v>214</v>
@@ -814,507 +814,507 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>nitr0</t>
+          <t>Magisk</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.3974</v>
+        <v>3.631</v>
       </c>
       <c r="C9" t="n">
-        <v>1.4676</v>
+        <v>1.5685</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9096</v>
+        <v>1.0012</v>
       </c>
       <c r="E9" t="n">
-        <v>3.3974</v>
+        <v>3.631</v>
       </c>
       <c r="F9" t="n">
-        <v>2.0759</v>
+        <v>1.4001</v>
       </c>
       <c r="G9" t="n">
-        <v>1.3215</v>
+        <v>2.2309</v>
       </c>
       <c r="H9" t="n">
-        <v>2.0759</v>
+        <v>1.4001</v>
       </c>
       <c r="I9" t="n">
-        <v>1.6826</v>
+        <v>0.728</v>
       </c>
       <c r="J9" t="n">
-        <v>1.3215</v>
+        <v>2.2309</v>
       </c>
       <c r="K9" t="n">
-        <v>152</v>
+        <v>110</v>
       </c>
       <c r="L9" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="M9" t="n">
-        <v>3.0041</v>
+        <v>2.9589</v>
       </c>
       <c r="N9" t="n">
-        <v>255</v>
+        <v>212</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>oskar</t>
+          <t>electroNic</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.2903</v>
+        <v>3.3559</v>
       </c>
       <c r="C10" t="n">
-        <v>1.4213</v>
+        <v>1.4496</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8669</v>
+        <v>0.877</v>
       </c>
       <c r="E10" t="n">
-        <v>3.2903</v>
+        <v>3.3559</v>
       </c>
       <c r="F10" t="n">
-        <v>3.9595</v>
+        <v>3.1233</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.6692</v>
+        <v>0.2326</v>
       </c>
       <c r="H10" t="n">
-        <v>3.9595</v>
+        <v>5.5184</v>
       </c>
       <c r="I10" t="n">
-        <v>3.2093</v>
+        <v>2.8693</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.6692</v>
+        <v>0.2326</v>
       </c>
       <c r="K10" t="n">
-        <v>248</v>
+        <v>160</v>
       </c>
       <c r="L10" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="M10" t="n">
-        <v>2.5401</v>
+        <v>3.1019</v>
       </c>
       <c r="N10" t="n">
-        <v>301</v>
+        <v>214</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Magisk</t>
+          <t>flamie</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.1636</v>
+        <v>3.129</v>
       </c>
       <c r="C11" t="n">
-        <v>1.3666</v>
+        <v>1.3516</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8165</v>
+        <v>0.7746</v>
       </c>
       <c r="E11" t="n">
-        <v>3.1636</v>
+        <v>3.129</v>
       </c>
       <c r="F11" t="n">
-        <v>0.6908</v>
+        <v>2.8427</v>
       </c>
       <c r="G11" t="n">
-        <v>2.4728</v>
+        <v>0.2863</v>
       </c>
       <c r="H11" t="n">
-        <v>0.6908</v>
+        <v>4.5294</v>
       </c>
       <c r="I11" t="n">
-        <v>0.5599</v>
+        <v>2.3551</v>
       </c>
       <c r="J11" t="n">
-        <v>2.4728</v>
+        <v>0.2863</v>
       </c>
       <c r="K11" t="n">
-        <v>110</v>
+        <v>160</v>
       </c>
       <c r="L11" t="n">
-        <v>102</v>
+        <v>54</v>
       </c>
       <c r="M11" t="n">
-        <v>3.0327</v>
+        <v>2.6414</v>
       </c>
       <c r="N11" t="n">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>flamie</t>
+          <t>ropz</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.6855</v>
+        <v>2.9933</v>
       </c>
       <c r="C12" t="n">
-        <v>1.16</v>
+        <v>1.293</v>
       </c>
       <c r="D12" t="n">
-        <v>0.626</v>
+        <v>0.7133</v>
       </c>
       <c r="E12" t="n">
-        <v>2.6855</v>
+        <v>2.9933</v>
       </c>
       <c r="F12" t="n">
-        <v>2.4796</v>
+        <v>2.3978</v>
       </c>
       <c r="G12" t="n">
-        <v>0.2059</v>
+        <v>0.5955</v>
       </c>
       <c r="H12" t="n">
-        <v>2.4796</v>
+        <v>2.962</v>
       </c>
       <c r="I12" t="n">
-        <v>2.0098</v>
+        <v>1.5401</v>
       </c>
       <c r="J12" t="n">
-        <v>0.2059</v>
+        <v>0.5955</v>
       </c>
       <c r="K12" t="n">
-        <v>160</v>
+        <v>248</v>
       </c>
       <c r="L12" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="M12" t="n">
-        <v>2.2157</v>
+        <v>2.1356</v>
       </c>
       <c r="N12" t="n">
-        <v>214</v>
+        <v>301</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>NiKo</t>
+          <t>oskar</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.3169</v>
+        <v>2.9788</v>
       </c>
       <c r="C13" t="n">
-        <v>1.0008</v>
+        <v>1.2867</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4791</v>
+        <v>0.7068</v>
       </c>
       <c r="E13" t="n">
-        <v>2.3169</v>
+        <v>2.9788</v>
       </c>
       <c r="F13" t="n">
-        <v>2.3169</v>
+        <v>3.4238</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>-0.445</v>
       </c>
       <c r="H13" t="n">
-        <v>2.3169</v>
+        <v>6.5771</v>
       </c>
       <c r="I13" t="n">
-        <v>2.3169</v>
+        <v>3.4198</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>-0.445</v>
       </c>
       <c r="K13" t="n">
-        <v>148</v>
+        <v>248</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="M13" t="n">
-        <v>2.3169</v>
+        <v>2.9748</v>
       </c>
       <c r="N13" t="n">
-        <v>148</v>
+        <v>301</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>NiKo</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.2729</v>
+        <v>2.8546</v>
       </c>
       <c r="C14" t="n">
-        <v>0.9818</v>
+        <v>1.2331</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4616</v>
+        <v>0.6506999999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>2.2729</v>
+        <v>2.8546</v>
       </c>
       <c r="F14" t="n">
-        <v>2.8944</v>
+        <v>2.8546</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.6215000000000001</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>2.8944</v>
+        <v>2.9084</v>
       </c>
       <c r="I14" t="n">
-        <v>2.346</v>
+        <v>2.9084</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.6215000000000001</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="L14" t="n">
-        <v>103</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>1.7245</v>
+        <v>2.9084</v>
       </c>
       <c r="N14" t="n">
-        <v>255</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ropz</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.1556</v>
+        <v>2.5012</v>
       </c>
       <c r="C15" t="n">
-        <v>0.9311</v>
+        <v>1.0804</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4149</v>
+        <v>0.4912</v>
       </c>
       <c r="E15" t="n">
-        <v>2.1556</v>
+        <v>2.5012</v>
       </c>
       <c r="F15" t="n">
-        <v>1.5158</v>
+        <v>3.0594</v>
       </c>
       <c r="G15" t="n">
-        <v>0.6398</v>
+        <v>-0.5582</v>
       </c>
       <c r="H15" t="n">
-        <v>1.5158</v>
+        <v>5.293</v>
       </c>
       <c r="I15" t="n">
-        <v>1.2286</v>
+        <v>2.7521</v>
       </c>
       <c r="J15" t="n">
-        <v>0.6398</v>
+        <v>-0.5582</v>
       </c>
       <c r="K15" t="n">
-        <v>248</v>
+        <v>152</v>
       </c>
       <c r="L15" t="n">
-        <v>53</v>
+        <v>103</v>
       </c>
       <c r="M15" t="n">
-        <v>1.8684</v>
+        <v>2.1939</v>
       </c>
       <c r="N15" t="n">
-        <v>301</v>
+        <v>255</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>olofmeister</t>
+          <t>suNny</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.4471</v>
+        <v>2.3297</v>
       </c>
       <c r="C16" t="n">
-        <v>0.6251</v>
+        <v>1.0063</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1326</v>
+        <v>0.4137</v>
       </c>
       <c r="E16" t="n">
-        <v>1.4471</v>
+        <v>2.3297</v>
       </c>
       <c r="F16" t="n">
-        <v>1.4471</v>
+        <v>2.8063</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>-0.4766</v>
       </c>
       <c r="H16" t="n">
-        <v>1.4471</v>
+        <v>4.4014</v>
       </c>
       <c r="I16" t="n">
-        <v>1.4471</v>
+        <v>2.2885</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>-0.4766</v>
       </c>
       <c r="K16" t="n">
-        <v>148</v>
+        <v>248</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="M16" t="n">
-        <v>1.4471</v>
+        <v>1.8119</v>
       </c>
       <c r="N16" t="n">
-        <v>148</v>
+        <v>301</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>KRIMZ</t>
+          <t>Edward</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.3587</v>
+        <v>1.7759</v>
       </c>
       <c r="C17" t="n">
-        <v>0.5869</v>
+        <v>0.7671</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0974</v>
+        <v>0.1637</v>
       </c>
       <c r="E17" t="n">
-        <v>1.3587</v>
+        <v>1.7759</v>
       </c>
       <c r="F17" t="n">
-        <v>1.3587</v>
+        <v>2.165</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>-0.3891</v>
       </c>
       <c r="H17" t="n">
-        <v>1.3587</v>
+        <v>2.165</v>
       </c>
       <c r="I17" t="n">
-        <v>1.3587</v>
+        <v>1.1257</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>-0.3891</v>
       </c>
       <c r="K17" t="n">
-        <v>228</v>
+        <v>160</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="M17" t="n">
-        <v>1.3587</v>
+        <v>0.7365999999999999</v>
       </c>
       <c r="N17" t="n">
-        <v>228</v>
+        <v>214</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>KRIMZ</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.289</v>
+        <v>1.6968</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5568</v>
+        <v>0.733</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0696</v>
+        <v>0.128</v>
       </c>
       <c r="E18" t="n">
-        <v>1.289</v>
+        <v>1.6968</v>
       </c>
       <c r="F18" t="n">
-        <v>1.289</v>
+        <v>1.6968</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>1.289</v>
+        <v>1.6968</v>
       </c>
       <c r="I18" t="n">
-        <v>1.289</v>
+        <v>1.6968</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>158</v>
+        <v>228</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>1.289</v>
+        <v>1.6968</v>
       </c>
       <c r="N18" t="n">
-        <v>158</v>
+        <v>228</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>suNny</t>
+          <t>olofmeister</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.2435</v>
+        <v>1.6368</v>
       </c>
       <c r="C19" t="n">
-        <v>0.5371</v>
+        <v>0.707</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0515</v>
+        <v>0.1009</v>
       </c>
       <c r="E19" t="n">
-        <v>1.2435</v>
+        <v>1.6368</v>
       </c>
       <c r="F19" t="n">
-        <v>1.9347</v>
+        <v>1.6368</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.6912</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>1.9347</v>
+        <v>1.6368</v>
       </c>
       <c r="I19" t="n">
-        <v>1.5682</v>
+        <v>1.6368</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.6912</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>248</v>
+        <v>148</v>
       </c>
       <c r="L19" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0.877</v>
+        <v>1.6368</v>
       </c>
       <c r="N19" t="n">
-        <v>301</v>
+        <v>148</v>
       </c>
     </row>
     <row r="20">
@@ -1324,28 +1324,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.1913</v>
+        <v>1.6106</v>
       </c>
       <c r="C20" t="n">
-        <v>0.5145999999999999</v>
+        <v>0.6957</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0307</v>
+        <v>0.0891</v>
       </c>
       <c r="E20" t="n">
-        <v>1.1913</v>
+        <v>1.6106</v>
       </c>
       <c r="F20" t="n">
-        <v>1.1913</v>
+        <v>1.6106</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>1.1913</v>
+        <v>1.6106</v>
       </c>
       <c r="I20" t="n">
-        <v>1.1913</v>
+        <v>1.6106</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1357,7 +1357,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1.1913</v>
+        <v>1.6106</v>
       </c>
       <c r="N20" t="n">
         <v>158</v>
@@ -1366,47 +1366,47 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>autimatic</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.9466</v>
+        <v>1.3111</v>
       </c>
       <c r="C21" t="n">
-        <v>0.4089</v>
+        <v>0.5663</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.0668</v>
+        <v>-0.0461</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9466</v>
+        <v>1.3111</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9466</v>
+        <v>1.3111</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0.9466</v>
+        <v>1.3111</v>
       </c>
       <c r="I21" t="n">
-        <v>0.9466</v>
+        <v>1.3111</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>116</v>
+        <v>158</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.9466</v>
+        <v>1.3111</v>
       </c>
       <c r="N21" t="n">
-        <v>116</v>
+        <v>158</v>
       </c>
     </row>
     <row r="22">
@@ -1416,28 +1416,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.6821</v>
+        <v>1.1495</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2946</v>
+        <v>0.4965</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1722</v>
+        <v>-0.1191</v>
       </c>
       <c r="E22" t="n">
-        <v>0.6821</v>
+        <v>1.1495</v>
       </c>
       <c r="F22" t="n">
-        <v>0.6821</v>
+        <v>1.1495</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.6821</v>
+        <v>1.1495</v>
       </c>
       <c r="I22" t="n">
-        <v>0.6821</v>
+        <v>1.1495</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.6821</v>
+        <v>1.1495</v>
       </c>
       <c r="N22" t="n">
         <v>158</v>
@@ -1458,47 +1458,47 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Edward</t>
+          <t>autimatic</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.4382</v>
+        <v>0.9905</v>
       </c>
       <c r="C23" t="n">
-        <v>0.1893</v>
+        <v>0.4279</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.2693</v>
+        <v>-0.1909</v>
       </c>
       <c r="E23" t="n">
-        <v>0.4382</v>
+        <v>0.9905</v>
       </c>
       <c r="F23" t="n">
-        <v>1.0214</v>
+        <v>0.9905</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.5832000000000001</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>1.0214</v>
+        <v>0.9905</v>
       </c>
       <c r="I23" t="n">
-        <v>0.8279</v>
+        <v>0.9905</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.5832000000000001</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>160</v>
+        <v>116</v>
       </c>
       <c r="L23" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.2446999999999999</v>
+        <v>0.9905</v>
       </c>
       <c r="N23" t="n">
-        <v>214</v>
+        <v>116</v>
       </c>
     </row>
     <row r="24">
@@ -1508,28 +1508,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.3327</v>
+        <v>0.7079</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1437</v>
+        <v>0.3058</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.3114</v>
+        <v>-0.3184</v>
       </c>
       <c r="E24" t="n">
-        <v>0.3327</v>
+        <v>0.7079</v>
       </c>
       <c r="F24" t="n">
-        <v>0.3327</v>
+        <v>0.7079</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.3327</v>
+        <v>0.7079</v>
       </c>
       <c r="I24" t="n">
-        <v>0.3327</v>
+        <v>0.7079</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.3327</v>
+        <v>0.7079</v>
       </c>
       <c r="N24" t="n">
         <v>228</v>
@@ -1550,32 +1550,32 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>flusha</t>
+          <t>draken</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.1776</v>
+        <v>0.2307</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.0767</v>
+        <v>0.0997</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.5147</v>
+        <v>-0.5339</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.1776</v>
+        <v>0.2307</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.1776</v>
+        <v>0.2307</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.1776</v>
+        <v>0.2307</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.1776</v>
+        <v>0.2307</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.1776</v>
+        <v>0.2307</v>
       </c>
       <c r="N25" t="n">
         <v>228</v>
@@ -1596,93 +1596,93 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Stewie2K</t>
+          <t>flusha</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.2393</v>
+        <v>0.2088</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.1034</v>
+        <v>0.0902</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.5392</v>
+        <v>-0.5438</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.2393</v>
+        <v>0.2088</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.2393</v>
+        <v>0.2088</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.2393</v>
+        <v>0.2088</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.2393</v>
+        <v>0.2088</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>158</v>
+        <v>228</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.2393</v>
+        <v>0.2088</v>
       </c>
       <c r="N26" t="n">
-        <v>158</v>
+        <v>228</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>draken</t>
+          <t>Stewie2K</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.2447</v>
+        <v>0.2034</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.1057</v>
+        <v>0.08790000000000001</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.5414</v>
+        <v>-0.5462</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.2447</v>
+        <v>0.2034</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.2447</v>
+        <v>0.2034</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.2447</v>
+        <v>0.2034</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.2447</v>
+        <v>0.2034</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>228</v>
+        <v>158</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.2447</v>
+        <v>0.2034</v>
       </c>
       <c r="N27" t="n">
-        <v>228</v>
+        <v>158</v>
       </c>
     </row>
     <row r="28">
@@ -1692,28 +1692,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.3904</v>
+        <v>0.0054</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.1686</v>
+        <v>0.0023</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.5994</v>
+        <v>-0.6356000000000001</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.3904</v>
+        <v>0.0054</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.3904</v>
+        <v>0.0054</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.3904</v>
+        <v>0.0054</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.3904</v>
+        <v>0.0054</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.3904</v>
+        <v>0.0054</v>
       </c>
       <c r="N28" t="n">
         <v>148</v>
@@ -1734,139 +1734,139 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Snax</t>
+          <t>Skadoodle</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.6754</v>
+        <v>-0.1654</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.2917</v>
+        <v>-0.07140000000000001</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.713</v>
+        <v>-0.7127</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.6754</v>
+        <v>-0.1654</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.4981</v>
+        <v>-0.1654</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.1773</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.4981</v>
+        <v>-0.1654</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.4037</v>
+        <v>-0.1654</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.1773</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>248</v>
+        <v>116</v>
       </c>
       <c r="L29" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.581</v>
+        <v>-0.1654</v>
       </c>
       <c r="N29" t="n">
-        <v>301</v>
+        <v>116</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Skadoodle</t>
+          <t>Zeus</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.7534999999999999</v>
+        <v>-0.1738</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.3255</v>
+        <v>-0.0751</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.7441</v>
+        <v>-0.7165</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.7534999999999999</v>
+        <v>-0.1738</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.7534999999999999</v>
+        <v>-0.2142</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>0.0404</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.7534999999999999</v>
+        <v>-0.2142</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.7534999999999999</v>
+        <v>-0.1114</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>0.0404</v>
       </c>
       <c r="K30" t="n">
-        <v>116</v>
+        <v>160</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.7534999999999999</v>
+        <v>-0.07100000000000001</v>
       </c>
       <c r="N30" t="n">
-        <v>116</v>
+        <v>214</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>chrisJ</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.9203</v>
+        <v>-0.415</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.3975</v>
+        <v>-0.1793</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.8106</v>
+        <v>-0.8254</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.9203</v>
+        <v>-0.415</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.9203</v>
+        <v>-0.236</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>-0.179</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.9203</v>
+        <v>-0.236</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.9203</v>
+        <v>-0.1227</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>-0.179</v>
       </c>
       <c r="K31" t="n">
-        <v>148</v>
+        <v>248</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.9203</v>
+        <v>-0.3017</v>
       </c>
       <c r="N31" t="n">
-        <v>148</v>
+        <v>301</v>
       </c>
     </row>
     <row r="32">
@@ -1876,28 +1876,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.9474</v>
+        <v>-0.4269</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.4092</v>
+        <v>-0.1844</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.8214</v>
+        <v>-0.8307</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.9474</v>
+        <v>-0.4269</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.9474</v>
+        <v>-0.4269</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.9474</v>
+        <v>-0.4269</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.9474</v>
+        <v>-0.4269</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.9474</v>
+        <v>-0.4269</v>
       </c>
       <c r="N32" t="n">
         <v>116</v>
@@ -1918,231 +1918,231 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Zeus</t>
+          <t>Snax</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-1.0649</v>
+        <v>-0.464</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.46</v>
+        <v>-0.2004</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.8682</v>
+        <v>-0.8475</v>
       </c>
       <c r="E33" t="n">
-        <v>-1.0649</v>
+        <v>-0.464</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.8994</v>
+        <v>-0.3725</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.1655</v>
+        <v>-0.0915</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.8994</v>
+        <v>-0.3725</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.729</v>
+        <v>-0.1937</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.1655</v>
+        <v>-0.0915</v>
       </c>
       <c r="K33" t="n">
-        <v>160</v>
+        <v>248</v>
       </c>
       <c r="L33" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.8945</v>
+        <v>-0.2852</v>
       </c>
       <c r="N33" t="n">
-        <v>214</v>
+        <v>301</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Xizt</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-1.1994</v>
+        <v>-0.4832</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.5181</v>
+        <v>-0.2087</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.9218</v>
+        <v>-0.8562</v>
       </c>
       <c r="E34" t="n">
-        <v>-1.1994</v>
+        <v>-0.4832</v>
       </c>
       <c r="F34" t="n">
-        <v>-1.1994</v>
+        <v>-0.4832</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-1.1994</v>
+        <v>-0.4832</v>
       </c>
       <c r="I34" t="n">
-        <v>-1.1994</v>
+        <v>-0.4832</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>228</v>
+        <v>148</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-1.1994</v>
+        <v>-0.4832</v>
       </c>
       <c r="N34" t="n">
-        <v>228</v>
+        <v>148</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>tarik</t>
+          <t>Xizt</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-1.3121</v>
+        <v>-0.589</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.5668</v>
+        <v>-0.2544</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.9667</v>
+        <v>-0.9039</v>
       </c>
       <c r="E35" t="n">
-        <v>-1.3121</v>
+        <v>-0.589</v>
       </c>
       <c r="F35" t="n">
-        <v>-1.3121</v>
+        <v>-0.589</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-1.3121</v>
+        <v>-0.589</v>
       </c>
       <c r="I35" t="n">
-        <v>-1.3121</v>
+        <v>-0.589</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>158</v>
+        <v>228</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-1.3121</v>
+        <v>-0.589</v>
       </c>
       <c r="N35" t="n">
-        <v>158</v>
+        <v>228</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>tarik</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-1.3134</v>
+        <v>-0.7905</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.5673</v>
+        <v>-0.3415</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9671999999999999</v>
+        <v>-0.9949</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.3134</v>
+        <v>-0.7905</v>
       </c>
       <c r="F36" t="n">
-        <v>-1.3134</v>
+        <v>-0.7905</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-1.3134</v>
+        <v>-0.7905</v>
       </c>
       <c r="I36" t="n">
-        <v>-1.3134</v>
+        <v>-0.7905</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-1.3134</v>
+        <v>-0.7905</v>
       </c>
       <c r="N36" t="n">
-        <v>148</v>
+        <v>158</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>chrisJ</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.4592</v>
+        <v>-0.8231000000000001</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.6303</v>
+        <v>-0.3555</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.0253</v>
+        <v>-1.0096</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.4592</v>
+        <v>-0.8231000000000001</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.2059</v>
+        <v>-0.8231000000000001</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.2533</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-1.2059</v>
+        <v>-0.8231000000000001</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.9774</v>
+        <v>-0.8231000000000001</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.2533</v>
+        <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>248</v>
+        <v>148</v>
       </c>
       <c r="L37" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.2307</v>
+        <v>-0.8231000000000001</v>
       </c>
       <c r="N37" t="n">
-        <v>301</v>
+        <v>148</v>
       </c>
     </row>
     <row r="38">
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.4951</v>
+        <v>-1.0137</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.6458</v>
+        <v>-0.4379</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.0396</v>
+        <v>-1.0956</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.4951</v>
+        <v>-1.0137</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.4951</v>
+        <v>-1.0137</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.4951</v>
+        <v>-1.0137</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.4951</v>
+        <v>-1.0137</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.4951</v>
+        <v>-1.0137</v>
       </c>
       <c r="N38" t="n">
         <v>116</v>
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.528</v>
+        <v>-1.1094</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.66</v>
+        <v>-0.4792</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.0527</v>
+        <v>-1.1389</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.528</v>
+        <v>-1.1094</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.528</v>
+        <v>-1.1094</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.528</v>
+        <v>-1.1094</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.528</v>
+        <v>-1.1094</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.528</v>
+        <v>-1.1094</v>
       </c>
       <c r="N39" t="n">
         <v>116</v>
@@ -2244,31 +2244,31 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-2.1191</v>
+        <v>-1.9747</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.9154</v>
+        <v>-0.853</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.2882</v>
+        <v>-1.5295</v>
       </c>
       <c r="E40" t="n">
-        <v>-2.1191</v>
+        <v>-1.9747</v>
       </c>
       <c r="F40" t="n">
-        <v>-0.9694</v>
+        <v>-1.008</v>
       </c>
       <c r="G40" t="n">
-        <v>-1.1497</v>
+        <v>-0.9667</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.9694</v>
+        <v>-1.008</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.7857</v>
+        <v>-0.5241</v>
       </c>
       <c r="J40" t="n">
-        <v>-1.1497</v>
+        <v>-0.9667</v>
       </c>
       <c r="K40" t="n">
         <v>110</v>
@@ -2277,7 +2277,7 @@
         <v>102</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.9354</v>
+        <v>-1.4908</v>
       </c>
       <c r="N40" t="n">
         <v>212</v>
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-3.5297</v>
+        <v>-4.4217</v>
       </c>
       <c r="C41" t="n">
-        <v>-1.5247</v>
+        <v>-1.91</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.8501</v>
+        <v>-2.6342</v>
       </c>
       <c r="E41" t="n">
-        <v>-3.5297</v>
+        <v>-4.4217</v>
       </c>
       <c r="F41" t="n">
-        <v>-2.9873</v>
+        <v>-3.8221</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.5424</v>
+        <v>-0.5996</v>
       </c>
       <c r="H41" t="n">
-        <v>-2.9873</v>
+        <v>-3.8221</v>
       </c>
       <c r="I41" t="n">
-        <v>-2.4213</v>
+        <v>-1.9873</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.5424</v>
+        <v>-0.5996</v>
       </c>
       <c r="K41" t="n">
         <v>152</v>
@@ -2323,7 +2323,7 @@
         <v>103</v>
       </c>
       <c r="M41" t="n">
-        <v>-2.9637</v>
+        <v>-2.5869</v>
       </c>
       <c r="N41" t="n">
         <v>255</v>
@@ -2429,10 +2429,10 @@
         <v>1.8</v>
       </c>
       <c r="I2" t="n">
-        <v>1.6902</v>
+        <v>1.4575</v>
       </c>
       <c r="J2" t="n">
-        <v>35.4942</v>
+        <v>30.6075</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.78</v>
       </c>
       <c r="I3" t="n">
-        <v>1.6548</v>
+        <v>1.4344</v>
       </c>
       <c r="J3" t="n">
-        <v>34.7508</v>
+        <v>30.1224</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>1.29</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6244</v>
+        <v>0.7321</v>
       </c>
       <c r="J4" t="n">
-        <v>13.1124</v>
+        <v>15.3741</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>1.18</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3662</v>
+        <v>0.4687</v>
       </c>
       <c r="J5" t="n">
-        <v>7.6902</v>
+        <v>9.842700000000001</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.98</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2811</v>
+        <v>-0.1921</v>
       </c>
       <c r="J6" t="n">
-        <v>-5.9031</v>
+        <v>-4.0341</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>0.85</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1173</v>
+        <v>-0.121</v>
       </c>
       <c r="J7" t="n">
-        <v>-2.4633</v>
+        <v>-2.541</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>0.64</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4516</v>
+        <v>-0.3413</v>
       </c>
       <c r="J8" t="n">
-        <v>-9.483599999999999</v>
+        <v>-7.1673</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>0.6</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.5345</v>
+        <v>-0.3762</v>
       </c>
       <c r="J9" t="n">
-        <v>-11.2245</v>
+        <v>-7.9002</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.5992</v>
+        <v>-0.4127</v>
       </c>
       <c r="J10" t="n">
-        <v>-12.5832</v>
+        <v>-8.666700000000001</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.45</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.7546</v>
+        <v>-0.516</v>
       </c>
       <c r="J11" t="n">
-        <v>-15.8466</v>
+        <v>-10.836</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.42</v>
       </c>
       <c r="I12" t="n">
-        <v>1.1068</v>
+        <v>1.061</v>
       </c>
       <c r="J12" t="n">
-        <v>30.9904</v>
+        <v>29.708</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.07</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1992</v>
+        <v>0.237</v>
       </c>
       <c r="J13" t="n">
-        <v>5.5776</v>
+        <v>6.636</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>1.05</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1314</v>
+        <v>0.1752</v>
       </c>
       <c r="J14" t="n">
-        <v>3.6792</v>
+        <v>4.9056</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>1.05</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1314</v>
+        <v>0.1752</v>
       </c>
       <c r="J15" t="n">
-        <v>3.6792</v>
+        <v>4.9056</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.3254</v>
+        <v>-0.258</v>
       </c>
       <c r="J16" t="n">
-        <v>-9.1112</v>
+        <v>-7.224</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1</v>
       </c>
       <c r="I17" t="n">
-        <v>0.0373</v>
+        <v>0.0114</v>
       </c>
       <c r="J17" t="n">
-        <v>1.0444</v>
+        <v>0.3192</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>0.99</v>
       </c>
       <c r="I18" t="n">
-        <v>0.002</v>
+        <v>-0.015</v>
       </c>
       <c r="J18" t="n">
-        <v>0.056</v>
+        <v>-0.42</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>0.96</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.0707</v>
+        <v>-0.0582</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.9796</v>
+        <v>-1.6296</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.95</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.0931</v>
+        <v>-0.0708</v>
       </c>
       <c r="J20" t="n">
-        <v>-2.6068</v>
+        <v>-1.9824</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.78</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.3964</v>
+        <v>-0.2512</v>
       </c>
       <c r="J21" t="n">
-        <v>-11.0992</v>
+        <v>-7.0336</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.29</v>
       </c>
       <c r="I22" t="n">
-        <v>0.4821</v>
+        <v>0.4755</v>
       </c>
       <c r="J22" t="n">
-        <v>13.9809</v>
+        <v>13.7895</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.17</v>
       </c>
       <c r="I23" t="n">
-        <v>0.3122</v>
+        <v>0.3511</v>
       </c>
       <c r="J23" t="n">
-        <v>9.053800000000001</v>
+        <v>10.1819</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>1.17</v>
       </c>
       <c r="I24" t="n">
-        <v>0.3122</v>
+        <v>0.3511</v>
       </c>
       <c r="J24" t="n">
-        <v>9.053800000000001</v>
+        <v>10.1819</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.97</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.1202</v>
+        <v>-0.0575</v>
       </c>
       <c r="J25" t="n">
-        <v>-3.4858</v>
+        <v>-1.6675</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.78</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.4272</v>
+        <v>-0.2674</v>
       </c>
       <c r="J26" t="n">
-        <v>-12.3888</v>
+        <v>-7.7546</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.34</v>
       </c>
       <c r="I27" t="n">
-        <v>0.9382</v>
+        <v>0.6802</v>
       </c>
       <c r="J27" t="n">
-        <v>27.2078</v>
+        <v>19.7258</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.27</v>
       </c>
       <c r="I28" t="n">
-        <v>0.7786</v>
+        <v>0.5821</v>
       </c>
       <c r="J28" t="n">
-        <v>22.5794</v>
+        <v>16.8809</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.2</v>
       </c>
       <c r="I29" t="n">
-        <v>0.6066</v>
+        <v>0.4808</v>
       </c>
       <c r="J29" t="n">
-        <v>17.5914</v>
+        <v>13.9432</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.91</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.4137</v>
+        <v>-0.348</v>
       </c>
       <c r="J30" t="n">
-        <v>-11.9973</v>
+        <v>-10.092</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.78</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.7504999999999999</v>
+        <v>-0.7013</v>
       </c>
       <c r="J31" t="n">
-        <v>-21.7645</v>
+        <v>-20.3377</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.13</v>
       </c>
       <c r="I32" t="n">
-        <v>0.3261</v>
+        <v>0.3438</v>
       </c>
       <c r="J32" t="n">
-        <v>8.1525</v>
+        <v>8.595000000000001</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>0.9</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.156</v>
+        <v>-0.1217</v>
       </c>
       <c r="J33" t="n">
-        <v>-3.9</v>
+        <v>-3.0425</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>0.83</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.2957</v>
+        <v>-0.1932</v>
       </c>
       <c r="J34" t="n">
-        <v>-7.3925</v>
+        <v>-4.83</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.78</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.3758</v>
+        <v>-0.2429</v>
       </c>
       <c r="J35" t="n">
-        <v>-9.395</v>
+        <v>-6.0725</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.71</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.4777</v>
+        <v>-0.3107</v>
       </c>
       <c r="J36" t="n">
-        <v>-11.9425</v>
+        <v>-7.7675</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.58</v>
       </c>
       <c r="I37" t="n">
-        <v>1.3261</v>
+        <v>0.9426</v>
       </c>
       <c r="J37" t="n">
-        <v>33.1525</v>
+        <v>23.565</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.52</v>
       </c>
       <c r="I38" t="n">
-        <v>1.2081</v>
+        <v>0.8689</v>
       </c>
       <c r="J38" t="n">
-        <v>30.2025</v>
+        <v>21.7225</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.34</v>
       </c>
       <c r="I39" t="n">
-        <v>0.8167</v>
+        <v>0.6424</v>
       </c>
       <c r="J39" t="n">
-        <v>20.4175</v>
+        <v>16.06</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>1.31</v>
       </c>
       <c r="I40" t="n">
-        <v>0.7309</v>
+        <v>0.6045</v>
       </c>
       <c r="J40" t="n">
-        <v>18.2725</v>
+        <v>15.1125</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.7309</v>
+        <v>-0.6742</v>
       </c>
       <c r="J41" t="n">
-        <v>-18.2725</v>
+        <v>-16.855</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.62</v>
       </c>
       <c r="I42" t="n">
-        <v>1.5188</v>
+        <v>1.0611</v>
       </c>
       <c r="J42" t="n">
-        <v>41.0076</v>
+        <v>28.6497</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.08</v>
       </c>
       <c r="I43" t="n">
-        <v>0.2706</v>
+        <v>0.271</v>
       </c>
       <c r="J43" t="n">
-        <v>7.3062</v>
+        <v>7.317</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.02</v>
       </c>
       <c r="I44" t="n">
-        <v>0.0382</v>
+        <v>0.0785</v>
       </c>
       <c r="J44" t="n">
-        <v>1.0314</v>
+        <v>2.1195</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.96</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.2452</v>
+        <v>-0.1844</v>
       </c>
       <c r="J45" t="n">
-        <v>-6.6204</v>
+        <v>-4.9788</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.7</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.9271</v>
+        <v>-0.8948</v>
       </c>
       <c r="J46" t="n">
-        <v>-25.0317</v>
+        <v>-24.1596</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.02</v>
       </c>
       <c r="I47" t="n">
-        <v>0.098</v>
+        <v>0.0795</v>
       </c>
       <c r="J47" t="n">
-        <v>2.646</v>
+        <v>2.1465</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>0.98</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.0241</v>
+        <v>-0.0307</v>
       </c>
       <c r="J48" t="n">
-        <v>-0.6506999999999999</v>
+        <v>-0.8289</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.1162</v>
+        <v>-0.0827</v>
       </c>
       <c r="J49" t="n">
-        <v>-3.1374</v>
+        <v>-2.2329</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.89</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.2217</v>
+        <v>-0.1382</v>
       </c>
       <c r="J50" t="n">
-        <v>-5.9859</v>
+        <v>-3.7314</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.85</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.2895</v>
+        <v>-0.1805</v>
       </c>
       <c r="J51" t="n">
-        <v>-7.8165</v>
+        <v>-4.8735</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.41</v>
       </c>
       <c r="I52" t="n">
-        <v>1.0616</v>
+        <v>0.7621</v>
       </c>
       <c r="J52" t="n">
-        <v>27.6016</v>
+        <v>19.8146</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.28</v>
       </c>
       <c r="I53" t="n">
-        <v>0.7725</v>
+        <v>0.5856</v>
       </c>
       <c r="J53" t="n">
-        <v>20.085</v>
+        <v>15.2256</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>1.19</v>
       </c>
       <c r="I54" t="n">
-        <v>0.5452</v>
+        <v>0.4579</v>
       </c>
       <c r="J54" t="n">
-        <v>14.1752</v>
+        <v>11.9054</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>1.12</v>
       </c>
       <c r="I55" t="n">
-        <v>0.3234</v>
+        <v>0.3541</v>
       </c>
       <c r="J55" t="n">
-        <v>8.4084</v>
+        <v>9.2066</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.76</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.8112</v>
+        <v>-0.7654</v>
       </c>
       <c r="J56" t="n">
-        <v>-21.0912</v>
+        <v>-19.9004</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.29</v>
       </c>
       <c r="I57" t="n">
-        <v>0.5417999999999999</v>
+        <v>0.516</v>
       </c>
       <c r="J57" t="n">
-        <v>14.0868</v>
+        <v>13.416</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.02</v>
       </c>
       <c r="I58" t="n">
-        <v>0.1122</v>
+        <v>0.089</v>
       </c>
       <c r="J58" t="n">
-        <v>2.9172</v>
+        <v>2.314</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>0.97</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.0316</v>
+        <v>-0.0408</v>
       </c>
       <c r="J59" t="n">
-        <v>-0.8216</v>
+        <v>-1.0608</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.66</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.553</v>
+        <v>-0.3623</v>
       </c>
       <c r="J60" t="n">
-        <v>-14.378</v>
+        <v>-9.4198</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.57</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.6671</v>
+        <v>-0.4459</v>
       </c>
       <c r="J61" t="n">
-        <v>-17.3446</v>
+        <v>-11.5934</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.45</v>
       </c>
       <c r="I62" t="n">
-        <v>0.6743</v>
+        <v>0.6356000000000001</v>
       </c>
       <c r="J62" t="n">
-        <v>19.5547</v>
+        <v>18.4324</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.34</v>
       </c>
       <c r="I63" t="n">
-        <v>0.5399</v>
+        <v>0.4985</v>
       </c>
       <c r="J63" t="n">
-        <v>15.6571</v>
+        <v>14.4565</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.09</v>
       </c>
       <c r="I64" t="n">
-        <v>0.1576</v>
+        <v>0.16</v>
       </c>
       <c r="J64" t="n">
-        <v>4.5704</v>
+        <v>4.64</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>0.95</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.1664</v>
+        <v>-0.0861</v>
       </c>
       <c r="J65" t="n">
-        <v>-4.8256</v>
+        <v>-2.4969</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.66</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.586</v>
+        <v>-0.3838</v>
       </c>
       <c r="J66" t="n">
-        <v>-16.994</v>
+        <v>-11.1302</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.14</v>
       </c>
       <c r="I67" t="n">
-        <v>0.2861</v>
+        <v>0.2281</v>
       </c>
       <c r="J67" t="n">
-        <v>8.296900000000001</v>
+        <v>6.6149</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.11</v>
       </c>
       <c r="I68" t="n">
-        <v>0.2371</v>
+        <v>0.1863</v>
       </c>
       <c r="J68" t="n">
-        <v>6.8759</v>
+        <v>5.4027</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>1.07</v>
       </c>
       <c r="I69" t="n">
-        <v>0.1657</v>
+        <v>0.1278</v>
       </c>
       <c r="J69" t="n">
-        <v>4.8053</v>
+        <v>3.7062</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.92</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.1993</v>
+        <v>-0.1138</v>
       </c>
       <c r="J70" t="n">
-        <v>-5.7797</v>
+        <v>-3.3002</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.86</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.2988</v>
+        <v>-0.1797</v>
       </c>
       <c r="J71" t="n">
-        <v>-8.6652</v>
+        <v>-5.2113</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.38</v>
       </c>
       <c r="I72" t="n">
-        <v>0.9955000000000001</v>
+        <v>0.9827</v>
       </c>
       <c r="J72" t="n">
-        <v>29.865</v>
+        <v>29.481</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.37</v>
       </c>
       <c r="I73" t="n">
-        <v>0.9739</v>
+        <v>0.9636</v>
       </c>
       <c r="J73" t="n">
-        <v>29.217</v>
+        <v>28.908</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1.22</v>
       </c>
       <c r="I74" t="n">
-        <v>0.6223</v>
+        <v>0.6166</v>
       </c>
       <c r="J74" t="n">
-        <v>18.669</v>
+        <v>18.498</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>1.13</v>
       </c>
       <c r="I75" t="n">
-        <v>0.3506</v>
+        <v>0.3939</v>
       </c>
       <c r="J75" t="n">
-        <v>10.518</v>
+        <v>11.817</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.68</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.9893999999999999</v>
+        <v>-0.963</v>
       </c>
       <c r="J76" t="n">
-        <v>-29.682</v>
+        <v>-28.89</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.05</v>
       </c>
       <c r="I77" t="n">
-        <v>0.182</v>
+        <v>0.1707</v>
       </c>
       <c r="J77" t="n">
-        <v>5.46</v>
+        <v>5.121</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>0.91</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.1459</v>
+        <v>-0.1124</v>
       </c>
       <c r="J78" t="n">
-        <v>-4.377</v>
+        <v>-3.372</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>0.88</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.2125</v>
+        <v>-0.144</v>
       </c>
       <c r="J79" t="n">
-        <v>-6.375</v>
+        <v>-4.32</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.84</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.2862</v>
+        <v>-0.185</v>
       </c>
       <c r="J80" t="n">
-        <v>-8.586</v>
+        <v>-5.55</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.75</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.4256</v>
+        <v>-0.2742</v>
       </c>
       <c r="J81" t="n">
-        <v>-12.768</v>
+        <v>-8.226000000000001</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.7</v>
       </c>
       <c r="I82" t="n">
-        <v>1.6114</v>
+        <v>1.3977</v>
       </c>
       <c r="J82" t="n">
-        <v>40.285</v>
+        <v>34.9425</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.28</v>
       </c>
       <c r="I83" t="n">
-        <v>0.7538</v>
+        <v>0.7516</v>
       </c>
       <c r="J83" t="n">
-        <v>18.845</v>
+        <v>18.79</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.16</v>
       </c>
       <c r="I84" t="n">
-        <v>0.4176</v>
+        <v>0.4657</v>
       </c>
       <c r="J84" t="n">
-        <v>10.44</v>
+        <v>11.6425</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>1.06</v>
       </c>
       <c r="I85" t="n">
-        <v>0.1227</v>
+        <v>0.188</v>
       </c>
       <c r="J85" t="n">
-        <v>3.0675</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.72</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.9085</v>
+        <v>-0.8722</v>
       </c>
       <c r="J86" t="n">
-        <v>-22.7125</v>
+        <v>-21.805</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.16</v>
       </c>
       <c r="I87" t="n">
-        <v>0.3654</v>
+        <v>0.4045</v>
       </c>
       <c r="J87" t="n">
-        <v>9.135</v>
+        <v>10.1125</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.12</v>
       </c>
       <c r="I88" t="n">
-        <v>0.3033</v>
+        <v>0.3237</v>
       </c>
       <c r="J88" t="n">
-        <v>7.5825</v>
+        <v>8.092499999999999</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>0.89</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.189</v>
+        <v>-0.134</v>
       </c>
       <c r="J89" t="n">
-        <v>-4.725</v>
+        <v>-3.35</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.67</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.5367</v>
+        <v>-0.3511</v>
       </c>
       <c r="J90" t="n">
-        <v>-13.4175</v>
+        <v>-8.7775</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.6</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.6272</v>
+        <v>-0.4165</v>
       </c>
       <c r="J91" t="n">
-        <v>-15.68</v>
+        <v>-10.4125</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.43</v>
       </c>
       <c r="I92" t="n">
-        <v>1.0658</v>
+        <v>1.0447</v>
       </c>
       <c r="J92" t="n">
-        <v>27.7108</v>
+        <v>27.1622</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.38</v>
       </c>
       <c r="I93" t="n">
-        <v>0.9587</v>
+        <v>0.9622000000000001</v>
       </c>
       <c r="J93" t="n">
-        <v>24.9262</v>
+        <v>25.0172</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.22</v>
       </c>
       <c r="I94" t="n">
-        <v>0.5567</v>
+        <v>0.6036</v>
       </c>
       <c r="J94" t="n">
-        <v>14.4742</v>
+        <v>15.6936</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>1.2</v>
       </c>
       <c r="I95" t="n">
-        <v>0.4989</v>
+        <v>0.5564</v>
       </c>
       <c r="J95" t="n">
-        <v>12.9714</v>
+        <v>14.4664</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.9</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.4837</v>
+        <v>-0.4099</v>
       </c>
       <c r="J96" t="n">
-        <v>-12.5762</v>
+        <v>-10.6574</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.18</v>
       </c>
       <c r="I97" t="n">
-        <v>0.4177</v>
+        <v>0.4726</v>
       </c>
       <c r="J97" t="n">
-        <v>10.8602</v>
+        <v>12.2876</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>0.98</v>
       </c>
       <c r="I98" t="n">
-        <v>0.0225</v>
+        <v>-0.014</v>
       </c>
       <c r="J98" t="n">
-        <v>0.585</v>
+        <v>-0.364</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>0.75</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.4066</v>
+        <v>-0.2668</v>
       </c>
       <c r="J99" t="n">
-        <v>-10.5716</v>
+        <v>-6.9368</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.65</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.549</v>
+        <v>-0.3621</v>
       </c>
       <c r="J100" t="n">
-        <v>-14.274</v>
+        <v>-9.4146</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.59</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.6278</v>
+        <v>-0.4182</v>
       </c>
       <c r="J101" t="n">
-        <v>-16.3228</v>
+        <v>-10.8732</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.55</v>
       </c>
       <c r="I102" t="n">
-        <v>1.277</v>
+        <v>1.1836</v>
       </c>
       <c r="J102" t="n">
-        <v>33.202</v>
+        <v>30.7736</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.38</v>
       </c>
       <c r="I103" t="n">
-        <v>0.9229000000000001</v>
+        <v>0.946</v>
       </c>
       <c r="J103" t="n">
-        <v>23.9954</v>
+        <v>24.596</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.31</v>
       </c>
       <c r="I104" t="n">
-        <v>0.7558</v>
+        <v>0.7956</v>
       </c>
       <c r="J104" t="n">
-        <v>19.6508</v>
+        <v>20.6856</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>1.27</v>
       </c>
       <c r="I105" t="n">
-        <v>0.6379</v>
+        <v>0.7081</v>
       </c>
       <c r="J105" t="n">
-        <v>16.5854</v>
+        <v>18.4106</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.95</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.3557</v>
+        <v>-0.2726</v>
       </c>
       <c r="J106" t="n">
-        <v>-9.248200000000001</v>
+        <v>-7.0876</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.03</v>
       </c>
       <c r="I107" t="n">
-        <v>0.1615</v>
+        <v>0.1395</v>
       </c>
       <c r="J107" t="n">
-        <v>4.199</v>
+        <v>3.627</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>0.98</v>
       </c>
       <c r="I108" t="n">
-        <v>0.0199</v>
+        <v>-0.0151</v>
       </c>
       <c r="J108" t="n">
-        <v>0.5174</v>
+        <v>-0.3926</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.3124</v>
+        <v>-0.2093</v>
       </c>
       <c r="J109" t="n">
-        <v>-8.122400000000001</v>
+        <v>-5.4418</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.79</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.3462</v>
+        <v>-0.2288</v>
       </c>
       <c r="J110" t="n">
-        <v>-9.001200000000001</v>
+        <v>-5.9488</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.57</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.6546</v>
+        <v>-0.4376</v>
       </c>
       <c r="J111" t="n">
-        <v>-17.0196</v>
+        <v>-11.3776</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.44</v>
       </c>
       <c r="I112" t="n">
-        <v>1.1212</v>
+        <v>1.074</v>
       </c>
       <c r="J112" t="n">
-        <v>38.1208</v>
+        <v>36.516</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.16</v>
       </c>
       <c r="I113" t="n">
-        <v>0.4493</v>
+        <v>0.4694</v>
       </c>
       <c r="J113" t="n">
-        <v>15.2762</v>
+        <v>15.9596</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>1.15</v>
       </c>
       <c r="I114" t="n">
-        <v>0.4109</v>
+        <v>0.4448</v>
       </c>
       <c r="J114" t="n">
-        <v>13.9706</v>
+        <v>15.1232</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>1.13</v>
       </c>
       <c r="I115" t="n">
-        <v>0.349</v>
+        <v>0.3935</v>
       </c>
       <c r="J115" t="n">
-        <v>11.866</v>
+        <v>13.379</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.91</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.4349</v>
+        <v>-0.3635</v>
       </c>
       <c r="J116" t="n">
-        <v>-14.7866</v>
+        <v>-12.359</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.11</v>
       </c>
       <c r="I117" t="n">
-        <v>0.2629</v>
+        <v>0.2803</v>
       </c>
       <c r="J117" t="n">
-        <v>8.938599999999999</v>
+        <v>9.530200000000001</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.08</v>
       </c>
       <c r="I118" t="n">
-        <v>0.2116</v>
+        <v>0.2174</v>
       </c>
       <c r="J118" t="n">
-        <v>7.1944</v>
+        <v>7.3916</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>0.9</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.2106</v>
+        <v>-0.129</v>
       </c>
       <c r="J119" t="n">
-        <v>-7.1604</v>
+        <v>-4.386</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.86</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.2788</v>
+        <v>-0.1719</v>
       </c>
       <c r="J120" t="n">
-        <v>-9.479200000000001</v>
+        <v>-5.8446</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.3567</v>
+        <v>-0.2233</v>
       </c>
       <c r="J121" t="n">
-        <v>-12.1278</v>
+        <v>-7.5922</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.26</v>
       </c>
       <c r="I122" t="n">
-        <v>0.8177</v>
+        <v>0.7785</v>
       </c>
       <c r="J122" t="n">
-        <v>24.531</v>
+        <v>23.355</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.18</v>
       </c>
       <c r="I123" t="n">
-        <v>0.6216</v>
+        <v>0.5722</v>
       </c>
       <c r="J123" t="n">
-        <v>18.648</v>
+        <v>17.166</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>0.9</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.392</v>
+        <v>-0.3466</v>
       </c>
       <c r="J124" t="n">
-        <v>-11.76</v>
+        <v>-10.398</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.82</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.6132</v>
+        <v>-0.5663</v>
       </c>
       <c r="J125" t="n">
-        <v>-18.396</v>
+        <v>-16.989</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.8</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.6642</v>
+        <v>-0.6187</v>
       </c>
       <c r="J126" t="n">
-        <v>-19.926</v>
+        <v>-18.561</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.64</v>
       </c>
       <c r="I127" t="n">
-        <v>0.8613</v>
+        <v>1.0539</v>
       </c>
       <c r="J127" t="n">
-        <v>25.839</v>
+        <v>31.617</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.21</v>
       </c>
       <c r="I128" t="n">
-        <v>0.3288</v>
+        <v>0.4135</v>
       </c>
       <c r="J128" t="n">
-        <v>9.864000000000001</v>
+        <v>12.405</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>1.11</v>
       </c>
       <c r="I129" t="n">
-        <v>0.156</v>
+        <v>0.2353</v>
       </c>
       <c r="J129" t="n">
-        <v>4.68</v>
+        <v>7.059</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>1.01</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.0346</v>
+        <v>0.0066</v>
       </c>
       <c r="J130" t="n">
-        <v>-1.038</v>
+        <v>0.198</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.97</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.1476</v>
+        <v>-0.0689</v>
       </c>
       <c r="J131" t="n">
-        <v>-4.428</v>
+        <v>-2.067</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>0.97</v>
       </c>
       <c r="I132" t="n">
-        <v>0.0891</v>
+        <v>0.0534</v>
       </c>
       <c r="J132" t="n">
-        <v>1.8711</v>
+        <v>1.1214</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I133" t="n">
-        <v>-0.3801</v>
+        <v>-0.2976</v>
       </c>
       <c r="J133" t="n">
-        <v>-7.9821</v>
+        <v>-6.2496</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>0.6</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.5466</v>
+        <v>-0.379</v>
       </c>
       <c r="J134" t="n">
-        <v>-11.4786</v>
+        <v>-7.959</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.52</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.6654</v>
+        <v>-0.4533</v>
       </c>
       <c r="J135" t="n">
-        <v>-13.9734</v>
+        <v>-9.519299999999999</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.41</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.8117</v>
+        <v>-0.5571</v>
       </c>
       <c r="J136" t="n">
-        <v>-17.0457</v>
+        <v>-11.6991</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.71</v>
       </c>
       <c r="I137" t="n">
-        <v>1.5006</v>
+        <v>1.341</v>
       </c>
       <c r="J137" t="n">
-        <v>31.5126</v>
+        <v>28.161</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.66</v>
       </c>
       <c r="I138" t="n">
-        <v>1.4073</v>
+        <v>1.2831</v>
       </c>
       <c r="J138" t="n">
-        <v>29.5533</v>
+        <v>26.9451</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>1.51</v>
       </c>
       <c r="I139" t="n">
-        <v>1.1054</v>
+        <v>1.1078</v>
       </c>
       <c r="J139" t="n">
-        <v>23.2134</v>
+        <v>23.2638</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>1.51</v>
       </c>
       <c r="I140" t="n">
-        <v>1.1054</v>
+        <v>1.1078</v>
       </c>
       <c r="J140" t="n">
-        <v>23.2134</v>
+        <v>23.2638</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.97</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.331</v>
+        <v>-0.2424</v>
       </c>
       <c r="J141" t="n">
-        <v>-6.951</v>
+        <v>-5.0904</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.22</v>
       </c>
       <c r="I142" t="n">
-        <v>0.4004</v>
+        <v>0.4645</v>
       </c>
       <c r="J142" t="n">
-        <v>14.4144</v>
+        <v>16.722</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.21</v>
       </c>
       <c r="I143" t="n">
-        <v>0.3862</v>
+        <v>0.4465</v>
       </c>
       <c r="J143" t="n">
-        <v>13.9032</v>
+        <v>16.074</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>0.95</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.1479</v>
+        <v>-0.0794</v>
       </c>
       <c r="J144" t="n">
-        <v>-5.3244</v>
+        <v>-2.8584</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.1671</v>
+        <v>-0.0917</v>
       </c>
       <c r="J145" t="n">
-        <v>-6.0156</v>
+        <v>-3.3012</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.85</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.3176</v>
+        <v>-0.1918</v>
       </c>
       <c r="J146" t="n">
-        <v>-11.4336</v>
+        <v>-6.9048</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.19</v>
       </c>
       <c r="I147" t="n">
-        <v>0.5742</v>
+        <v>0.555</v>
       </c>
       <c r="J147" t="n">
-        <v>20.6712</v>
+        <v>19.98</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.1</v>
       </c>
       <c r="I148" t="n">
-        <v>0.296</v>
+        <v>0.3218</v>
       </c>
       <c r="J148" t="n">
-        <v>10.656</v>
+        <v>11.5848</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.1</v>
       </c>
       <c r="I149" t="n">
-        <v>0.296</v>
+        <v>0.3218</v>
       </c>
       <c r="J149" t="n">
-        <v>10.656</v>
+        <v>11.5848</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>1.09</v>
       </c>
       <c r="I150" t="n">
-        <v>0.2623</v>
+        <v>0.2941</v>
       </c>
       <c r="J150" t="n">
-        <v>9.4428</v>
+        <v>10.5876</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>1.07</v>
       </c>
       <c r="I151" t="n">
-        <v>0.1963</v>
+        <v>0.2361</v>
       </c>
       <c r="J151" t="n">
-        <v>7.0668</v>
+        <v>8.499599999999999</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.08</v>
       </c>
       <c r="I152" t="n">
-        <v>0.2279</v>
+        <v>0.1765</v>
       </c>
       <c r="J152" t="n">
-        <v>6.837</v>
+        <v>5.295</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.07</v>
       </c>
       <c r="I153" t="n">
-        <v>0.21</v>
+        <v>0.1596</v>
       </c>
       <c r="J153" t="n">
-        <v>6.3</v>
+        <v>4.788</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>1.03</v>
       </c>
       <c r="I154" t="n">
-        <v>0.1315</v>
+        <v>0.0868</v>
       </c>
       <c r="J154" t="n">
-        <v>3.945</v>
+        <v>2.604</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.71</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.4881</v>
+        <v>-0.3159</v>
       </c>
       <c r="J155" t="n">
-        <v>-14.643</v>
+        <v>-9.477</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.66</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.5547</v>
+        <v>-0.3633</v>
       </c>
       <c r="J156" t="n">
-        <v>-16.641</v>
+        <v>-10.899</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.5</v>
       </c>
       <c r="I157" t="n">
-        <v>0.718</v>
+        <v>0.6358</v>
       </c>
       <c r="J157" t="n">
-        <v>21.54</v>
+        <v>19.074</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.22</v>
       </c>
       <c r="I158" t="n">
-        <v>0.3614</v>
+        <v>0.3114</v>
       </c>
       <c r="J158" t="n">
-        <v>10.842</v>
+        <v>9.342000000000001</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.08</v>
       </c>
       <c r="I159" t="n">
-        <v>0.1179</v>
+        <v>0.1296</v>
       </c>
       <c r="J159" t="n">
-        <v>3.537</v>
+        <v>3.888</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>1.07</v>
       </c>
       <c r="I160" t="n">
-        <v>0.0998</v>
+        <v>0.1146</v>
       </c>
       <c r="J160" t="n">
-        <v>2.994</v>
+        <v>3.438</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.86</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.3257</v>
+        <v>-0.1933</v>
       </c>
       <c r="J161" t="n">
-        <v>-9.771000000000001</v>
+        <v>-5.799</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.67</v>
       </c>
       <c r="I162" t="n">
-        <v>1.49</v>
+        <v>1.3224</v>
       </c>
       <c r="J162" t="n">
-        <v>34.27</v>
+        <v>30.4152</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.53</v>
       </c>
       <c r="I163" t="n">
-        <v>1.2214</v>
+        <v>1.1524</v>
       </c>
       <c r="J163" t="n">
-        <v>28.0922</v>
+        <v>26.5052</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>1.24</v>
       </c>
       <c r="I164" t="n">
-        <v>0.5426</v>
+        <v>0.6324</v>
       </c>
       <c r="J164" t="n">
-        <v>12.4798</v>
+        <v>14.5452</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>1.16</v>
       </c>
       <c r="I165" t="n">
-        <v>0.3443</v>
+        <v>0.4351</v>
       </c>
       <c r="J165" t="n">
-        <v>7.9189</v>
+        <v>10.0073</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>1.03</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.0276</v>
+        <v>0.0543</v>
       </c>
       <c r="J166" t="n">
-        <v>-0.6348</v>
+        <v>1.2489</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>0.88</v>
       </c>
       <c r="I167" t="n">
-        <v>-0.1268</v>
+        <v>-0.1213</v>
       </c>
       <c r="J167" t="n">
-        <v>-2.9164</v>
+        <v>-2.7899</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>0.86</v>
       </c>
       <c r="I168" t="n">
-        <v>-0.1604</v>
+        <v>-0.1439</v>
       </c>
       <c r="J168" t="n">
-        <v>-3.6892</v>
+        <v>-3.3097</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>0.85</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.1771</v>
+        <v>-0.1549</v>
       </c>
       <c r="J169" t="n">
-        <v>-4.0733</v>
+        <v>-3.5627</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.67</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.4893</v>
+        <v>-0.3298</v>
       </c>
       <c r="J170" t="n">
-        <v>-11.2539</v>
+        <v>-7.5854</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.43</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.8083</v>
+        <v>-0.5536</v>
       </c>
       <c r="J171" t="n">
-        <v>-18.5909</v>
+        <v>-12.7328</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.6</v>
       </c>
       <c r="I172" t="n">
-        <v>1.4451</v>
+        <v>1.285</v>
       </c>
       <c r="J172" t="n">
-        <v>39.0177</v>
+        <v>34.695</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.08</v>
       </c>
       <c r="I173" t="n">
-        <v>0.2064</v>
+        <v>0.2581</v>
       </c>
       <c r="J173" t="n">
-        <v>5.5728</v>
+        <v>6.9687</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>1.06</v>
       </c>
       <c r="I174" t="n">
-        <v>0.1426</v>
+        <v>0.1978</v>
       </c>
       <c r="J174" t="n">
-        <v>3.8502</v>
+        <v>5.3406</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>1.02</v>
       </c>
       <c r="I175" t="n">
-        <v>0.0011</v>
+        <v>0.0615</v>
       </c>
       <c r="J175" t="n">
-        <v>0.0297</v>
+        <v>1.6605</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.96</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.2753</v>
+        <v>-0.2026</v>
       </c>
       <c r="J176" t="n">
-        <v>-7.4331</v>
+        <v>-5.4702</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.22</v>
       </c>
       <c r="I177" t="n">
-        <v>0.4218</v>
+        <v>0.485</v>
       </c>
       <c r="J177" t="n">
-        <v>11.3886</v>
+        <v>13.095</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.2</v>
       </c>
       <c r="I178" t="n">
-        <v>0.3934</v>
+        <v>0.4481</v>
       </c>
       <c r="J178" t="n">
-        <v>10.6218</v>
+        <v>12.0987</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.12</v>
       </c>
       <c r="I179" t="n">
-        <v>0.2718</v>
+        <v>0.2944</v>
       </c>
       <c r="J179" t="n">
-        <v>7.3386</v>
+        <v>7.9488</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>0.75</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.4477</v>
+        <v>-0.285</v>
       </c>
       <c r="J180" t="n">
-        <v>-12.0879</v>
+        <v>-7.695</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.57</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.678</v>
+        <v>-0.4537</v>
       </c>
       <c r="J181" t="n">
-        <v>-18.306</v>
+        <v>-12.2499</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.22</v>
       </c>
       <c r="I182" t="n">
-        <v>0.6801</v>
+        <v>0.6464</v>
       </c>
       <c r="J182" t="n">
-        <v>19.0428</v>
+        <v>18.0992</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.07</v>
       </c>
       <c r="I183" t="n">
-        <v>0.2505</v>
+        <v>0.2444</v>
       </c>
       <c r="J183" t="n">
-        <v>7.014</v>
+        <v>6.8432</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>1.06</v>
       </c>
       <c r="I184" t="n">
-        <v>0.2061</v>
+        <v>0.2152</v>
       </c>
       <c r="J184" t="n">
-        <v>5.7708</v>
+        <v>6.0256</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>1.03</v>
       </c>
       <c r="I185" t="n">
-        <v>0.0886</v>
+        <v>0.1184</v>
       </c>
       <c r="J185" t="n">
-        <v>2.4808</v>
+        <v>3.3152</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.93</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.3371</v>
+        <v>-0.2772</v>
       </c>
       <c r="J186" t="n">
-        <v>-9.438800000000001</v>
+        <v>-7.7616</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.33</v>
       </c>
       <c r="I187" t="n">
-        <v>0.5431</v>
+        <v>0.6511</v>
       </c>
       <c r="J187" t="n">
-        <v>15.2068</v>
+        <v>18.2308</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.17</v>
       </c>
       <c r="I188" t="n">
-        <v>0.3224</v>
+        <v>0.3697</v>
       </c>
       <c r="J188" t="n">
-        <v>9.027200000000001</v>
+        <v>10.3516</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>1.14</v>
       </c>
       <c r="I189" t="n">
-        <v>0.2756</v>
+        <v>0.3136</v>
       </c>
       <c r="J189" t="n">
-        <v>7.7168</v>
+        <v>8.780799999999999</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.83</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.3507</v>
+        <v>-0.2141</v>
       </c>
       <c r="J190" t="n">
-        <v>-9.819599999999999</v>
+        <v>-5.9948</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.77</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.4357</v>
+        <v>-0.2742</v>
       </c>
       <c r="J191" t="n">
-        <v>-12.1996</v>
+        <v>-7.6776</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.82</v>
       </c>
       <c r="I192" t="n">
-        <v>1.7684</v>
+        <v>1.5059</v>
       </c>
       <c r="J192" t="n">
-        <v>40.6732</v>
+        <v>34.6357</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.64</v>
       </c>
       <c r="I193" t="n">
-        <v>1.4431</v>
+        <v>1.2907</v>
       </c>
       <c r="J193" t="n">
-        <v>33.1913</v>
+        <v>29.6861</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.41</v>
       </c>
       <c r="I194" t="n">
-        <v>0.9816</v>
+        <v>0.9977</v>
       </c>
       <c r="J194" t="n">
-        <v>22.5768</v>
+        <v>22.9471</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>0.83</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.6822</v>
+        <v>-0.6208</v>
       </c>
       <c r="J195" t="n">
-        <v>-15.6906</v>
+        <v>-14.2784</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.83</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.6822</v>
+        <v>-0.6208</v>
       </c>
       <c r="J196" t="n">
-        <v>-15.6906</v>
+        <v>-14.2784</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.31</v>
       </c>
       <c r="I197" t="n">
-        <v>0.5886</v>
+        <v>0.7097</v>
       </c>
       <c r="J197" t="n">
-        <v>13.5378</v>
+        <v>16.3231</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.09</v>
       </c>
       <c r="I198" t="n">
-        <v>0.2694</v>
+        <v>0.2768</v>
       </c>
       <c r="J198" t="n">
-        <v>6.1962</v>
+        <v>6.3664</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>1.01</v>
       </c>
       <c r="I199" t="n">
-        <v>0.1093</v>
+        <v>0.07729999999999999</v>
       </c>
       <c r="J199" t="n">
-        <v>2.5139</v>
+        <v>1.7779</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.49</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.7551</v>
+        <v>-0.5125999999999999</v>
       </c>
       <c r="J200" t="n">
-        <v>-17.3673</v>
+        <v>-11.7898</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.34</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.9282</v>
+        <v>-0.6478</v>
       </c>
       <c r="J201" t="n">
-        <v>-21.3486</v>
+        <v>-14.8994</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.38</v>
       </c>
       <c r="I202" t="n">
-        <v>0.5807</v>
+        <v>0.5042</v>
       </c>
       <c r="J202" t="n">
-        <v>15.6789</v>
+        <v>13.6134</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.3</v>
       </c>
       <c r="I203" t="n">
-        <v>0.4786</v>
+        <v>0.4106</v>
       </c>
       <c r="J203" t="n">
-        <v>12.9222</v>
+        <v>11.0862</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>1.13</v>
       </c>
       <c r="I204" t="n">
-        <v>0.221</v>
+        <v>0.2002</v>
       </c>
       <c r="J204" t="n">
-        <v>5.967</v>
+        <v>5.4054</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>1</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.0538</v>
+        <v>-0.0116</v>
       </c>
       <c r="J205" t="n">
-        <v>-1.4526</v>
+        <v>-0.3132</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.83</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.3663</v>
+        <v>-0.2226</v>
       </c>
       <c r="J206" t="n">
-        <v>-9.8901</v>
+        <v>-6.0102</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.17</v>
       </c>
       <c r="I207" t="n">
-        <v>0.3517</v>
+        <v>0.3013</v>
       </c>
       <c r="J207" t="n">
-        <v>9.495900000000001</v>
+        <v>8.1351</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.03</v>
       </c>
       <c r="I208" t="n">
-        <v>0.1081</v>
+        <v>0.0755</v>
       </c>
       <c r="J208" t="n">
-        <v>2.9187</v>
+        <v>2.0385</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>0.93</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.1605</v>
+        <v>-0.09660000000000001</v>
       </c>
       <c r="J209" t="n">
-        <v>-4.3335</v>
+        <v>-2.6082</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>0.91</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.1982</v>
+        <v>-0.1194</v>
       </c>
       <c r="J210" t="n">
-        <v>-5.3514</v>
+        <v>-3.2238</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.79</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.3898</v>
+        <v>-0.245</v>
       </c>
       <c r="J211" t="n">
-        <v>-10.5246</v>
+        <v>-6.615</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.32</v>
       </c>
       <c r="I212" t="n">
-        <v>0.5543</v>
+        <v>0.6616</v>
       </c>
       <c r="J212" t="n">
-        <v>15.5204</v>
+        <v>18.5248</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.29</v>
       </c>
       <c r="I213" t="n">
-        <v>0.5154</v>
+        <v>0.6091</v>
       </c>
       <c r="J213" t="n">
-        <v>14.4312</v>
+        <v>17.0548</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>0.83</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.3332</v>
+        <v>-0.2058</v>
       </c>
       <c r="J214" t="n">
-        <v>-9.329599999999999</v>
+        <v>-5.7624</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>0.78</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.4066</v>
+        <v>-0.2561</v>
       </c>
       <c r="J215" t="n">
-        <v>-11.3848</v>
+        <v>-7.1708</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.66</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.5675</v>
+        <v>-0.3712</v>
       </c>
       <c r="J216" t="n">
-        <v>-15.89</v>
+        <v>-10.3936</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.39</v>
       </c>
       <c r="I217" t="n">
-        <v>1.051</v>
+        <v>1.021</v>
       </c>
       <c r="J217" t="n">
-        <v>29.428</v>
+        <v>28.588</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.39</v>
       </c>
       <c r="I218" t="n">
-        <v>1.051</v>
+        <v>1.021</v>
       </c>
       <c r="J218" t="n">
-        <v>29.428</v>
+        <v>28.588</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>1.01</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.0154</v>
+        <v>0.0338</v>
       </c>
       <c r="J219" t="n">
-        <v>-0.4312</v>
+        <v>0.9464</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>0.97</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.2171</v>
+        <v>-0.1538</v>
       </c>
       <c r="J220" t="n">
-        <v>-6.0788</v>
+        <v>-4.3064</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.7</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.9312</v>
+        <v>-0.899</v>
       </c>
       <c r="J221" t="n">
-        <v>-26.0736</v>
+        <v>-25.172</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.42</v>
       </c>
       <c r="I222" t="n">
-        <v>0.6673</v>
+        <v>0.8177</v>
       </c>
       <c r="J222" t="n">
-        <v>19.3517</v>
+        <v>23.7133</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>0.96</v>
       </c>
       <c r="I223" t="n">
-        <v>-0.1179</v>
+        <v>-0.064</v>
       </c>
       <c r="J223" t="n">
-        <v>-3.4191</v>
+        <v>-1.856</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>0.95</v>
       </c>
       <c r="I224" t="n">
-        <v>-0.1386</v>
+        <v>-0.0767</v>
       </c>
       <c r="J224" t="n">
-        <v>-4.0194</v>
+        <v>-2.2243</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>0.9</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.2304</v>
+        <v>-0.1351</v>
       </c>
       <c r="J225" t="n">
-        <v>-6.6816</v>
+        <v>-3.9179</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.371</v>
+        <v>-0.2299</v>
       </c>
       <c r="J226" t="n">
-        <v>-10.759</v>
+        <v>-6.6671</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.3</v>
       </c>
       <c r="I227" t="n">
-        <v>0.8628</v>
+        <v>0.8379</v>
       </c>
       <c r="J227" t="n">
-        <v>25.0212</v>
+        <v>24.2991</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>1.1</v>
       </c>
       <c r="I228" t="n">
-        <v>0.3419</v>
+        <v>0.3275</v>
       </c>
       <c r="J228" t="n">
-        <v>9.915100000000001</v>
+        <v>9.4975</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>1.04</v>
       </c>
       <c r="I229" t="n">
-        <v>0.1177</v>
+        <v>0.1499</v>
       </c>
       <c r="J229" t="n">
-        <v>3.4133</v>
+        <v>4.3471</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>1.03</v>
       </c>
       <c r="I230" t="n">
-        <v>0.07969999999999999</v>
+        <v>0.1157</v>
       </c>
       <c r="J230" t="n">
-        <v>2.3113</v>
+        <v>3.3553</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.9</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.4319</v>
+        <v>-0.37</v>
       </c>
       <c r="J231" t="n">
-        <v>-12.5251</v>
+        <v>-10.73</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.52</v>
       </c>
       <c r="I232" t="n">
-        <v>1.264</v>
+        <v>1.168</v>
       </c>
       <c r="J232" t="n">
-        <v>36.656</v>
+        <v>33.872</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1.45</v>
       </c>
       <c r="I233" t="n">
-        <v>1.1226</v>
+        <v>1.078</v>
       </c>
       <c r="J233" t="n">
-        <v>32.5554</v>
+        <v>31.262</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>1.09</v>
       </c>
       <c r="I234" t="n">
-        <v>0.2089</v>
+        <v>0.2749</v>
       </c>
       <c r="J234" t="n">
-        <v>6.0581</v>
+        <v>7.9721</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>0.98</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.2222</v>
+        <v>-0.1437</v>
       </c>
       <c r="J235" t="n">
-        <v>-6.4438</v>
+        <v>-4.1673</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.3587</v>
+        <v>-0.2817</v>
       </c>
       <c r="J236" t="n">
-        <v>-10.4023</v>
+        <v>-8.1693</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.15</v>
       </c>
       <c r="I237" t="n">
-        <v>0.339</v>
+        <v>0.3724</v>
       </c>
       <c r="J237" t="n">
-        <v>9.831</v>
+        <v>10.7996</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>1.01</v>
       </c>
       <c r="I238" t="n">
-        <v>0.08019999999999999</v>
+        <v>0.0549</v>
       </c>
       <c r="J238" t="n">
-        <v>2.3258</v>
+        <v>1.5921</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>0.9</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.194</v>
+        <v>-0.1256</v>
       </c>
       <c r="J239" t="n">
-        <v>-5.626</v>
+        <v>-3.6424</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>0.82</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.3309</v>
+        <v>-0.209</v>
       </c>
       <c r="J240" t="n">
-        <v>-9.5961</v>
+        <v>-6.061</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.71</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.49</v>
+        <v>-0.3169</v>
       </c>
       <c r="J241" t="n">
-        <v>-14.21</v>
+        <v>-9.190099999999999</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1.1</v>
       </c>
       <c r="I242" t="n">
-        <v>0.2823</v>
+        <v>0.2251</v>
       </c>
       <c r="J242" t="n">
-        <v>7.6221</v>
+        <v>6.0777</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>0.99</v>
       </c>
       <c r="I243" t="n">
-        <v>0.0358</v>
+        <v>-0.003</v>
       </c>
       <c r="J243" t="n">
-        <v>0.9666</v>
+        <v>-0.081</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>0.82</v>
       </c>
       <c r="I244" t="n">
-        <v>-0.3068</v>
+        <v>-0.2019</v>
       </c>
       <c r="J244" t="n">
-        <v>-8.2836</v>
+        <v>-5.4513</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>0.76</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.4018</v>
+        <v>-0.2608</v>
       </c>
       <c r="J245" t="n">
-        <v>-10.8486</v>
+        <v>-7.0416</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>0.62</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.5954</v>
+        <v>-0.3941</v>
       </c>
       <c r="J246" t="n">
-        <v>-16.0758</v>
+        <v>-10.6407</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>2.09</v>
       </c>
       <c r="I247" t="n">
-        <v>1.2884</v>
+        <v>1.1277</v>
       </c>
       <c r="J247" t="n">
-        <v>34.7868</v>
+        <v>30.4479</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>1.13</v>
       </c>
       <c r="I248" t="n">
-        <v>0.1676</v>
+        <v>0.1864</v>
       </c>
       <c r="J248" t="n">
-        <v>4.5252</v>
+        <v>5.0328</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>1.11</v>
       </c>
       <c r="I249" t="n">
-        <v>0.1361</v>
+        <v>0.1589</v>
       </c>
       <c r="J249" t="n">
-        <v>3.6747</v>
+        <v>4.2903</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>1.06</v>
       </c>
       <c r="I250" t="n">
-        <v>0.0524</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="J250" t="n">
-        <v>1.4148</v>
+        <v>2.295</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.92</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.2515</v>
+        <v>-0.1383</v>
       </c>
       <c r="J251" t="n">
-        <v>-6.7905</v>
+        <v>-3.7341</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>1.66</v>
       </c>
       <c r="I252" t="n">
-        <v>1.4732</v>
+        <v>1.3113</v>
       </c>
       <c r="J252" t="n">
-        <v>35.3568</v>
+        <v>31.4712</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>1.43</v>
       </c>
       <c r="I253" t="n">
-        <v>1.0165</v>
+        <v>1.0259</v>
       </c>
       <c r="J253" t="n">
-        <v>24.396</v>
+        <v>24.6216</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>1.41</v>
       </c>
       <c r="I254" t="n">
-        <v>0.9728</v>
+        <v>0.9947</v>
       </c>
       <c r="J254" t="n">
-        <v>23.3472</v>
+        <v>23.8728</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>1.13</v>
       </c>
       <c r="I255" t="n">
-        <v>0.2681</v>
+        <v>0.3569</v>
       </c>
       <c r="J255" t="n">
-        <v>6.4344</v>
+        <v>8.5656</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>0.98</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.2608</v>
+        <v>-0.1739</v>
       </c>
       <c r="J256" t="n">
-        <v>-6.2592</v>
+        <v>-4.1736</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>1.31</v>
       </c>
       <c r="I257" t="n">
-        <v>0.5894</v>
+        <v>0.7109</v>
       </c>
       <c r="J257" t="n">
-        <v>14.1456</v>
+        <v>17.0616</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>1.02</v>
       </c>
       <c r="I258" t="n">
-        <v>0.1351</v>
+        <v>0.1081</v>
       </c>
       <c r="J258" t="n">
-        <v>3.2424</v>
+        <v>2.5944</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>0.85</v>
       </c>
       <c r="I259" t="n">
-        <v>-0.2379</v>
+        <v>-0.1713</v>
       </c>
       <c r="J259" t="n">
-        <v>-5.7096</v>
+        <v>-4.1112</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>0.7</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.4848</v>
+        <v>-0.317</v>
       </c>
       <c r="J260" t="n">
-        <v>-11.6352</v>
+        <v>-7.608</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>0.35</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.9167999999999999</v>
+        <v>-0.6387</v>
       </c>
       <c r="J261" t="n">
-        <v>-22.0032</v>
+        <v>-15.3288</v>
       </c>
     </row>
     <row r="262">
@@ -12829,10 +12829,10 @@
         <v>1.71</v>
       </c>
       <c r="I262" t="n">
-        <v>1.567</v>
+        <v>1.3721</v>
       </c>
       <c r="J262" t="n">
-        <v>37.608</v>
+        <v>32.9304</v>
       </c>
     </row>
     <row r="263">
@@ -12869,10 +12869,10 @@
         <v>1.57</v>
       </c>
       <c r="I263" t="n">
-        <v>1.3039</v>
+        <v>1.2029</v>
       </c>
       <c r="J263" t="n">
-        <v>31.2936</v>
+        <v>28.8696</v>
       </c>
     </row>
     <row r="264">
@@ -12909,10 +12909,10 @@
         <v>1.29</v>
       </c>
       <c r="I264" t="n">
-        <v>0.6708</v>
+        <v>0.7487</v>
       </c>
       <c r="J264" t="n">
-        <v>16.0992</v>
+        <v>17.9688</v>
       </c>
     </row>
     <row r="265">
@@ -12949,10 +12949,10 @@
         <v>1.24</v>
       </c>
       <c r="I265" t="n">
-        <v>0.5466</v>
+        <v>0.634</v>
       </c>
       <c r="J265" t="n">
-        <v>13.1184</v>
+        <v>15.216</v>
       </c>
     </row>
     <row r="266">
@@ -12989,10 +12989,10 @@
         <v>0.78</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.8013</v>
+        <v>-0.752</v>
       </c>
       <c r="J266" t="n">
-        <v>-19.2312</v>
+        <v>-18.048</v>
       </c>
     </row>
     <row r="267">
@@ -13029,10 +13029,10 @@
         <v>0.99</v>
       </c>
       <c r="I267" t="n">
-        <v>0.0518</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="J267" t="n">
-        <v>1.2432</v>
+        <v>0.2016</v>
       </c>
     </row>
     <row r="268">
@@ -13069,10 +13069,10 @@
         <v>0.95</v>
       </c>
       <c r="I268" t="n">
-        <v>-0.0372</v>
+        <v>-0.0541</v>
       </c>
       <c r="J268" t="n">
-        <v>-0.8928</v>
+        <v>-1.2984</v>
       </c>
     </row>
     <row r="269">
@@ -13109,10 +13109,10 @@
         <v>0.78</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.3548</v>
+        <v>-0.2366</v>
       </c>
       <c r="J269" t="n">
-        <v>-8.5152</v>
+        <v>-5.6784</v>
       </c>
     </row>
     <row r="270">
@@ -13149,10 +13149,10 @@
         <v>0.71</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.4622</v>
+        <v>-0.3038</v>
       </c>
       <c r="J270" t="n">
-        <v>-11.0928</v>
+        <v>-7.2912</v>
       </c>
     </row>
     <row r="271">
@@ -13189,10 +13189,10 @@
         <v>0.67</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.5188</v>
+        <v>-0.3418</v>
       </c>
       <c r="J271" t="n">
-        <v>-12.4512</v>
+        <v>-8.203200000000001</v>
       </c>
     </row>
     <row r="272">
@@ -13229,10 +13229,10 @@
         <v>1.8</v>
       </c>
       <c r="I272" t="n">
-        <v>1.7496</v>
+        <v>1.4926</v>
       </c>
       <c r="J272" t="n">
-        <v>43.74</v>
+        <v>37.315</v>
       </c>
     </row>
     <row r="273">
@@ -13269,10 +13269,10 @@
         <v>1.71</v>
       </c>
       <c r="I273" t="n">
-        <v>1.5887</v>
+        <v>1.3844</v>
       </c>
       <c r="J273" t="n">
-        <v>39.7175</v>
+        <v>34.61</v>
       </c>
     </row>
     <row r="274">
@@ -13309,10 +13309,10 @@
         <v>1.18</v>
       </c>
       <c r="I274" t="n">
-        <v>0.4197</v>
+        <v>0.4984</v>
       </c>
       <c r="J274" t="n">
-        <v>10.4925</v>
+        <v>12.46</v>
       </c>
     </row>
     <row r="275">
@@ -13349,10 +13349,10 @@
         <v>1.17</v>
       </c>
       <c r="I275" t="n">
-        <v>0.3937</v>
+        <v>0.4732</v>
       </c>
       <c r="J275" t="n">
-        <v>9.842499999999999</v>
+        <v>11.83</v>
       </c>
     </row>
     <row r="276">
@@ -13389,10 +13389,10 @@
         <v>0.49</v>
       </c>
       <c r="I276" t="n">
-        <v>-1.3883</v>
+        <v>-1.4234</v>
       </c>
       <c r="J276" t="n">
-        <v>-34.7075</v>
+        <v>-35.585</v>
       </c>
     </row>
     <row r="277">
@@ -13429,10 +13429,10 @@
         <v>1.13</v>
       </c>
       <c r="I277" t="n">
-        <v>0.3316</v>
+        <v>0.3582</v>
       </c>
       <c r="J277" t="n">
-        <v>8.289999999999999</v>
+        <v>8.955</v>
       </c>
     </row>
     <row r="278">
@@ -13469,10 +13469,10 @@
         <v>0.86</v>
       </c>
       <c r="I278" t="n">
-        <v>-0.2255</v>
+        <v>-0.1622</v>
       </c>
       <c r="J278" t="n">
-        <v>-5.6375</v>
+        <v>-4.055</v>
       </c>
     </row>
     <row r="279">
@@ -13509,10 +13509,10 @@
         <v>0.82</v>
       </c>
       <c r="I279" t="n">
-        <v>-0.3058</v>
+        <v>-0.2016</v>
       </c>
       <c r="J279" t="n">
-        <v>-7.645</v>
+        <v>-5.04</v>
       </c>
     </row>
     <row r="280">
@@ -13549,10 +13549,10 @@
         <v>0.79</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.3549</v>
+        <v>-0.2313</v>
       </c>
       <c r="J280" t="n">
-        <v>-8.8725</v>
+        <v>-5.7825</v>
       </c>
     </row>
     <row r="281">
@@ -13589,10 +13589,10 @@
         <v>0.68</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.5152</v>
+        <v>-0.3374</v>
       </c>
       <c r="J281" t="n">
-        <v>-12.88</v>
+        <v>-8.435</v>
       </c>
     </row>
     <row r="282">
@@ -13629,10 +13629,10 @@
         <v>1.63</v>
       </c>
       <c r="I282" t="n">
-        <v>1.4887</v>
+        <v>1.3148</v>
       </c>
       <c r="J282" t="n">
-        <v>50.6158</v>
+        <v>44.7032</v>
       </c>
     </row>
     <row r="283">
@@ -13669,10 +13669,10 @@
         <v>1.17</v>
       </c>
       <c r="I283" t="n">
-        <v>0.4656</v>
+        <v>0.4924</v>
       </c>
       <c r="J283" t="n">
-        <v>15.8304</v>
+        <v>16.7416</v>
       </c>
     </row>
     <row r="284">
@@ -13709,10 +13709,10 @@
         <v>1.09</v>
       </c>
       <c r="I284" t="n">
-        <v>0.2222</v>
+        <v>0.2811</v>
       </c>
       <c r="J284" t="n">
-        <v>7.5548</v>
+        <v>9.557399999999999</v>
       </c>
     </row>
     <row r="285">
@@ -13749,10 +13749,10 @@
         <v>1.04</v>
       </c>
       <c r="I285" t="n">
-        <v>0.0629</v>
+        <v>0.1267</v>
       </c>
       <c r="J285" t="n">
-        <v>2.1386</v>
+        <v>4.3078</v>
       </c>
     </row>
     <row r="286">
@@ -13789,10 +13789,10 @@
         <v>0.92</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.41</v>
+        <v>-0.3368</v>
       </c>
       <c r="J286" t="n">
-        <v>-13.94</v>
+        <v>-11.4512</v>
       </c>
     </row>
     <row r="287">
@@ -13829,10 +13829,10 @@
         <v>1.35</v>
       </c>
       <c r="I287" t="n">
-        <v>0.6078</v>
+        <v>0.7343</v>
       </c>
       <c r="J287" t="n">
-        <v>20.6652</v>
+        <v>24.9662</v>
       </c>
     </row>
     <row r="288">
@@ -13869,10 +13869,10 @@
         <v>1.03</v>
       </c>
       <c r="I288" t="n">
-        <v>0.1225</v>
+        <v>0.1071</v>
       </c>
       <c r="J288" t="n">
-        <v>4.165</v>
+        <v>3.6414</v>
       </c>
     </row>
     <row r="289">
@@ -13909,10 +13909,10 @@
         <v>1.02</v>
       </c>
       <c r="I289" t="n">
-        <v>0.0997</v>
+        <v>0.0805</v>
       </c>
       <c r="J289" t="n">
-        <v>3.3898</v>
+        <v>2.737</v>
       </c>
     </row>
     <row r="290">
@@ -13949,10 +13949,10 @@
         <v>0.63</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.5976</v>
+        <v>-0.394</v>
       </c>
       <c r="J290" t="n">
-        <v>-20.3184</v>
+        <v>-13.396</v>
       </c>
     </row>
     <row r="291">
@@ -13989,10 +13989,10 @@
         <v>0.63</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.5976</v>
+        <v>-0.394</v>
       </c>
       <c r="J291" t="n">
-        <v>-20.3184</v>
+        <v>-13.396</v>
       </c>
     </row>
     <row r="292">
@@ -14029,10 +14029,10 @@
         <v>1.94</v>
       </c>
       <c r="I292" t="n">
-        <v>1.948</v>
+        <v>1.6453</v>
       </c>
       <c r="J292" t="n">
-        <v>48.7</v>
+        <v>41.1325</v>
       </c>
     </row>
     <row r="293">
@@ -14069,10 +14069,10 @@
         <v>1.23</v>
       </c>
       <c r="I293" t="n">
-        <v>0.526</v>
+        <v>0.612</v>
       </c>
       <c r="J293" t="n">
-        <v>13.15</v>
+        <v>15.3</v>
       </c>
     </row>
     <row r="294">
@@ -14109,10 +14109,10 @@
         <v>1.22</v>
       </c>
       <c r="I294" t="n">
-        <v>0.5013</v>
+        <v>0.588</v>
       </c>
       <c r="J294" t="n">
-        <v>12.5325</v>
+        <v>14.7</v>
       </c>
     </row>
     <row r="295">
@@ -14149,10 +14149,10 @@
         <v>1.12</v>
       </c>
       <c r="I295" t="n">
-        <v>0.2458</v>
+        <v>0.3325</v>
       </c>
       <c r="J295" t="n">
-        <v>6.145</v>
+        <v>8.3125</v>
       </c>
     </row>
     <row r="296">
@@ -14189,10 +14189,10 @@
         <v>1.04</v>
       </c>
       <c r="I296" t="n">
-        <v>0.0114</v>
+        <v>0.09279999999999999</v>
       </c>
       <c r="J296" t="n">
-        <v>0.285</v>
+        <v>2.32</v>
       </c>
     </row>
     <row r="297">
@@ -14229,10 +14229,10 @@
         <v>1.14</v>
       </c>
       <c r="I297" t="n">
-        <v>0.3716</v>
+        <v>0.4101</v>
       </c>
       <c r="J297" t="n">
-        <v>9.289999999999999</v>
+        <v>10.2525</v>
       </c>
     </row>
     <row r="298">
@@ -14269,10 +14269,10 @@
         <v>0.93</v>
       </c>
       <c r="I298" t="n">
-        <v>-0.065</v>
+        <v>-0.0747</v>
       </c>
       <c r="J298" t="n">
-        <v>-1.625</v>
+        <v>-1.8675</v>
       </c>
     </row>
     <row r="299">
@@ -14309,10 +14309,10 @@
         <v>0.68</v>
       </c>
       <c r="I299" t="n">
-        <v>-0.4971</v>
+        <v>-0.3289</v>
       </c>
       <c r="J299" t="n">
-        <v>-12.4275</v>
+        <v>-8.2225</v>
       </c>
     </row>
     <row r="300">
@@ -14349,10 +14349,10 @@
         <v>0.67</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.5113</v>
+        <v>-0.3384</v>
       </c>
       <c r="J300" t="n">
-        <v>-12.7825</v>
+        <v>-8.460000000000001</v>
       </c>
     </row>
     <row r="301">
@@ -14389,10 +14389,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.6586</v>
+        <v>-0.4414</v>
       </c>
       <c r="J301" t="n">
-        <v>-16.465</v>
+        <v>-11.035</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/3515/event_3515_evp_summary.xlsx
+++ b/database/event/3515/event_3515_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.593</v>
+        <v>6.7761</v>
       </c>
       <c r="C2" t="n">
-        <v>2.8479</v>
+        <v>2.927</v>
       </c>
       <c r="D2" t="n">
-        <v>2.3384</v>
+        <v>2.4604</v>
       </c>
       <c r="E2" t="n">
-        <v>6.593</v>
+        <v>6.7761</v>
       </c>
       <c r="F2" t="n">
-        <v>4.2303</v>
+        <v>4.1844</v>
       </c>
       <c r="G2" t="n">
-        <v>2.3627</v>
+        <v>2.5917</v>
       </c>
       <c r="H2" t="n">
-        <v>9.4185</v>
+        <v>8.9116</v>
       </c>
       <c r="I2" t="n">
-        <v>4.8972</v>
+        <v>4.8122</v>
       </c>
       <c r="J2" t="n">
-        <v>2.3627</v>
+        <v>2.5917</v>
       </c>
       <c r="K2" t="n">
         <v>110</v>
@@ -529,7 +529,7 @@
         <v>102</v>
       </c>
       <c r="M2" t="n">
-        <v>7.2599</v>
+        <v>7.4039</v>
       </c>
       <c r="N2" t="n">
         <v>212</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.0273</v>
+        <v>5.0577</v>
       </c>
       <c r="C3" t="n">
-        <v>2.1716</v>
+        <v>2.1847</v>
       </c>
       <c r="D3" t="n">
-        <v>1.6316</v>
+        <v>1.6782</v>
       </c>
       <c r="E3" t="n">
-        <v>5.0273</v>
+        <v>5.0577</v>
       </c>
       <c r="F3" t="n">
-        <v>4.1882</v>
+        <v>4.1048</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8391</v>
+        <v>0.9529</v>
       </c>
       <c r="H3" t="n">
-        <v>9.2704</v>
+        <v>8.648999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>4.8202</v>
+        <v>4.6704</v>
       </c>
       <c r="J3" t="n">
-        <v>0.8391</v>
+        <v>0.9529</v>
       </c>
       <c r="K3" t="n">
         <v>152</v>
@@ -575,7 +575,7 @@
         <v>103</v>
       </c>
       <c r="M3" t="n">
-        <v>5.6593</v>
+        <v>5.6233</v>
       </c>
       <c r="N3" t="n">
         <v>255</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.4243</v>
+        <v>4.4884</v>
       </c>
       <c r="C4" t="n">
-        <v>1.9111</v>
+        <v>1.9388</v>
       </c>
       <c r="D4" t="n">
-        <v>1.3593</v>
+        <v>1.419</v>
       </c>
       <c r="E4" t="n">
-        <v>4.4243</v>
+        <v>4.4884</v>
       </c>
       <c r="F4" t="n">
-        <v>2.3035</v>
+        <v>2.2286</v>
       </c>
       <c r="G4" t="n">
-        <v>2.1208</v>
+        <v>2.2598</v>
       </c>
       <c r="H4" t="n">
-        <v>2.6297</v>
+        <v>2.4589</v>
       </c>
       <c r="I4" t="n">
-        <v>1.3673</v>
+        <v>1.3278</v>
       </c>
       <c r="J4" t="n">
-        <v>2.1208</v>
+        <v>2.2598</v>
       </c>
       <c r="K4" t="n">
         <v>110</v>
@@ -621,7 +621,7 @@
         <v>102</v>
       </c>
       <c r="M4" t="n">
-        <v>3.4881</v>
+        <v>3.5876</v>
       </c>
       <c r="N4" t="n">
         <v>212</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.3494</v>
+        <v>4.353</v>
       </c>
       <c r="C5" t="n">
-        <v>1.8788</v>
+        <v>1.8803</v>
       </c>
       <c r="D5" t="n">
-        <v>1.3255</v>
+        <v>1.3574</v>
       </c>
       <c r="E5" t="n">
-        <v>4.3494</v>
+        <v>4.353</v>
       </c>
       <c r="F5" t="n">
-        <v>4.1111</v>
+        <v>4.029</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2383</v>
+        <v>0.324</v>
       </c>
       <c r="H5" t="n">
-        <v>8.9985</v>
+        <v>8.398999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>4.6788</v>
+        <v>4.5354</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2383</v>
+        <v>0.324</v>
       </c>
       <c r="K5" t="n">
         <v>152</v>
@@ -667,7 +667,7 @@
         <v>103</v>
       </c>
       <c r="M5" t="n">
-        <v>4.9171</v>
+        <v>4.8594</v>
       </c>
       <c r="N5" t="n">
         <v>255</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.0162</v>
+        <v>4.0201</v>
       </c>
       <c r="C6" t="n">
-        <v>1.7349</v>
+        <v>1.7365</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1751</v>
+        <v>1.2058</v>
       </c>
       <c r="E6" t="n">
-        <v>4.0162</v>
+        <v>4.0201</v>
       </c>
       <c r="F6" t="n">
-        <v>2.7472</v>
+        <v>2.7201</v>
       </c>
       <c r="G6" t="n">
-        <v>1.269</v>
+        <v>1.3</v>
       </c>
       <c r="H6" t="n">
-        <v>4.1933</v>
+        <v>4.0804</v>
       </c>
       <c r="I6" t="n">
-        <v>2.1803</v>
+        <v>2.2034</v>
       </c>
       <c r="J6" t="n">
-        <v>1.269</v>
+        <v>1.3</v>
       </c>
       <c r="K6" t="n">
         <v>110</v>
@@ -713,7 +713,7 @@
         <v>102</v>
       </c>
       <c r="M6" t="n">
-        <v>3.4493</v>
+        <v>3.5034</v>
       </c>
       <c r="N6" t="n">
         <v>212</v>
@@ -722,139 +722,139 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>nitr0</t>
+          <t>Magisk</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.7841</v>
+        <v>3.8229</v>
       </c>
       <c r="C7" t="n">
-        <v>1.6346</v>
+        <v>1.6514</v>
       </c>
       <c r="D7" t="n">
-        <v>1.0703</v>
+        <v>1.1161</v>
       </c>
       <c r="E7" t="n">
-        <v>3.7841</v>
+        <v>3.8229</v>
       </c>
       <c r="F7" t="n">
-        <v>2.7767</v>
+        <v>1.3985</v>
       </c>
       <c r="G7" t="n">
-        <v>1.0074</v>
+        <v>2.4244</v>
       </c>
       <c r="H7" t="n">
-        <v>4.2971</v>
+        <v>1.3985</v>
       </c>
       <c r="I7" t="n">
-        <v>2.2343</v>
+        <v>0.7552</v>
       </c>
       <c r="J7" t="n">
-        <v>1.0074</v>
+        <v>2.4244</v>
       </c>
       <c r="K7" t="n">
-        <v>152</v>
+        <v>110</v>
       </c>
       <c r="L7" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="M7" t="n">
-        <v>3.2417</v>
+        <v>3.1796</v>
       </c>
       <c r="N7" t="n">
-        <v>255</v>
+        <v>212</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>s1mple</t>
+          <t>nitr0</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.7222</v>
+        <v>3.8075</v>
       </c>
       <c r="C8" t="n">
-        <v>1.6079</v>
+        <v>1.6447</v>
       </c>
       <c r="D8" t="n">
-        <v>1.0424</v>
+        <v>1.109</v>
       </c>
       <c r="E8" t="n">
-        <v>3.7222</v>
+        <v>3.8075</v>
       </c>
       <c r="F8" t="n">
-        <v>3.5643</v>
+        <v>2.7098</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1579</v>
+        <v>1.0977</v>
       </c>
       <c r="H8" t="n">
-        <v>7.072</v>
+        <v>4.0464</v>
       </c>
       <c r="I8" t="n">
-        <v>3.6771</v>
+        <v>2.185</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1579</v>
+        <v>1.0977</v>
       </c>
       <c r="K8" t="n">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="L8" t="n">
-        <v>54</v>
+        <v>103</v>
       </c>
       <c r="M8" t="n">
-        <v>3.835</v>
+        <v>3.2827</v>
       </c>
       <c r="N8" t="n">
-        <v>214</v>
+        <v>255</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Magisk</t>
+          <t>s1mple</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.631</v>
+        <v>3.6688</v>
       </c>
       <c r="C9" t="n">
-        <v>1.5685</v>
+        <v>1.5848</v>
       </c>
       <c r="D9" t="n">
-        <v>1.0012</v>
+        <v>1.0459</v>
       </c>
       <c r="E9" t="n">
-        <v>3.631</v>
+        <v>3.6688</v>
       </c>
       <c r="F9" t="n">
-        <v>1.4001</v>
+        <v>3.5117</v>
       </c>
       <c r="G9" t="n">
-        <v>2.2309</v>
+        <v>0.1571</v>
       </c>
       <c r="H9" t="n">
-        <v>1.4001</v>
+        <v>6.6923</v>
       </c>
       <c r="I9" t="n">
-        <v>0.728</v>
+        <v>3.6138</v>
       </c>
       <c r="J9" t="n">
-        <v>2.2309</v>
+        <v>0.1571</v>
       </c>
       <c r="K9" t="n">
-        <v>110</v>
+        <v>160</v>
       </c>
       <c r="L9" t="n">
-        <v>102</v>
+        <v>54</v>
       </c>
       <c r="M9" t="n">
-        <v>2.9589</v>
+        <v>3.7709</v>
       </c>
       <c r="N9" t="n">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="10">
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.3559</v>
+        <v>3.3461</v>
       </c>
       <c r="C10" t="n">
-        <v>1.4496</v>
+        <v>1.4454</v>
       </c>
       <c r="D10" t="n">
-        <v>0.877</v>
+        <v>0.899</v>
       </c>
       <c r="E10" t="n">
-        <v>3.3559</v>
+        <v>3.3461</v>
       </c>
       <c r="F10" t="n">
-        <v>3.1233</v>
+        <v>3.0753</v>
       </c>
       <c r="G10" t="n">
-        <v>0.2326</v>
+        <v>0.2708</v>
       </c>
       <c r="H10" t="n">
-        <v>5.5184</v>
+        <v>5.2525</v>
       </c>
       <c r="I10" t="n">
-        <v>2.8693</v>
+        <v>2.8363</v>
       </c>
       <c r="J10" t="n">
-        <v>0.2326</v>
+        <v>0.2708</v>
       </c>
       <c r="K10" t="n">
         <v>160</v>
@@ -897,7 +897,7 @@
         <v>54</v>
       </c>
       <c r="M10" t="n">
-        <v>3.1019</v>
+        <v>3.1071</v>
       </c>
       <c r="N10" t="n">
         <v>214</v>
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.129</v>
+        <v>3.0082</v>
       </c>
       <c r="C11" t="n">
-        <v>1.3516</v>
+        <v>1.2994</v>
       </c>
       <c r="D11" t="n">
-        <v>0.7746</v>
+        <v>0.7452</v>
       </c>
       <c r="E11" t="n">
-        <v>3.129</v>
+        <v>3.0082</v>
       </c>
       <c r="F11" t="n">
-        <v>2.8427</v>
+        <v>2.7291</v>
       </c>
       <c r="G11" t="n">
-        <v>0.2863</v>
+        <v>0.2791</v>
       </c>
       <c r="H11" t="n">
-        <v>4.5294</v>
+        <v>4.1102</v>
       </c>
       <c r="I11" t="n">
-        <v>2.3551</v>
+        <v>2.2195</v>
       </c>
       <c r="J11" t="n">
-        <v>0.2863</v>
+        <v>0.2791</v>
       </c>
       <c r="K11" t="n">
         <v>160</v>
@@ -943,7 +943,7 @@
         <v>54</v>
       </c>
       <c r="M11" t="n">
-        <v>2.6414</v>
+        <v>2.4986</v>
       </c>
       <c r="N11" t="n">
         <v>214</v>
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.9933</v>
+        <v>2.9213</v>
       </c>
       <c r="C12" t="n">
-        <v>1.293</v>
+        <v>1.2619</v>
       </c>
       <c r="D12" t="n">
-        <v>0.7133</v>
+        <v>0.7056</v>
       </c>
       <c r="E12" t="n">
-        <v>2.9933</v>
+        <v>2.9213</v>
       </c>
       <c r="F12" t="n">
-        <v>2.3978</v>
+        <v>2.2705</v>
       </c>
       <c r="G12" t="n">
-        <v>0.5955</v>
+        <v>0.6508</v>
       </c>
       <c r="H12" t="n">
-        <v>2.962</v>
+        <v>2.5969</v>
       </c>
       <c r="I12" t="n">
-        <v>1.5401</v>
+        <v>1.4023</v>
       </c>
       <c r="J12" t="n">
-        <v>0.5955</v>
+        <v>0.6508</v>
       </c>
       <c r="K12" t="n">
         <v>248</v>
@@ -989,7 +989,7 @@
         <v>53</v>
       </c>
       <c r="M12" t="n">
-        <v>2.1356</v>
+        <v>2.0531</v>
       </c>
       <c r="N12" t="n">
         <v>301</v>
@@ -1002,31 +1002,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.9788</v>
+        <v>2.8717</v>
       </c>
       <c r="C13" t="n">
-        <v>1.2867</v>
+        <v>1.2405</v>
       </c>
       <c r="D13" t="n">
-        <v>0.7068</v>
+        <v>0.6831</v>
       </c>
       <c r="E13" t="n">
-        <v>2.9788</v>
+        <v>2.8717</v>
       </c>
       <c r="F13" t="n">
-        <v>3.4238</v>
+        <v>3.3416</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.445</v>
+        <v>-0.4699</v>
       </c>
       <c r="H13" t="n">
-        <v>6.5771</v>
+        <v>6.1308</v>
       </c>
       <c r="I13" t="n">
-        <v>3.4198</v>
+        <v>3.3106</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.445</v>
+        <v>-0.4699</v>
       </c>
       <c r="K13" t="n">
         <v>248</v>
@@ -1035,7 +1035,7 @@
         <v>53</v>
       </c>
       <c r="M13" t="n">
-        <v>2.9748</v>
+        <v>2.8407</v>
       </c>
       <c r="N13" t="n">
         <v>301</v>
@@ -1048,28 +1048,28 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.8546</v>
+        <v>2.5262</v>
       </c>
       <c r="C14" t="n">
-        <v>1.2331</v>
+        <v>1.0912</v>
       </c>
       <c r="D14" t="n">
-        <v>0.6506999999999999</v>
+        <v>0.5258</v>
       </c>
       <c r="E14" t="n">
-        <v>2.8546</v>
+        <v>2.5262</v>
       </c>
       <c r="F14" t="n">
-        <v>2.8546</v>
+        <v>2.5262</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>2.9084</v>
+        <v>2.8042</v>
       </c>
       <c r="I14" t="n">
-        <v>2.9084</v>
+        <v>2.8042</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1081,7 +1081,7 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>2.9084</v>
+        <v>2.8042</v>
       </c>
       <c r="N14" t="n">
         <v>148</v>
@@ -1094,31 +1094,31 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.5012</v>
+        <v>2.4808</v>
       </c>
       <c r="C15" t="n">
-        <v>1.0804</v>
+        <v>1.0716</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4912</v>
+        <v>0.5051</v>
       </c>
       <c r="E15" t="n">
-        <v>2.5012</v>
+        <v>2.4808</v>
       </c>
       <c r="F15" t="n">
-        <v>3.0594</v>
+        <v>2.9594</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.5582</v>
+        <v>-0.4786</v>
       </c>
       <c r="H15" t="n">
-        <v>5.293</v>
+        <v>4.8701</v>
       </c>
       <c r="I15" t="n">
-        <v>2.7521</v>
+        <v>2.6298</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.5582</v>
+        <v>-0.4786</v>
       </c>
       <c r="K15" t="n">
         <v>152</v>
@@ -1127,7 +1127,7 @@
         <v>103</v>
       </c>
       <c r="M15" t="n">
-        <v>2.1939</v>
+        <v>2.1512</v>
       </c>
       <c r="N15" t="n">
         <v>255</v>
@@ -1140,31 +1140,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.3297</v>
+        <v>2.2489</v>
       </c>
       <c r="C16" t="n">
-        <v>1.0063</v>
+        <v>0.9714</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4137</v>
+        <v>0.3995</v>
       </c>
       <c r="E16" t="n">
-        <v>2.3297</v>
+        <v>2.2489</v>
       </c>
       <c r="F16" t="n">
-        <v>2.8063</v>
+        <v>2.7426</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.4766</v>
+        <v>-0.4937</v>
       </c>
       <c r="H16" t="n">
-        <v>4.4014</v>
+        <v>4.1547</v>
       </c>
       <c r="I16" t="n">
-        <v>2.2885</v>
+        <v>2.2435</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.4766</v>
+        <v>-0.4937</v>
       </c>
       <c r="K16" t="n">
         <v>248</v>
@@ -1173,7 +1173,7 @@
         <v>53</v>
       </c>
       <c r="M16" t="n">
-        <v>1.8119</v>
+        <v>1.7498</v>
       </c>
       <c r="N16" t="n">
         <v>301</v>
@@ -1182,139 +1182,139 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Edward</t>
+          <t>olofmeister</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.7759</v>
+        <v>1.6245</v>
       </c>
       <c r="C17" t="n">
-        <v>0.7671</v>
+        <v>0.7017</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1637</v>
+        <v>0.1153</v>
       </c>
       <c r="E17" t="n">
-        <v>1.7759</v>
+        <v>1.6245</v>
       </c>
       <c r="F17" t="n">
-        <v>2.165</v>
+        <v>1.6245</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.3891</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>2.165</v>
+        <v>1.6245</v>
       </c>
       <c r="I17" t="n">
-        <v>1.1257</v>
+        <v>1.6245</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.3891</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>160</v>
+        <v>148</v>
       </c>
       <c r="L17" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0.7365999999999999</v>
+        <v>1.6245</v>
       </c>
       <c r="N17" t="n">
-        <v>214</v>
+        <v>148</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>KRIMZ</t>
+          <t>Edward</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.6968</v>
+        <v>1.6158</v>
       </c>
       <c r="C18" t="n">
-        <v>0.733</v>
+        <v>0.698</v>
       </c>
       <c r="D18" t="n">
-        <v>0.128</v>
+        <v>0.1113</v>
       </c>
       <c r="E18" t="n">
-        <v>1.6968</v>
+        <v>1.6158</v>
       </c>
       <c r="F18" t="n">
-        <v>1.6968</v>
+        <v>2.0319</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>-0.4161</v>
       </c>
       <c r="H18" t="n">
-        <v>1.6968</v>
+        <v>2.0319</v>
       </c>
       <c r="I18" t="n">
-        <v>1.6968</v>
+        <v>1.0972</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>-0.4161</v>
       </c>
       <c r="K18" t="n">
-        <v>228</v>
+        <v>160</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="M18" t="n">
-        <v>1.6968</v>
+        <v>0.6810999999999999</v>
       </c>
       <c r="N18" t="n">
-        <v>228</v>
+        <v>214</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>olofmeister</t>
+          <t>KRIMZ</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.6368</v>
+        <v>1.5992</v>
       </c>
       <c r="C19" t="n">
-        <v>0.707</v>
+        <v>0.6908</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1009</v>
+        <v>0.1038</v>
       </c>
       <c r="E19" t="n">
-        <v>1.6368</v>
+        <v>1.5992</v>
       </c>
       <c r="F19" t="n">
-        <v>1.6368</v>
+        <v>1.5992</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>1.6368</v>
+        <v>1.5992</v>
       </c>
       <c r="I19" t="n">
-        <v>1.6368</v>
+        <v>1.5992</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>148</v>
+        <v>228</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1.6368</v>
+        <v>1.5992</v>
       </c>
       <c r="N19" t="n">
-        <v>148</v>
+        <v>228</v>
       </c>
     </row>
     <row r="20">
@@ -1324,28 +1324,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.6106</v>
+        <v>1.5188</v>
       </c>
       <c r="C20" t="n">
-        <v>0.6957</v>
+        <v>0.6561</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0891</v>
+        <v>0.0672</v>
       </c>
       <c r="E20" t="n">
-        <v>1.6106</v>
+        <v>1.5188</v>
       </c>
       <c r="F20" t="n">
-        <v>1.6106</v>
+        <v>1.5188</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>1.6106</v>
+        <v>1.5188</v>
       </c>
       <c r="I20" t="n">
-        <v>1.6106</v>
+        <v>1.5188</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1357,7 +1357,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1.6106</v>
+        <v>1.5188</v>
       </c>
       <c r="N20" t="n">
         <v>158</v>
@@ -1370,28 +1370,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.3111</v>
+        <v>1.2352</v>
       </c>
       <c r="C21" t="n">
-        <v>0.5663</v>
+        <v>0.5336</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.0461</v>
+        <v>-0.0619</v>
       </c>
       <c r="E21" t="n">
-        <v>1.3111</v>
+        <v>1.2352</v>
       </c>
       <c r="F21" t="n">
-        <v>1.3111</v>
+        <v>1.2352</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>1.3111</v>
+        <v>1.2352</v>
       </c>
       <c r="I21" t="n">
-        <v>1.3111</v>
+        <v>1.2352</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1.3111</v>
+        <v>1.2352</v>
       </c>
       <c r="N21" t="n">
         <v>158</v>
@@ -1416,28 +1416,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.1495</v>
+        <v>1.0486</v>
       </c>
       <c r="C22" t="n">
-        <v>0.4965</v>
+        <v>0.453</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1191</v>
+        <v>-0.1469</v>
       </c>
       <c r="E22" t="n">
-        <v>1.1495</v>
+        <v>1.0486</v>
       </c>
       <c r="F22" t="n">
-        <v>1.1495</v>
+        <v>1.0486</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>1.1495</v>
+        <v>1.0486</v>
       </c>
       <c r="I22" t="n">
-        <v>1.1495</v>
+        <v>1.0486</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1.1495</v>
+        <v>1.0486</v>
       </c>
       <c r="N22" t="n">
         <v>158</v>
@@ -1462,28 +1462,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.9905</v>
+        <v>0.9233</v>
       </c>
       <c r="C23" t="n">
-        <v>0.4279</v>
+        <v>0.3988</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.1909</v>
+        <v>-0.2039</v>
       </c>
       <c r="E23" t="n">
-        <v>0.9905</v>
+        <v>0.9233</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9905</v>
+        <v>0.9233</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.9905</v>
+        <v>0.9233</v>
       </c>
       <c r="I23" t="n">
-        <v>0.9905</v>
+        <v>0.9233</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.9905</v>
+        <v>0.9233</v>
       </c>
       <c r="N23" t="n">
         <v>116</v>
@@ -1508,28 +1508,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.7079</v>
+        <v>0.6078</v>
       </c>
       <c r="C24" t="n">
-        <v>0.3058</v>
+        <v>0.2625</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.3184</v>
+        <v>-0.3475</v>
       </c>
       <c r="E24" t="n">
-        <v>0.7079</v>
+        <v>0.6078</v>
       </c>
       <c r="F24" t="n">
-        <v>0.7079</v>
+        <v>0.6078</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.7079</v>
+        <v>0.6078</v>
       </c>
       <c r="I24" t="n">
-        <v>0.7079</v>
+        <v>0.6078</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.7079</v>
+        <v>0.6078</v>
       </c>
       <c r="N24" t="n">
         <v>228</v>
@@ -1550,32 +1550,32 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>draken</t>
+          <t>flusha</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.2307</v>
+        <v>0.2101</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0997</v>
+        <v>0.09080000000000001</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.5339</v>
+        <v>-0.5286</v>
       </c>
       <c r="E25" t="n">
-        <v>0.2307</v>
+        <v>0.2101</v>
       </c>
       <c r="F25" t="n">
-        <v>0.2307</v>
+        <v>0.2101</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.2307</v>
+        <v>0.2101</v>
       </c>
       <c r="I25" t="n">
-        <v>0.2307</v>
+        <v>0.2101</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.2307</v>
+        <v>0.2101</v>
       </c>
       <c r="N25" t="n">
         <v>228</v>
@@ -1596,32 +1596,32 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>flusha</t>
+          <t>draken</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.2088</v>
+        <v>0.21</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0902</v>
+        <v>0.0907</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.5438</v>
+        <v>-0.5286</v>
       </c>
       <c r="E26" t="n">
-        <v>0.2088</v>
+        <v>0.21</v>
       </c>
       <c r="F26" t="n">
-        <v>0.2088</v>
+        <v>0.21</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.2088</v>
+        <v>0.21</v>
       </c>
       <c r="I26" t="n">
-        <v>0.2088</v>
+        <v>0.21</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.2088</v>
+        <v>0.21</v>
       </c>
       <c r="N26" t="n">
         <v>228</v>
@@ -1646,28 +1646,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.2034</v>
+        <v>0.1396</v>
       </c>
       <c r="C27" t="n">
-        <v>0.08790000000000001</v>
+        <v>0.0603</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.5462</v>
+        <v>-0.5607</v>
       </c>
       <c r="E27" t="n">
-        <v>0.2034</v>
+        <v>0.1396</v>
       </c>
       <c r="F27" t="n">
-        <v>0.2034</v>
+        <v>0.1396</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.2034</v>
+        <v>0.1396</v>
       </c>
       <c r="I27" t="n">
-        <v>0.2034</v>
+        <v>0.1396</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.2034</v>
+        <v>0.1396</v>
       </c>
       <c r="N27" t="n">
         <v>158</v>
@@ -1692,28 +1692,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.0054</v>
+        <v>-0.0011</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0023</v>
+        <v>-0.0005</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.6356000000000001</v>
+        <v>-0.6247</v>
       </c>
       <c r="E28" t="n">
-        <v>0.0054</v>
+        <v>-0.0011</v>
       </c>
       <c r="F28" t="n">
-        <v>0.0054</v>
+        <v>-0.0011</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.0054</v>
+        <v>-0.0011</v>
       </c>
       <c r="I28" t="n">
-        <v>0.0054</v>
+        <v>-0.0011</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0.0054</v>
+        <v>-0.0011</v>
       </c>
       <c r="N28" t="n">
         <v>148</v>
@@ -1734,127 +1734,127 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Skadoodle</t>
+          <t>Zeus</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.1654</v>
+        <v>-0.1124</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.07140000000000001</v>
+        <v>-0.0486</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.7127</v>
+        <v>-0.6754</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.1654</v>
+        <v>-0.1124</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.1654</v>
+        <v>-0.1539</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>0.0415</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.1654</v>
+        <v>-0.1539</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.1654</v>
+        <v>-0.08309999999999999</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>0.0415</v>
       </c>
       <c r="K29" t="n">
-        <v>116</v>
+        <v>160</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.1654</v>
+        <v>-0.04159999999999999</v>
       </c>
       <c r="N29" t="n">
-        <v>116</v>
+        <v>214</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Zeus</t>
+          <t>Skadoodle</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.1738</v>
+        <v>-0.2495</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.0751</v>
+        <v>-0.1078</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.7165</v>
+        <v>-0.7378</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.1738</v>
+        <v>-0.2495</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.2142</v>
+        <v>-0.2495</v>
       </c>
       <c r="G30" t="n">
-        <v>0.0404</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.2142</v>
+        <v>-0.2495</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.1114</v>
+        <v>-0.2495</v>
       </c>
       <c r="J30" t="n">
-        <v>0.0404</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>160</v>
+        <v>116</v>
       </c>
       <c r="L30" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.07100000000000001</v>
+        <v>-0.2495</v>
       </c>
       <c r="N30" t="n">
-        <v>214</v>
+        <v>116</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>chrisJ</t>
+          <t>Snax</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.415</v>
+        <v>-0.2945</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.1793</v>
+        <v>-0.1272</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.8254</v>
+        <v>-0.7583</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.415</v>
+        <v>-0.2945</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.236</v>
+        <v>-0.1887</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.179</v>
+        <v>-0.1058</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.236</v>
+        <v>-0.1887</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.1227</v>
+        <v>-0.1019</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.179</v>
+        <v>-0.1058</v>
       </c>
       <c r="K31" t="n">
         <v>248</v>
@@ -1863,7 +1863,7 @@
         <v>53</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.3017</v>
+        <v>-0.2077</v>
       </c>
       <c r="N31" t="n">
         <v>301</v>
@@ -1876,28 +1876,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.4269</v>
+        <v>-0.4468</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.1844</v>
+        <v>-0.193</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.8307</v>
+        <v>-0.8276</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.4269</v>
+        <v>-0.4468</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.4269</v>
+        <v>-0.4468</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.4269</v>
+        <v>-0.4468</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.4269</v>
+        <v>-0.4468</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.4269</v>
+        <v>-0.4468</v>
       </c>
       <c r="N32" t="n">
         <v>116</v>
@@ -1918,35 +1918,35 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Snax</t>
+          <t>chrisJ</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.464</v>
+        <v>-0.4918</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.2004</v>
+        <v>-0.2124</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.8475</v>
+        <v>-0.8481</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.464</v>
+        <v>-0.4918</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.3725</v>
+        <v>-0.2878</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.0915</v>
+        <v>-0.204</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.3725</v>
+        <v>-0.2878</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.1937</v>
+        <v>-0.1554</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.0915</v>
+        <v>-0.204</v>
       </c>
       <c r="K33" t="n">
         <v>248</v>
@@ -1955,7 +1955,7 @@
         <v>53</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.2852</v>
+        <v>-0.3594</v>
       </c>
       <c r="N33" t="n">
         <v>301</v>
@@ -1968,28 +1968,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.4832</v>
+        <v>-0.5117</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.2087</v>
+        <v>-0.221</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.8562</v>
+        <v>-0.8571</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.4832</v>
+        <v>-0.5117</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.4832</v>
+        <v>-0.5117</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.4832</v>
+        <v>-0.5117</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.4832</v>
+        <v>-0.5117</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.4832</v>
+        <v>-0.5117</v>
       </c>
       <c r="N34" t="n">
         <v>148</v>
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.589</v>
+        <v>-0.613</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.2544</v>
+        <v>-0.2648</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.9039</v>
+        <v>-0.9033</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.589</v>
+        <v>-0.613</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.589</v>
+        <v>-0.613</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.589</v>
+        <v>-0.613</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.589</v>
+        <v>-0.613</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.589</v>
+        <v>-0.613</v>
       </c>
       <c r="N35" t="n">
         <v>228</v>
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.7905</v>
+        <v>-0.8216</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.3415</v>
+        <v>-0.3549</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9949</v>
+        <v>-0.9982</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.7905</v>
+        <v>-0.8216</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.7905</v>
+        <v>-0.8216</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.7905</v>
+        <v>-0.8216</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.7905</v>
+        <v>-0.8216</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.7905</v>
+        <v>-0.8216</v>
       </c>
       <c r="N36" t="n">
         <v>158</v>
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.8231000000000001</v>
+        <v>-0.8538</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.3555</v>
+        <v>-0.3688</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.0096</v>
+        <v>-1.0129</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.8231000000000001</v>
+        <v>-0.8538</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.8231000000000001</v>
+        <v>-0.8538</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.8231000000000001</v>
+        <v>-0.8538</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.8231000000000001</v>
+        <v>-0.8538</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.8231000000000001</v>
+        <v>-0.8538</v>
       </c>
       <c r="N37" t="n">
         <v>148</v>
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.0137</v>
+        <v>-1.0668</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.4379</v>
+        <v>-0.4608</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.0956</v>
+        <v>-1.1098</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.0137</v>
+        <v>-1.0668</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.0137</v>
+        <v>-1.0668</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.0137</v>
+        <v>-1.0668</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.0137</v>
+        <v>-1.0668</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.0137</v>
+        <v>-1.0668</v>
       </c>
       <c r="N38" t="n">
         <v>116</v>
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.1094</v>
+        <v>-1.1675</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.4792</v>
+        <v>-0.5043</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.1389</v>
+        <v>-1.1557</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.1094</v>
+        <v>-1.1675</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.1094</v>
+        <v>-1.1675</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.1094</v>
+        <v>-1.1675</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.1094</v>
+        <v>-1.1675</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.1094</v>
+        <v>-1.1675</v>
       </c>
       <c r="N39" t="n">
         <v>116</v>
@@ -2244,31 +2244,31 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.9747</v>
+        <v>-1.6795</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.853</v>
+        <v>-0.7255</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.5295</v>
+        <v>-1.3887</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.9747</v>
+        <v>-1.6795</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.008</v>
+        <v>-0.8069</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.9667</v>
+        <v>-0.8726</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.008</v>
+        <v>-0.8069</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.5241</v>
+        <v>-0.4357</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.9667</v>
+        <v>-0.8726</v>
       </c>
       <c r="K40" t="n">
         <v>110</v>
@@ -2277,7 +2277,7 @@
         <v>102</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.4908</v>
+        <v>-1.3083</v>
       </c>
       <c r="N40" t="n">
         <v>212</v>
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-4.4217</v>
+        <v>-3.7721</v>
       </c>
       <c r="C41" t="n">
-        <v>-1.91</v>
+        <v>-1.6294</v>
       </c>
       <c r="D41" t="n">
-        <v>-2.6342</v>
+        <v>-2.3413</v>
       </c>
       <c r="E41" t="n">
-        <v>-4.4217</v>
+        <v>-3.7721</v>
       </c>
       <c r="F41" t="n">
-        <v>-3.8221</v>
+        <v>-3.2886</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.5996</v>
+        <v>-0.4835</v>
       </c>
       <c r="H41" t="n">
-        <v>-3.8221</v>
+        <v>-3.2886</v>
       </c>
       <c r="I41" t="n">
-        <v>-1.9873</v>
+        <v>-1.7758</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.5996</v>
+        <v>-0.4835</v>
       </c>
       <c r="K41" t="n">
         <v>152</v>
@@ -2323,7 +2323,7 @@
         <v>103</v>
       </c>
       <c r="M41" t="n">
-        <v>-2.5869</v>
+        <v>-2.2593</v>
       </c>
       <c r="N41" t="n">
         <v>255</v>
@@ -2429,10 +2429,10 @@
         <v>1.8</v>
       </c>
       <c r="I2" t="n">
-        <v>1.4575</v>
+        <v>1.5857</v>
       </c>
       <c r="J2" t="n">
-        <v>30.6075</v>
+        <v>33.2997</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.78</v>
       </c>
       <c r="I3" t="n">
-        <v>1.4344</v>
+        <v>1.5584</v>
       </c>
       <c r="J3" t="n">
-        <v>30.1224</v>
+        <v>32.7264</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>1.29</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7321</v>
+        <v>0.7065</v>
       </c>
       <c r="J4" t="n">
-        <v>15.3741</v>
+        <v>14.8365</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>1.18</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4687</v>
+        <v>0.4718</v>
       </c>
       <c r="J5" t="n">
-        <v>9.842700000000001</v>
+        <v>9.9078</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.98</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1921</v>
+        <v>-0.1681</v>
       </c>
       <c r="J6" t="n">
-        <v>-4.0341</v>
+        <v>-3.5301</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>0.85</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.121</v>
+        <v>-0.1495</v>
       </c>
       <c r="J7" t="n">
-        <v>-2.541</v>
+        <v>-3.1395</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>0.64</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3413</v>
+        <v>-0.3622</v>
       </c>
       <c r="J8" t="n">
-        <v>-7.1673</v>
+        <v>-7.6062</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>0.6</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3762</v>
+        <v>-0.3958</v>
       </c>
       <c r="J9" t="n">
-        <v>-7.9002</v>
+        <v>-8.3118</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.4127</v>
+        <v>-0.4304</v>
       </c>
       <c r="J10" t="n">
-        <v>-8.666700000000001</v>
+        <v>-9.038399999999999</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.45</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.516</v>
+        <v>-0.5271</v>
       </c>
       <c r="J11" t="n">
-        <v>-10.836</v>
+        <v>-11.0691</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.42</v>
       </c>
       <c r="I12" t="n">
-        <v>1.061</v>
+        <v>1.0164</v>
       </c>
       <c r="J12" t="n">
-        <v>29.708</v>
+        <v>28.4592</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.07</v>
       </c>
       <c r="I13" t="n">
-        <v>0.237</v>
+        <v>0.2439</v>
       </c>
       <c r="J13" t="n">
-        <v>6.636</v>
+        <v>6.8292</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>1.05</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1752</v>
+        <v>0.1854</v>
       </c>
       <c r="J14" t="n">
-        <v>4.9056</v>
+        <v>5.1912</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>1.05</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1752</v>
+        <v>0.1854</v>
       </c>
       <c r="J15" t="n">
-        <v>4.9056</v>
+        <v>5.1912</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.258</v>
+        <v>-0.2505</v>
       </c>
       <c r="J16" t="n">
-        <v>-7.224</v>
+        <v>-7.014</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1</v>
       </c>
       <c r="I17" t="n">
-        <v>0.0114</v>
+        <v>0.0081</v>
       </c>
       <c r="J17" t="n">
-        <v>0.3192</v>
+        <v>0.2268</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>0.99</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.015</v>
+        <v>-0.021</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.42</v>
+        <v>-0.588</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>0.96</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.0582</v>
+        <v>-0.0687</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.6296</v>
+        <v>-1.9236</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.95</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.0708</v>
+        <v>-0.0822</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.9824</v>
+        <v>-2.3016</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.78</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.2512</v>
+        <v>-0.2661</v>
       </c>
       <c r="J21" t="n">
-        <v>-7.0336</v>
+        <v>-7.4508</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.29</v>
       </c>
       <c r="I22" t="n">
-        <v>0.4755</v>
+        <v>0.5304</v>
       </c>
       <c r="J22" t="n">
-        <v>13.7895</v>
+        <v>15.3816</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.17</v>
       </c>
       <c r="I23" t="n">
-        <v>0.3511</v>
+        <v>0.3674</v>
       </c>
       <c r="J23" t="n">
-        <v>10.1819</v>
+        <v>10.6546</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>1.17</v>
       </c>
       <c r="I24" t="n">
-        <v>0.3511</v>
+        <v>0.3674</v>
       </c>
       <c r="J24" t="n">
-        <v>10.1819</v>
+        <v>10.6546</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.97</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.0575</v>
+        <v>-0.064</v>
       </c>
       <c r="J25" t="n">
-        <v>-1.6675</v>
+        <v>-1.856</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.78</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.2674</v>
+        <v>-0.2787</v>
       </c>
       <c r="J26" t="n">
-        <v>-7.7546</v>
+        <v>-8.0823</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.34</v>
       </c>
       <c r="I27" t="n">
-        <v>0.6802</v>
+        <v>0.7492</v>
       </c>
       <c r="J27" t="n">
-        <v>19.7258</v>
+        <v>21.7268</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.27</v>
       </c>
       <c r="I28" t="n">
-        <v>0.5821</v>
+        <v>0.6417</v>
       </c>
       <c r="J28" t="n">
-        <v>16.8809</v>
+        <v>18.6093</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.2</v>
       </c>
       <c r="I29" t="n">
-        <v>0.4808</v>
+        <v>0.529</v>
       </c>
       <c r="J29" t="n">
-        <v>13.9432</v>
+        <v>15.341</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.91</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.348</v>
+        <v>-0.3348</v>
       </c>
       <c r="J30" t="n">
-        <v>-10.092</v>
+        <v>-9.709199999999999</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.78</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.7013</v>
+        <v>-0.6532</v>
       </c>
       <c r="J31" t="n">
-        <v>-20.3377</v>
+        <v>-18.9428</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.13</v>
       </c>
       <c r="I32" t="n">
-        <v>0.3438</v>
+        <v>0.3431</v>
       </c>
       <c r="J32" t="n">
-        <v>8.595000000000001</v>
+        <v>8.577500000000001</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>0.9</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.1217</v>
+        <v>-0.1374</v>
       </c>
       <c r="J33" t="n">
-        <v>-3.0425</v>
+        <v>-3.435</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>0.83</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.1932</v>
+        <v>-0.2103</v>
       </c>
       <c r="J34" t="n">
-        <v>-4.83</v>
+        <v>-5.2575</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.78</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.2429</v>
+        <v>-0.2596</v>
       </c>
       <c r="J35" t="n">
-        <v>-6.0725</v>
+        <v>-6.49</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.71</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.3107</v>
+        <v>-0.3259</v>
       </c>
       <c r="J36" t="n">
-        <v>-7.7675</v>
+        <v>-8.147500000000001</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.58</v>
       </c>
       <c r="I37" t="n">
-        <v>0.9426</v>
+        <v>1.042</v>
       </c>
       <c r="J37" t="n">
-        <v>23.565</v>
+        <v>26.05</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.52</v>
       </c>
       <c r="I38" t="n">
-        <v>0.8689</v>
+        <v>0.9629</v>
       </c>
       <c r="J38" t="n">
-        <v>21.7225</v>
+        <v>24.0725</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.34</v>
       </c>
       <c r="I39" t="n">
-        <v>0.6424</v>
+        <v>0.7163</v>
       </c>
       <c r="J39" t="n">
-        <v>16.06</v>
+        <v>17.9075</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>1.31</v>
       </c>
       <c r="I40" t="n">
-        <v>0.6045</v>
+        <v>0.6742</v>
       </c>
       <c r="J40" t="n">
-        <v>15.1125</v>
+        <v>16.855</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.6742</v>
+        <v>-0.6199</v>
       </c>
       <c r="J41" t="n">
-        <v>-16.855</v>
+        <v>-15.4975</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.62</v>
       </c>
       <c r="I42" t="n">
-        <v>1.0611</v>
+        <v>1.1558</v>
       </c>
       <c r="J42" t="n">
-        <v>28.6497</v>
+        <v>31.2066</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.08</v>
       </c>
       <c r="I43" t="n">
-        <v>0.271</v>
+        <v>0.2746</v>
       </c>
       <c r="J43" t="n">
-        <v>7.317</v>
+        <v>7.4142</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.02</v>
       </c>
       <c r="I44" t="n">
-        <v>0.0785</v>
+        <v>0.0893</v>
       </c>
       <c r="J44" t="n">
-        <v>2.1195</v>
+        <v>2.4111</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.96</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.1844</v>
+        <v>-0.1826</v>
       </c>
       <c r="J45" t="n">
-        <v>-4.9788</v>
+        <v>-4.9302</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.7</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.8948</v>
+        <v>-0.8239</v>
       </c>
       <c r="J46" t="n">
-        <v>-24.1596</v>
+        <v>-22.2453</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.02</v>
       </c>
       <c r="I47" t="n">
-        <v>0.0795</v>
+        <v>0.083</v>
       </c>
       <c r="J47" t="n">
-        <v>2.1465</v>
+        <v>2.241</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>0.98</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.0307</v>
+        <v>-0.0388</v>
       </c>
       <c r="J48" t="n">
-        <v>-0.8289</v>
+        <v>-1.0476</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.0827</v>
+        <v>-0.0949</v>
       </c>
       <c r="J49" t="n">
-        <v>-2.2329</v>
+        <v>-2.5623</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.89</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.1382</v>
+        <v>-0.1528</v>
       </c>
       <c r="J50" t="n">
-        <v>-3.7314</v>
+        <v>-4.1256</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.85</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.1805</v>
+        <v>-0.1957</v>
       </c>
       <c r="J51" t="n">
-        <v>-4.8735</v>
+        <v>-5.2839</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.41</v>
       </c>
       <c r="I52" t="n">
-        <v>0.7621</v>
+        <v>0.8408</v>
       </c>
       <c r="J52" t="n">
-        <v>19.8146</v>
+        <v>21.8608</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.28</v>
       </c>
       <c r="I53" t="n">
-        <v>0.5856</v>
+        <v>0.648</v>
       </c>
       <c r="J53" t="n">
-        <v>15.2256</v>
+        <v>16.848</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>1.19</v>
       </c>
       <c r="I54" t="n">
-        <v>0.4579</v>
+        <v>0.5054999999999999</v>
       </c>
       <c r="J54" t="n">
-        <v>11.9054</v>
+        <v>13.143</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>1.12</v>
       </c>
       <c r="I55" t="n">
-        <v>0.3541</v>
+        <v>0.3682</v>
       </c>
       <c r="J55" t="n">
-        <v>9.2066</v>
+        <v>9.5732</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.76</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.7654</v>
+        <v>-0.7073</v>
       </c>
       <c r="J56" t="n">
-        <v>-19.9004</v>
+        <v>-18.3898</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.29</v>
       </c>
       <c r="I57" t="n">
-        <v>0.516</v>
+        <v>0.5678</v>
       </c>
       <c r="J57" t="n">
-        <v>13.416</v>
+        <v>14.7628</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.02</v>
       </c>
       <c r="I58" t="n">
-        <v>0.089</v>
+        <v>0.08989999999999999</v>
       </c>
       <c r="J58" t="n">
-        <v>2.314</v>
+        <v>2.3374</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>0.97</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.0408</v>
+        <v>-0.0512</v>
       </c>
       <c r="J59" t="n">
-        <v>-1.0608</v>
+        <v>-1.3312</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.66</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.3623</v>
+        <v>-0.375</v>
       </c>
       <c r="J60" t="n">
-        <v>-9.4198</v>
+        <v>-9.75</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.57</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.4459</v>
+        <v>-0.4549</v>
       </c>
       <c r="J61" t="n">
-        <v>-11.5934</v>
+        <v>-11.8274</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.45</v>
       </c>
       <c r="I62" t="n">
-        <v>0.6356000000000001</v>
+        <v>0.6232</v>
       </c>
       <c r="J62" t="n">
-        <v>18.4324</v>
+        <v>18.0728</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.34</v>
       </c>
       <c r="I63" t="n">
-        <v>0.4985</v>
+        <v>0.4969</v>
       </c>
       <c r="J63" t="n">
-        <v>14.4565</v>
+        <v>14.4101</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.09</v>
       </c>
       <c r="I64" t="n">
-        <v>0.16</v>
+        <v>0.1729</v>
       </c>
       <c r="J64" t="n">
-        <v>4.64</v>
+        <v>5.0141</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>0.95</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.0861</v>
+        <v>-0.0939</v>
       </c>
       <c r="J65" t="n">
-        <v>-2.4969</v>
+        <v>-2.7231</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.66</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.3838</v>
+        <v>-0.3919</v>
       </c>
       <c r="J66" t="n">
-        <v>-11.1302</v>
+        <v>-11.3651</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.14</v>
       </c>
       <c r="I67" t="n">
-        <v>0.2281</v>
+        <v>0.2408</v>
       </c>
       <c r="J67" t="n">
-        <v>6.6149</v>
+        <v>6.9832</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.11</v>
       </c>
       <c r="I68" t="n">
-        <v>0.1863</v>
+        <v>0.1994</v>
       </c>
       <c r="J68" t="n">
-        <v>5.4027</v>
+        <v>5.7826</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>1.07</v>
       </c>
       <c r="I69" t="n">
-        <v>0.1278</v>
+        <v>0.1401</v>
       </c>
       <c r="J69" t="n">
-        <v>3.7062</v>
+        <v>4.0629</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.92</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.1138</v>
+        <v>-0.1253</v>
       </c>
       <c r="J70" t="n">
-        <v>-3.3002</v>
+        <v>-3.6337</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.86</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.1797</v>
+        <v>-0.1927</v>
       </c>
       <c r="J71" t="n">
-        <v>-5.2113</v>
+        <v>-5.5883</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.38</v>
       </c>
       <c r="I72" t="n">
-        <v>0.9827</v>
+        <v>0.9223</v>
       </c>
       <c r="J72" t="n">
-        <v>29.481</v>
+        <v>27.669</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.37</v>
       </c>
       <c r="I73" t="n">
-        <v>0.9636</v>
+        <v>0.9029</v>
       </c>
       <c r="J73" t="n">
-        <v>28.908</v>
+        <v>27.087</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1.22</v>
       </c>
       <c r="I74" t="n">
-        <v>0.6166</v>
+        <v>0.594</v>
       </c>
       <c r="J74" t="n">
-        <v>18.498</v>
+        <v>17.82</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>1.13</v>
       </c>
       <c r="I75" t="n">
-        <v>0.3939</v>
+        <v>0.3921</v>
       </c>
       <c r="J75" t="n">
-        <v>11.817</v>
+        <v>11.763</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.68</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.963</v>
+        <v>-0.88</v>
       </c>
       <c r="J76" t="n">
-        <v>-28.89</v>
+        <v>-26.4</v>
       </c>
     </row>
     <row r="77">
@@ -5469,10 +5469,10 @@
         <v>0.91</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.1124</v>
+        <v>-0.1273</v>
       </c>
       <c r="J78" t="n">
-        <v>-3.372</v>
+        <v>-3.819</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>0.88</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.144</v>
+        <v>-0.16</v>
       </c>
       <c r="J79" t="n">
-        <v>-4.32</v>
+        <v>-4.8</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.84</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.185</v>
+        <v>-0.2015</v>
       </c>
       <c r="J80" t="n">
-        <v>-5.55</v>
+        <v>-6.045</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.75</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.2742</v>
+        <v>-0.29</v>
       </c>
       <c r="J81" t="n">
-        <v>-8.226000000000001</v>
+        <v>-8.699999999999999</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.7</v>
       </c>
       <c r="I82" t="n">
-        <v>1.3977</v>
+        <v>1.3758</v>
       </c>
       <c r="J82" t="n">
-        <v>34.9425</v>
+        <v>34.395</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.28</v>
       </c>
       <c r="I83" t="n">
-        <v>0.7516</v>
+        <v>0.7151999999999999</v>
       </c>
       <c r="J83" t="n">
-        <v>18.79</v>
+        <v>17.88</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.16</v>
       </c>
       <c r="I84" t="n">
-        <v>0.4657</v>
+        <v>0.4589</v>
       </c>
       <c r="J84" t="n">
-        <v>11.6425</v>
+        <v>11.4725</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>1.06</v>
       </c>
       <c r="I85" t="n">
-        <v>0.188</v>
+        <v>0.2024</v>
       </c>
       <c r="J85" t="n">
-        <v>4.7</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.72</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.8722</v>
+        <v>-0.7998</v>
       </c>
       <c r="J86" t="n">
-        <v>-21.805</v>
+        <v>-19.995</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.16</v>
       </c>
       <c r="I87" t="n">
-        <v>0.4045</v>
+        <v>0.3938</v>
       </c>
       <c r="J87" t="n">
-        <v>10.1125</v>
+        <v>9.845000000000001</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.12</v>
       </c>
       <c r="I88" t="n">
-        <v>0.3237</v>
+        <v>0.3181</v>
       </c>
       <c r="J88" t="n">
-        <v>8.092499999999999</v>
+        <v>7.9525</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>0.89</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.134</v>
+        <v>-0.1496</v>
       </c>
       <c r="J89" t="n">
-        <v>-3.35</v>
+        <v>-3.74</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.67</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.3511</v>
+        <v>-0.3645</v>
       </c>
       <c r="J90" t="n">
-        <v>-8.7775</v>
+        <v>-9.112500000000001</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.6</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.4165</v>
+        <v>-0.4272</v>
       </c>
       <c r="J91" t="n">
-        <v>-10.4125</v>
+        <v>-10.68</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.43</v>
       </c>
       <c r="I92" t="n">
-        <v>1.0447</v>
+        <v>0.9953</v>
       </c>
       <c r="J92" t="n">
-        <v>27.1622</v>
+        <v>25.8778</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.38</v>
       </c>
       <c r="I93" t="n">
-        <v>0.9622000000000001</v>
+        <v>0.9056</v>
       </c>
       <c r="J93" t="n">
-        <v>25.0172</v>
+        <v>23.5456</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.22</v>
       </c>
       <c r="I94" t="n">
-        <v>0.6036</v>
+        <v>0.5852000000000001</v>
       </c>
       <c r="J94" t="n">
-        <v>15.6936</v>
+        <v>15.2152</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>1.2</v>
       </c>
       <c r="I95" t="n">
-        <v>0.5564</v>
+        <v>0.5427</v>
       </c>
       <c r="J95" t="n">
-        <v>14.4664</v>
+        <v>14.1102</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.9</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.4099</v>
+        <v>-0.3846</v>
       </c>
       <c r="J96" t="n">
-        <v>-10.6574</v>
+        <v>-9.999599999999999</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.18</v>
       </c>
       <c r="I97" t="n">
-        <v>0.4726</v>
+        <v>0.4515</v>
       </c>
       <c r="J97" t="n">
-        <v>12.2876</v>
+        <v>11.739</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>0.98</v>
       </c>
       <c r="I98" t="n">
-        <v>-0.014</v>
+        <v>-0.0257</v>
       </c>
       <c r="J98" t="n">
-        <v>-0.364</v>
+        <v>-0.6682</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>0.75</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.2668</v>
+        <v>-0.2842</v>
       </c>
       <c r="J99" t="n">
-        <v>-6.9368</v>
+        <v>-7.3892</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.65</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.3621</v>
+        <v>-0.3765</v>
       </c>
       <c r="J100" t="n">
-        <v>-9.4146</v>
+        <v>-9.789</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.59</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.4182</v>
+        <v>-0.4301</v>
       </c>
       <c r="J101" t="n">
-        <v>-10.8732</v>
+        <v>-11.1826</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.55</v>
       </c>
       <c r="I102" t="n">
-        <v>1.1836</v>
+        <v>1.1534</v>
       </c>
       <c r="J102" t="n">
-        <v>30.7736</v>
+        <v>29.9884</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.38</v>
       </c>
       <c r="I103" t="n">
-        <v>0.946</v>
+        <v>0.893</v>
       </c>
       <c r="J103" t="n">
-        <v>24.596</v>
+        <v>23.218</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.31</v>
       </c>
       <c r="I104" t="n">
-        <v>0.7956</v>
+        <v>0.7588</v>
       </c>
       <c r="J104" t="n">
-        <v>20.6856</v>
+        <v>19.7288</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>1.27</v>
       </c>
       <c r="I105" t="n">
-        <v>0.7081</v>
+        <v>0.6808999999999999</v>
       </c>
       <c r="J105" t="n">
-        <v>18.4106</v>
+        <v>17.7034</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.95</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.2726</v>
+        <v>-0.2529</v>
       </c>
       <c r="J106" t="n">
-        <v>-7.0876</v>
+        <v>-6.5754</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.03</v>
       </c>
       <c r="I107" t="n">
-        <v>0.1395</v>
+        <v>0.1346</v>
       </c>
       <c r="J107" t="n">
-        <v>3.627</v>
+        <v>3.4996</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>0.98</v>
       </c>
       <c r="I108" t="n">
-        <v>-0.0151</v>
+        <v>-0.0267</v>
       </c>
       <c r="J108" t="n">
-        <v>-0.3926</v>
+        <v>-0.6942</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.2093</v>
+        <v>-0.2272</v>
       </c>
       <c r="J109" t="n">
-        <v>-5.4418</v>
+        <v>-5.9072</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.79</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.2288</v>
+        <v>-0.2466</v>
       </c>
       <c r="J110" t="n">
-        <v>-5.9488</v>
+        <v>-6.4116</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.57</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.4376</v>
+        <v>-0.4483</v>
       </c>
       <c r="J111" t="n">
-        <v>-11.3776</v>
+        <v>-11.6558</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.44</v>
       </c>
       <c r="I112" t="n">
-        <v>1.074</v>
+        <v>1.0269</v>
       </c>
       <c r="J112" t="n">
-        <v>36.516</v>
+        <v>34.9146</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.16</v>
       </c>
       <c r="I113" t="n">
-        <v>0.4694</v>
+        <v>0.4614</v>
       </c>
       <c r="J113" t="n">
-        <v>15.9596</v>
+        <v>15.6876</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>1.15</v>
       </c>
       <c r="I114" t="n">
-        <v>0.4448</v>
+        <v>0.4389</v>
       </c>
       <c r="J114" t="n">
-        <v>15.1232</v>
+        <v>14.9226</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>1.13</v>
       </c>
       <c r="I115" t="n">
-        <v>0.3935</v>
+        <v>0.3918</v>
       </c>
       <c r="J115" t="n">
-        <v>13.379</v>
+        <v>13.3212</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.91</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.3635</v>
+        <v>-0.3456</v>
       </c>
       <c r="J116" t="n">
-        <v>-12.359</v>
+        <v>-11.7504</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.11</v>
       </c>
       <c r="I117" t="n">
-        <v>0.2803</v>
+        <v>0.2818</v>
       </c>
       <c r="J117" t="n">
-        <v>9.530200000000001</v>
+        <v>9.581200000000001</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.08</v>
       </c>
       <c r="I118" t="n">
-        <v>0.2174</v>
+        <v>0.2215</v>
       </c>
       <c r="J118" t="n">
-        <v>7.3916</v>
+        <v>7.531</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>0.9</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.129</v>
+        <v>-0.1429</v>
       </c>
       <c r="J119" t="n">
-        <v>-4.386</v>
+        <v>-4.8586</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.86</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.1719</v>
+        <v>-0.1866</v>
       </c>
       <c r="J120" t="n">
-        <v>-5.8446</v>
+        <v>-6.3444</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.2233</v>
+        <v>-0.238</v>
       </c>
       <c r="J121" t="n">
-        <v>-7.5922</v>
+        <v>-8.092000000000001</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.26</v>
       </c>
       <c r="I122" t="n">
-        <v>0.7785</v>
+        <v>0.7252999999999999</v>
       </c>
       <c r="J122" t="n">
-        <v>23.355</v>
+        <v>21.759</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.18</v>
       </c>
       <c r="I123" t="n">
-        <v>0.5722</v>
+        <v>0.5433</v>
       </c>
       <c r="J123" t="n">
-        <v>17.166</v>
+        <v>16.299</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>0.9</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.3466</v>
+        <v>-0.3404</v>
       </c>
       <c r="J124" t="n">
-        <v>-10.398</v>
+        <v>-10.212</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.82</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.5663</v>
+        <v>-0.5391</v>
       </c>
       <c r="J125" t="n">
-        <v>-16.989</v>
+        <v>-16.173</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.8</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.6187</v>
+        <v>-0.5857</v>
       </c>
       <c r="J126" t="n">
-        <v>-18.561</v>
+        <v>-17.571</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.64</v>
       </c>
       <c r="I127" t="n">
-        <v>1.0539</v>
+        <v>1.0219</v>
       </c>
       <c r="J127" t="n">
-        <v>31.617</v>
+        <v>30.657</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.21</v>
       </c>
       <c r="I128" t="n">
-        <v>0.4135</v>
+        <v>0.4191</v>
       </c>
       <c r="J128" t="n">
-        <v>12.405</v>
+        <v>12.573</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>1.11</v>
       </c>
       <c r="I129" t="n">
-        <v>0.2353</v>
+        <v>0.2495</v>
       </c>
       <c r="J129" t="n">
-        <v>7.059</v>
+        <v>7.485</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>1.01</v>
       </c>
       <c r="I130" t="n">
-        <v>0.0066</v>
+        <v>0.0209</v>
       </c>
       <c r="J130" t="n">
-        <v>0.198</v>
+        <v>0.627</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.97</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.0689</v>
+        <v>-0.0728</v>
       </c>
       <c r="J131" t="n">
-        <v>-2.067</v>
+        <v>-2.184</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>0.97</v>
       </c>
       <c r="I132" t="n">
-        <v>0.0534</v>
+        <v>0.0064</v>
       </c>
       <c r="J132" t="n">
-        <v>1.1214</v>
+        <v>0.1344</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I133" t="n">
-        <v>-0.2976</v>
+        <v>-0.3195</v>
       </c>
       <c r="J133" t="n">
-        <v>-6.2496</v>
+        <v>-6.7095</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>0.6</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.379</v>
+        <v>-0.3979</v>
       </c>
       <c r="J134" t="n">
-        <v>-7.959</v>
+        <v>-8.3559</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.52</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.4533</v>
+        <v>-0.4681</v>
       </c>
       <c r="J135" t="n">
-        <v>-9.519299999999999</v>
+        <v>-9.8301</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.41</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.5571</v>
+        <v>-0.5647</v>
       </c>
       <c r="J136" t="n">
-        <v>-11.6991</v>
+        <v>-11.8587</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.71</v>
       </c>
       <c r="I137" t="n">
-        <v>1.341</v>
+        <v>1.3278</v>
       </c>
       <c r="J137" t="n">
-        <v>28.161</v>
+        <v>27.8838</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.66</v>
       </c>
       <c r="I138" t="n">
-        <v>1.2831</v>
+        <v>1.2661</v>
       </c>
       <c r="J138" t="n">
-        <v>26.9451</v>
+        <v>26.5881</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>1.51</v>
       </c>
       <c r="I139" t="n">
-        <v>1.1078</v>
+        <v>1.0772</v>
       </c>
       <c r="J139" t="n">
-        <v>23.2638</v>
+        <v>22.6212</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>1.51</v>
       </c>
       <c r="I140" t="n">
-        <v>1.1078</v>
+        <v>1.0772</v>
       </c>
       <c r="J140" t="n">
-        <v>23.2638</v>
+        <v>22.6212</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.97</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.2424</v>
+        <v>-0.214</v>
       </c>
       <c r="J141" t="n">
-        <v>-5.0904</v>
+        <v>-4.494</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.22</v>
       </c>
       <c r="I142" t="n">
-        <v>0.4645</v>
+        <v>0.4597</v>
       </c>
       <c r="J142" t="n">
-        <v>16.722</v>
+        <v>16.5492</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.21</v>
       </c>
       <c r="I143" t="n">
-        <v>0.4465</v>
+        <v>0.443</v>
       </c>
       <c r="J143" t="n">
-        <v>16.074</v>
+        <v>15.948</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>0.95</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.0794</v>
+        <v>-0.0887</v>
       </c>
       <c r="J144" t="n">
-        <v>-2.8584</v>
+        <v>-3.1932</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.0917</v>
+        <v>-0.1018</v>
       </c>
       <c r="J145" t="n">
-        <v>-3.3012</v>
+        <v>-3.6648</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.85</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.1918</v>
+        <v>-0.2045</v>
       </c>
       <c r="J146" t="n">
-        <v>-6.9048</v>
+        <v>-7.362</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.19</v>
       </c>
       <c r="I147" t="n">
-        <v>0.555</v>
+        <v>0.5364</v>
       </c>
       <c r="J147" t="n">
-        <v>19.98</v>
+        <v>19.3104</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.1</v>
       </c>
       <c r="I148" t="n">
-        <v>0.3218</v>
+        <v>0.3234</v>
       </c>
       <c r="J148" t="n">
-        <v>11.5848</v>
+        <v>11.6424</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.1</v>
       </c>
       <c r="I149" t="n">
-        <v>0.3218</v>
+        <v>0.3234</v>
       </c>
       <c r="J149" t="n">
-        <v>11.5848</v>
+        <v>11.6424</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>1.09</v>
       </c>
       <c r="I150" t="n">
-        <v>0.2941</v>
+        <v>0.2976</v>
       </c>
       <c r="J150" t="n">
-        <v>10.5876</v>
+        <v>10.7136</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>1.07</v>
       </c>
       <c r="I151" t="n">
-        <v>0.2361</v>
+        <v>0.2433</v>
       </c>
       <c r="J151" t="n">
-        <v>8.499599999999999</v>
+        <v>8.758800000000001</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.08</v>
       </c>
       <c r="I152" t="n">
-        <v>0.1765</v>
+        <v>0.181</v>
       </c>
       <c r="J152" t="n">
-        <v>5.295</v>
+        <v>5.43</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.07</v>
       </c>
       <c r="I153" t="n">
-        <v>0.1596</v>
+        <v>0.1643</v>
       </c>
       <c r="J153" t="n">
-        <v>4.788</v>
+        <v>4.929</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>1.03</v>
       </c>
       <c r="I154" t="n">
-        <v>0.0868</v>
+        <v>0.0905</v>
       </c>
       <c r="J154" t="n">
-        <v>2.604</v>
+        <v>2.715</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.71</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.3159</v>
+        <v>-0.33</v>
       </c>
       <c r="J155" t="n">
-        <v>-9.477</v>
+        <v>-9.9</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.66</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.3633</v>
+        <v>-0.3758</v>
       </c>
       <c r="J156" t="n">
-        <v>-10.899</v>
+        <v>-11.274</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.5</v>
       </c>
       <c r="I157" t="n">
-        <v>0.6358</v>
+        <v>0.6345</v>
       </c>
       <c r="J157" t="n">
-        <v>19.074</v>
+        <v>19.035</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.22</v>
       </c>
       <c r="I158" t="n">
-        <v>0.3114</v>
+        <v>0.3269</v>
       </c>
       <c r="J158" t="n">
-        <v>9.342000000000001</v>
+        <v>9.807</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.08</v>
       </c>
       <c r="I159" t="n">
-        <v>0.1296</v>
+        <v>0.1457</v>
       </c>
       <c r="J159" t="n">
-        <v>3.888</v>
+        <v>4.371</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>1.07</v>
       </c>
       <c r="I160" t="n">
-        <v>0.1146</v>
+        <v>0.1304</v>
       </c>
       <c r="J160" t="n">
-        <v>3.438</v>
+        <v>3.912</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.86</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.1933</v>
+        <v>-0.2033</v>
       </c>
       <c r="J161" t="n">
-        <v>-5.799</v>
+        <v>-6.099</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.67</v>
       </c>
       <c r="I162" t="n">
-        <v>1.3224</v>
+        <v>1.3028</v>
       </c>
       <c r="J162" t="n">
-        <v>30.4152</v>
+        <v>29.9644</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.53</v>
       </c>
       <c r="I163" t="n">
-        <v>1.1524</v>
+        <v>1.1212</v>
       </c>
       <c r="J163" t="n">
-        <v>26.5052</v>
+        <v>25.7876</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>1.24</v>
       </c>
       <c r="I164" t="n">
-        <v>0.6324</v>
+        <v>0.6148</v>
       </c>
       <c r="J164" t="n">
-        <v>14.5452</v>
+        <v>14.1404</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>1.16</v>
       </c>
       <c r="I165" t="n">
-        <v>0.4351</v>
+        <v>0.4378</v>
       </c>
       <c r="J165" t="n">
-        <v>10.0073</v>
+        <v>10.0694</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>1.03</v>
       </c>
       <c r="I166" t="n">
-        <v>0.0543</v>
+        <v>0.08309999999999999</v>
       </c>
       <c r="J166" t="n">
-        <v>1.2489</v>
+        <v>1.9113</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>0.88</v>
       </c>
       <c r="I167" t="n">
-        <v>-0.1213</v>
+        <v>-0.1425</v>
       </c>
       <c r="J167" t="n">
-        <v>-2.7899</v>
+        <v>-3.2775</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>0.86</v>
       </c>
       <c r="I168" t="n">
-        <v>-0.1439</v>
+        <v>-0.1651</v>
       </c>
       <c r="J168" t="n">
-        <v>-3.3097</v>
+        <v>-3.7973</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>0.85</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.1549</v>
+        <v>-0.176</v>
       </c>
       <c r="J169" t="n">
-        <v>-3.5627</v>
+        <v>-4.048</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.67</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.3298</v>
+        <v>-0.3479</v>
       </c>
       <c r="J170" t="n">
-        <v>-7.5854</v>
+        <v>-8.0017</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.43</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.5536</v>
+        <v>-0.5594</v>
       </c>
       <c r="J171" t="n">
-        <v>-12.7328</v>
+        <v>-12.8662</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.6</v>
       </c>
       <c r="I172" t="n">
-        <v>1.285</v>
+        <v>1.2545</v>
       </c>
       <c r="J172" t="n">
-        <v>34.695</v>
+        <v>33.8715</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.08</v>
       </c>
       <c r="I173" t="n">
-        <v>0.2581</v>
+        <v>0.2658</v>
       </c>
       <c r="J173" t="n">
-        <v>6.9687</v>
+        <v>7.1766</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>1.06</v>
       </c>
       <c r="I174" t="n">
-        <v>0.1978</v>
+        <v>0.2091</v>
       </c>
       <c r="J174" t="n">
-        <v>5.3406</v>
+        <v>5.6457</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>1.02</v>
       </c>
       <c r="I175" t="n">
-        <v>0.0615</v>
+        <v>0.0775</v>
       </c>
       <c r="J175" t="n">
-        <v>1.6605</v>
+        <v>2.0925</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.96</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.2026</v>
+        <v>-0.1953</v>
       </c>
       <c r="J176" t="n">
-        <v>-5.4702</v>
+        <v>-5.2731</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.22</v>
       </c>
       <c r="I177" t="n">
-        <v>0.485</v>
+        <v>0.4747</v>
       </c>
       <c r="J177" t="n">
-        <v>13.095</v>
+        <v>12.8169</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.2</v>
       </c>
       <c r="I178" t="n">
-        <v>0.4481</v>
+        <v>0.4406</v>
       </c>
       <c r="J178" t="n">
-        <v>12.0987</v>
+        <v>11.8962</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.12</v>
       </c>
       <c r="I179" t="n">
-        <v>0.2944</v>
+        <v>0.2966</v>
       </c>
       <c r="J179" t="n">
-        <v>7.9488</v>
+        <v>8.0082</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>0.75</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.285</v>
+        <v>-0.2984</v>
       </c>
       <c r="J180" t="n">
-        <v>-7.695</v>
+        <v>-8.056800000000001</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.57</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.4537</v>
+        <v>-0.461</v>
       </c>
       <c r="J181" t="n">
-        <v>-12.2499</v>
+        <v>-12.447</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.22</v>
       </c>
       <c r="I182" t="n">
-        <v>0.6464</v>
+        <v>0.6147</v>
       </c>
       <c r="J182" t="n">
-        <v>18.0992</v>
+        <v>17.2116</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.07</v>
       </c>
       <c r="I183" t="n">
-        <v>0.2444</v>
+        <v>0.2489</v>
       </c>
       <c r="J183" t="n">
-        <v>6.8432</v>
+        <v>6.9692</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>1.06</v>
       </c>
       <c r="I184" t="n">
-        <v>0.2152</v>
+        <v>0.221</v>
       </c>
       <c r="J184" t="n">
-        <v>6.0256</v>
+        <v>6.188</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>1.03</v>
       </c>
       <c r="I185" t="n">
-        <v>0.1184</v>
+        <v>0.1276</v>
       </c>
       <c r="J185" t="n">
-        <v>3.3152</v>
+        <v>3.5728</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.93</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.2772</v>
+        <v>-0.2714</v>
       </c>
       <c r="J186" t="n">
-        <v>-7.7616</v>
+        <v>-7.5992</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.33</v>
       </c>
       <c r="I187" t="n">
-        <v>0.6511</v>
+        <v>0.6312</v>
       </c>
       <c r="J187" t="n">
-        <v>18.2308</v>
+        <v>17.6736</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.17</v>
       </c>
       <c r="I188" t="n">
-        <v>0.3697</v>
+        <v>0.3722</v>
       </c>
       <c r="J188" t="n">
-        <v>10.3516</v>
+        <v>10.4216</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>1.14</v>
       </c>
       <c r="I189" t="n">
-        <v>0.3136</v>
+        <v>0.3192</v>
       </c>
       <c r="J189" t="n">
-        <v>8.780799999999999</v>
+        <v>8.9376</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.83</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.2141</v>
+        <v>-0.2265</v>
       </c>
       <c r="J190" t="n">
-        <v>-5.9948</v>
+        <v>-6.342</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.77</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.2742</v>
+        <v>-0.286</v>
       </c>
       <c r="J191" t="n">
-        <v>-7.6776</v>
+        <v>-8.007999999999999</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.82</v>
       </c>
       <c r="I192" t="n">
-        <v>1.5059</v>
+        <v>1.4958</v>
       </c>
       <c r="J192" t="n">
-        <v>34.6357</v>
+        <v>34.4034</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.64</v>
       </c>
       <c r="I193" t="n">
-        <v>1.2907</v>
+        <v>1.2683</v>
       </c>
       <c r="J193" t="n">
-        <v>29.6861</v>
+        <v>29.1709</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.41</v>
       </c>
       <c r="I194" t="n">
-        <v>0.9977</v>
+        <v>0.9458</v>
       </c>
       <c r="J194" t="n">
-        <v>22.9471</v>
+        <v>21.7534</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>0.83</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.6208</v>
+        <v>-0.5723</v>
       </c>
       <c r="J195" t="n">
-        <v>-14.2784</v>
+        <v>-13.1629</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.83</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.6208</v>
+        <v>-0.5723</v>
       </c>
       <c r="J196" t="n">
-        <v>-14.2784</v>
+        <v>-13.1629</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.31</v>
       </c>
       <c r="I197" t="n">
-        <v>0.7097</v>
+        <v>0.6688</v>
       </c>
       <c r="J197" t="n">
-        <v>16.3231</v>
+        <v>15.3824</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.09</v>
       </c>
       <c r="I198" t="n">
-        <v>0.2768</v>
+        <v>0.2699</v>
       </c>
       <c r="J198" t="n">
-        <v>6.3664</v>
+        <v>6.2077</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>1.01</v>
       </c>
       <c r="I199" t="n">
-        <v>0.07729999999999999</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="J199" t="n">
-        <v>1.7779</v>
+        <v>1.656</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.49</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.5125999999999999</v>
+        <v>-0.5189</v>
       </c>
       <c r="J200" t="n">
-        <v>-11.7898</v>
+        <v>-11.9347</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.34</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.6478</v>
+        <v>-0.6453</v>
       </c>
       <c r="J201" t="n">
-        <v>-14.8994</v>
+        <v>-14.8419</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.38</v>
       </c>
       <c r="I202" t="n">
-        <v>0.5042</v>
+        <v>0.5106000000000001</v>
       </c>
       <c r="J202" t="n">
-        <v>13.6134</v>
+        <v>13.7862</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.3</v>
       </c>
       <c r="I203" t="n">
-        <v>0.4106</v>
+        <v>0.4218</v>
       </c>
       <c r="J203" t="n">
-        <v>11.0862</v>
+        <v>11.3886</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>1.13</v>
       </c>
       <c r="I204" t="n">
-        <v>0.2002</v>
+        <v>0.2166</v>
       </c>
       <c r="J204" t="n">
-        <v>5.4054</v>
+        <v>5.8482</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>1</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.0116</v>
+        <v>-0.0089</v>
       </c>
       <c r="J205" t="n">
-        <v>-0.3132</v>
+        <v>-0.2403</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.83</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.2226</v>
+        <v>-0.2331</v>
       </c>
       <c r="J206" t="n">
-        <v>-6.0102</v>
+        <v>-6.2937</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.17</v>
       </c>
       <c r="I207" t="n">
-        <v>0.3013</v>
+        <v>0.3053</v>
       </c>
       <c r="J207" t="n">
-        <v>8.1351</v>
+        <v>8.2431</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.03</v>
       </c>
       <c r="I208" t="n">
-        <v>0.0755</v>
+        <v>0.0822</v>
       </c>
       <c r="J208" t="n">
-        <v>2.0385</v>
+        <v>2.2194</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>0.93</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.09660000000000001</v>
+        <v>-0.1089</v>
       </c>
       <c r="J209" t="n">
-        <v>-2.6082</v>
+        <v>-2.9403</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>0.91</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.1194</v>
+        <v>-0.1326</v>
       </c>
       <c r="J210" t="n">
-        <v>-3.2238</v>
+        <v>-3.5802</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.79</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.245</v>
+        <v>-0.2591</v>
       </c>
       <c r="J211" t="n">
-        <v>-6.615</v>
+        <v>-6.9957</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.32</v>
       </c>
       <c r="I212" t="n">
-        <v>0.6616</v>
+        <v>0.6361</v>
       </c>
       <c r="J212" t="n">
-        <v>18.5248</v>
+        <v>17.8108</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.29</v>
       </c>
       <c r="I213" t="n">
-        <v>0.6091</v>
+        <v>0.5885</v>
       </c>
       <c r="J213" t="n">
-        <v>17.0548</v>
+        <v>16.478</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>0.83</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.2058</v>
+        <v>-0.22</v>
       </c>
       <c r="J214" t="n">
-        <v>-5.7624</v>
+        <v>-6.16</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>0.78</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.2561</v>
+        <v>-0.2699</v>
       </c>
       <c r="J215" t="n">
-        <v>-7.1708</v>
+        <v>-7.5572</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.66</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.3712</v>
+        <v>-0.3819</v>
       </c>
       <c r="J216" t="n">
-        <v>-10.3936</v>
+        <v>-10.6932</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.39</v>
       </c>
       <c r="I217" t="n">
-        <v>1.021</v>
+        <v>0.9597</v>
       </c>
       <c r="J217" t="n">
-        <v>28.588</v>
+        <v>26.8716</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.39</v>
       </c>
       <c r="I218" t="n">
-        <v>1.021</v>
+        <v>0.9597</v>
       </c>
       <c r="J218" t="n">
-        <v>28.588</v>
+        <v>26.8716</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>1.01</v>
       </c>
       <c r="I219" t="n">
-        <v>0.0338</v>
+        <v>0.0454</v>
       </c>
       <c r="J219" t="n">
-        <v>0.9464</v>
+        <v>1.2712</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>0.97</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.1538</v>
+        <v>-0.1518</v>
       </c>
       <c r="J220" t="n">
-        <v>-4.3064</v>
+        <v>-4.2504</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.7</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.899</v>
+        <v>-0.8268</v>
       </c>
       <c r="J221" t="n">
-        <v>-25.172</v>
+        <v>-23.1504</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.42</v>
       </c>
       <c r="I222" t="n">
-        <v>0.8177</v>
+        <v>0.7785</v>
       </c>
       <c r="J222" t="n">
-        <v>23.7133</v>
+        <v>22.5765</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>0.96</v>
       </c>
       <c r="I223" t="n">
-        <v>-0.064</v>
+        <v>-0.0731</v>
       </c>
       <c r="J223" t="n">
-        <v>-1.856</v>
+        <v>-2.1199</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>0.95</v>
       </c>
       <c r="I224" t="n">
-        <v>-0.0767</v>
+        <v>-0.0867</v>
       </c>
       <c r="J224" t="n">
-        <v>-2.2243</v>
+        <v>-2.5143</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>0.9</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.1351</v>
+        <v>-0.1476</v>
       </c>
       <c r="J225" t="n">
-        <v>-3.9179</v>
+        <v>-4.2804</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.2299</v>
+        <v>-0.2432</v>
       </c>
       <c r="J226" t="n">
-        <v>-6.6671</v>
+        <v>-7.0528</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.3</v>
       </c>
       <c r="I227" t="n">
-        <v>0.8379</v>
+        <v>0.7839</v>
       </c>
       <c r="J227" t="n">
-        <v>24.2991</v>
+        <v>22.7331</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>1.1</v>
       </c>
       <c r="I228" t="n">
-        <v>0.3275</v>
+        <v>0.3273</v>
       </c>
       <c r="J228" t="n">
-        <v>9.4975</v>
+        <v>9.4917</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>1.04</v>
       </c>
       <c r="I229" t="n">
-        <v>0.1499</v>
+        <v>0.159</v>
       </c>
       <c r="J229" t="n">
-        <v>4.3471</v>
+        <v>4.611</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>1.03</v>
       </c>
       <c r="I230" t="n">
-        <v>0.1157</v>
+        <v>0.1257</v>
       </c>
       <c r="J230" t="n">
-        <v>3.3553</v>
+        <v>3.6453</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.9</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.37</v>
+        <v>-0.3567</v>
       </c>
       <c r="J231" t="n">
-        <v>-10.73</v>
+        <v>-10.3443</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.52</v>
       </c>
       <c r="I232" t="n">
-        <v>1.168</v>
+        <v>1.1325</v>
       </c>
       <c r="J232" t="n">
-        <v>33.872</v>
+        <v>32.8425</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1.45</v>
       </c>
       <c r="I233" t="n">
-        <v>1.078</v>
+        <v>1.0336</v>
       </c>
       <c r="J233" t="n">
-        <v>31.262</v>
+        <v>29.9744</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>1.09</v>
       </c>
       <c r="I234" t="n">
-        <v>0.2749</v>
+        <v>0.2845</v>
       </c>
       <c r="J234" t="n">
-        <v>7.9721</v>
+        <v>8.250500000000001</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>0.98</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.1437</v>
+        <v>-0.1342</v>
       </c>
       <c r="J235" t="n">
-        <v>-4.1673</v>
+        <v>-3.8918</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.2817</v>
+        <v>-0.2671</v>
       </c>
       <c r="J236" t="n">
-        <v>-8.1693</v>
+        <v>-7.7459</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.15</v>
       </c>
       <c r="I237" t="n">
-        <v>0.3724</v>
+        <v>0.3663</v>
       </c>
       <c r="J237" t="n">
-        <v>10.7996</v>
+        <v>10.6227</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>1.01</v>
       </c>
       <c r="I238" t="n">
-        <v>0.0549</v>
+        <v>0.0557</v>
       </c>
       <c r="J238" t="n">
-        <v>1.5921</v>
+        <v>1.6153</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>0.9</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.1256</v>
+        <v>-0.1403</v>
       </c>
       <c r="J239" t="n">
-        <v>-3.6424</v>
+        <v>-4.0687</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>0.82</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.209</v>
+        <v>-0.2247</v>
       </c>
       <c r="J240" t="n">
-        <v>-6.061</v>
+        <v>-6.5163</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.71</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.3169</v>
+        <v>-0.3307</v>
       </c>
       <c r="J241" t="n">
-        <v>-9.190099999999999</v>
+        <v>-9.590299999999999</v>
       </c>
     </row>
     <row r="242">
@@ -12069,10 +12069,10 @@
         <v>0.99</v>
       </c>
       <c r="I243" t="n">
-        <v>-0.003</v>
+        <v>-0.0118</v>
       </c>
       <c r="J243" t="n">
-        <v>-0.081</v>
+        <v>-0.3186</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>0.82</v>
       </c>
       <c r="I244" t="n">
-        <v>-0.2019</v>
+        <v>-0.2192</v>
       </c>
       <c r="J244" t="n">
-        <v>-5.4513</v>
+        <v>-5.9184</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>0.76</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.2608</v>
+        <v>-0.2776</v>
       </c>
       <c r="J245" t="n">
-        <v>-7.0416</v>
+        <v>-7.4952</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>0.62</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.3941</v>
+        <v>-0.4064</v>
       </c>
       <c r="J246" t="n">
-        <v>-10.6407</v>
+        <v>-10.9728</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>2.09</v>
       </c>
       <c r="I247" t="n">
-        <v>1.1277</v>
+        <v>1.1262</v>
       </c>
       <c r="J247" t="n">
-        <v>30.4479</v>
+        <v>30.4074</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>1.13</v>
       </c>
       <c r="I248" t="n">
-        <v>0.1864</v>
+        <v>0.2063</v>
       </c>
       <c r="J248" t="n">
-        <v>5.0328</v>
+        <v>5.5701</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>1.11</v>
       </c>
       <c r="I249" t="n">
-        <v>0.1589</v>
+        <v>0.1788</v>
       </c>
       <c r="J249" t="n">
-        <v>4.2903</v>
+        <v>4.8276</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>1.06</v>
       </c>
       <c r="I250" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.1038</v>
       </c>
       <c r="J250" t="n">
-        <v>2.295</v>
+        <v>2.8026</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.92</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.1383</v>
+        <v>-0.1444</v>
       </c>
       <c r="J251" t="n">
-        <v>-3.7341</v>
+        <v>-3.8988</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>1.66</v>
       </c>
       <c r="I252" t="n">
-        <v>1.3113</v>
+        <v>1.2908</v>
       </c>
       <c r="J252" t="n">
-        <v>31.4712</v>
+        <v>30.9792</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>1.43</v>
       </c>
       <c r="I253" t="n">
-        <v>1.0259</v>
+        <v>0.9777</v>
       </c>
       <c r="J253" t="n">
-        <v>24.6216</v>
+        <v>23.4648</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>1.41</v>
       </c>
       <c r="I254" t="n">
-        <v>0.9947</v>
+        <v>0.9433</v>
       </c>
       <c r="J254" t="n">
-        <v>23.8728</v>
+        <v>22.6392</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>1.13</v>
       </c>
       <c r="I255" t="n">
-        <v>0.3569</v>
+        <v>0.3665</v>
       </c>
       <c r="J255" t="n">
-        <v>8.5656</v>
+        <v>8.795999999999999</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>0.98</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.1739</v>
+        <v>-0.1553</v>
       </c>
       <c r="J256" t="n">
-        <v>-4.1736</v>
+        <v>-3.7272</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>1.31</v>
       </c>
       <c r="I257" t="n">
-        <v>0.7109</v>
+        <v>0.6697</v>
       </c>
       <c r="J257" t="n">
-        <v>17.0616</v>
+        <v>16.0728</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>1.02</v>
       </c>
       <c r="I258" t="n">
-        <v>0.1081</v>
+        <v>0.1039</v>
       </c>
       <c r="J258" t="n">
-        <v>2.5944</v>
+        <v>2.4936</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>0.85</v>
       </c>
       <c r="I259" t="n">
-        <v>-0.1713</v>
+        <v>-0.1887</v>
       </c>
       <c r="J259" t="n">
-        <v>-4.1112</v>
+        <v>-4.5288</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>0.7</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.317</v>
+        <v>-0.3326</v>
       </c>
       <c r="J260" t="n">
-        <v>-7.608</v>
+        <v>-7.9824</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>0.35</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.6387</v>
+        <v>-0.6368</v>
       </c>
       <c r="J261" t="n">
-        <v>-15.3288</v>
+        <v>-15.2832</v>
       </c>
     </row>
     <row r="262">
@@ -12829,10 +12829,10 @@
         <v>1.71</v>
       </c>
       <c r="I262" t="n">
-        <v>1.3721</v>
+        <v>1.3553</v>
       </c>
       <c r="J262" t="n">
-        <v>32.9304</v>
+        <v>32.5272</v>
       </c>
     </row>
     <row r="263">
@@ -12869,10 +12869,10 @@
         <v>1.57</v>
       </c>
       <c r="I263" t="n">
-        <v>1.2029</v>
+        <v>1.1751</v>
       </c>
       <c r="J263" t="n">
-        <v>28.8696</v>
+        <v>28.2024</v>
       </c>
     </row>
     <row r="264">
@@ -12909,10 +12909,10 @@
         <v>1.29</v>
       </c>
       <c r="I264" t="n">
-        <v>0.7487</v>
+        <v>0.7178</v>
       </c>
       <c r="J264" t="n">
-        <v>17.9688</v>
+        <v>17.2272</v>
       </c>
     </row>
     <row r="265">
@@ -12949,10 +12949,10 @@
         <v>1.24</v>
       </c>
       <c r="I265" t="n">
-        <v>0.634</v>
+        <v>0.6159</v>
       </c>
       <c r="J265" t="n">
-        <v>15.216</v>
+        <v>14.7816</v>
       </c>
     </row>
     <row r="266">
@@ -12989,10 +12989,10 @@
         <v>0.78</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.752</v>
+        <v>-0.6889999999999999</v>
       </c>
       <c r="J266" t="n">
-        <v>-18.048</v>
+        <v>-16.536</v>
       </c>
     </row>
     <row r="267">
@@ -13029,10 +13029,10 @@
         <v>0.99</v>
       </c>
       <c r="I267" t="n">
-        <v>0.008399999999999999</v>
+        <v>-0.0058</v>
       </c>
       <c r="J267" t="n">
-        <v>0.2016</v>
+        <v>-0.1392</v>
       </c>
     </row>
     <row r="268">
@@ -13069,10 +13069,10 @@
         <v>0.95</v>
       </c>
       <c r="I268" t="n">
-        <v>-0.0541</v>
+        <v>-0.0693</v>
       </c>
       <c r="J268" t="n">
-        <v>-1.2984</v>
+        <v>-1.6632</v>
       </c>
     </row>
     <row r="269">
@@ -13109,10 +13109,10 @@
         <v>0.78</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.2366</v>
+        <v>-0.2547</v>
       </c>
       <c r="J269" t="n">
-        <v>-5.6784</v>
+        <v>-6.1128</v>
       </c>
     </row>
     <row r="270">
@@ -13149,10 +13149,10 @@
         <v>0.71</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.3038</v>
+        <v>-0.3205</v>
       </c>
       <c r="J270" t="n">
-        <v>-7.2912</v>
+        <v>-7.692</v>
       </c>
     </row>
     <row r="271">
@@ -13189,10 +13189,10 @@
         <v>0.67</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.3418</v>
+        <v>-0.3572</v>
       </c>
       <c r="J271" t="n">
-        <v>-8.203200000000001</v>
+        <v>-8.572800000000001</v>
       </c>
     </row>
     <row r="272">
@@ -13229,10 +13229,10 @@
         <v>1.8</v>
       </c>
       <c r="I272" t="n">
-        <v>1.4926</v>
+        <v>1.48</v>
       </c>
       <c r="J272" t="n">
-        <v>37.315</v>
+        <v>37</v>
       </c>
     </row>
     <row r="273">
@@ -13269,10 +13269,10 @@
         <v>1.71</v>
       </c>
       <c r="I273" t="n">
-        <v>1.3844</v>
+        <v>1.3661</v>
       </c>
       <c r="J273" t="n">
-        <v>34.61</v>
+        <v>34.1525</v>
       </c>
     </row>
     <row r="274">
@@ -13309,10 +13309,10 @@
         <v>1.18</v>
       </c>
       <c r="I274" t="n">
-        <v>0.4984</v>
+        <v>0.4924</v>
       </c>
       <c r="J274" t="n">
-        <v>12.46</v>
+        <v>12.31</v>
       </c>
     </row>
     <row r="275">
@@ -13349,10 +13349,10 @@
         <v>1.17</v>
       </c>
       <c r="I275" t="n">
-        <v>0.4732</v>
+        <v>0.4696</v>
       </c>
       <c r="J275" t="n">
-        <v>11.83</v>
+        <v>11.74</v>
       </c>
     </row>
     <row r="276">
@@ -13389,10 +13389,10 @@
         <v>0.49</v>
       </c>
       <c r="I276" t="n">
-        <v>-1.4234</v>
+        <v>-1.2724</v>
       </c>
       <c r="J276" t="n">
-        <v>-35.585</v>
+        <v>-31.81</v>
       </c>
     </row>
     <row r="277">
@@ -13429,10 +13429,10 @@
         <v>1.13</v>
       </c>
       <c r="I277" t="n">
-        <v>0.3582</v>
+        <v>0.3477</v>
       </c>
       <c r="J277" t="n">
-        <v>8.955</v>
+        <v>8.692500000000001</v>
       </c>
     </row>
     <row r="278">
@@ -13469,10 +13469,10 @@
         <v>0.86</v>
       </c>
       <c r="I278" t="n">
-        <v>-0.1622</v>
+        <v>-0.1792</v>
       </c>
       <c r="J278" t="n">
-        <v>-4.055</v>
+        <v>-4.48</v>
       </c>
     </row>
     <row r="279">
@@ -13509,10 +13509,10 @@
         <v>0.82</v>
       </c>
       <c r="I279" t="n">
-        <v>-0.2016</v>
+        <v>-0.2191</v>
       </c>
       <c r="J279" t="n">
-        <v>-5.04</v>
+        <v>-5.4775</v>
       </c>
     </row>
     <row r="280">
@@ -13549,10 +13549,10 @@
         <v>0.79</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.2313</v>
+        <v>-0.2485</v>
       </c>
       <c r="J280" t="n">
-        <v>-5.7825</v>
+        <v>-6.2125</v>
       </c>
     </row>
     <row r="281">
@@ -13589,10 +13589,10 @@
         <v>0.68</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.3374</v>
+        <v>-0.352</v>
       </c>
       <c r="J281" t="n">
-        <v>-8.435</v>
+        <v>-8.800000000000001</v>
       </c>
     </row>
     <row r="282">
@@ -13629,10 +13629,10 @@
         <v>1.63</v>
       </c>
       <c r="I282" t="n">
-        <v>1.3148</v>
+        <v>1.2874</v>
       </c>
       <c r="J282" t="n">
-        <v>44.7032</v>
+        <v>43.7716</v>
       </c>
     </row>
     <row r="283">
@@ -13669,10 +13669,10 @@
         <v>1.17</v>
       </c>
       <c r="I283" t="n">
-        <v>0.4924</v>
+        <v>0.4827</v>
       </c>
       <c r="J283" t="n">
-        <v>16.7416</v>
+        <v>16.4118</v>
       </c>
     </row>
     <row r="284">
@@ -13709,10 +13709,10 @@
         <v>1.09</v>
       </c>
       <c r="I284" t="n">
-        <v>0.2811</v>
+        <v>0.2887</v>
       </c>
       <c r="J284" t="n">
-        <v>9.557399999999999</v>
+        <v>9.815799999999999</v>
       </c>
     </row>
     <row r="285">
@@ -13749,10 +13749,10 @@
         <v>1.04</v>
       </c>
       <c r="I285" t="n">
-        <v>0.1267</v>
+        <v>0.143</v>
       </c>
       <c r="J285" t="n">
-        <v>4.3078</v>
+        <v>4.862</v>
       </c>
     </row>
     <row r="286">
@@ -13789,10 +13789,10 @@
         <v>0.92</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.3368</v>
+        <v>-0.3202</v>
       </c>
       <c r="J286" t="n">
-        <v>-11.4512</v>
+        <v>-10.8868</v>
       </c>
     </row>
     <row r="287">
@@ -13829,10 +13829,10 @@
         <v>1.35</v>
       </c>
       <c r="I287" t="n">
-        <v>0.7343</v>
+        <v>0.6983</v>
       </c>
       <c r="J287" t="n">
-        <v>24.9662</v>
+        <v>23.7422</v>
       </c>
     </row>
     <row r="288">
@@ -13869,10 +13869,10 @@
         <v>1.03</v>
       </c>
       <c r="I288" t="n">
-        <v>0.1071</v>
+        <v>0.111</v>
       </c>
       <c r="J288" t="n">
-        <v>3.6414</v>
+        <v>3.774</v>
       </c>
     </row>
     <row r="289">
@@ -13909,10 +13909,10 @@
         <v>1.02</v>
       </c>
       <c r="I289" t="n">
-        <v>0.0805</v>
+        <v>0.0838</v>
       </c>
       <c r="J289" t="n">
-        <v>2.737</v>
+        <v>2.8492</v>
       </c>
     </row>
     <row r="290">
@@ -13949,10 +13949,10 @@
         <v>0.63</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.394</v>
+        <v>-0.4048</v>
       </c>
       <c r="J290" t="n">
-        <v>-13.396</v>
+        <v>-13.7632</v>
       </c>
     </row>
     <row r="291">
@@ -13989,10 +13989,10 @@
         <v>0.63</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.394</v>
+        <v>-0.4048</v>
       </c>
       <c r="J291" t="n">
-        <v>-13.396</v>
+        <v>-13.7632</v>
       </c>
     </row>
     <row r="292">
@@ -14029,10 +14029,10 @@
         <v>1.94</v>
       </c>
       <c r="I292" t="n">
-        <v>1.6453</v>
+        <v>1.6418</v>
       </c>
       <c r="J292" t="n">
-        <v>41.1325</v>
+        <v>41.045</v>
       </c>
     </row>
     <row r="293">
@@ -14069,10 +14069,10 @@
         <v>1.23</v>
       </c>
       <c r="I293" t="n">
-        <v>0.612</v>
+        <v>0.5959</v>
       </c>
       <c r="J293" t="n">
-        <v>15.3</v>
+        <v>14.8975</v>
       </c>
     </row>
     <row r="294">
@@ -14109,10 +14109,10 @@
         <v>1.22</v>
       </c>
       <c r="I294" t="n">
-        <v>0.588</v>
+        <v>0.5746</v>
       </c>
       <c r="J294" t="n">
-        <v>14.7</v>
+        <v>14.365</v>
       </c>
     </row>
     <row r="295">
@@ -14149,10 +14149,10 @@
         <v>1.12</v>
       </c>
       <c r="I295" t="n">
-        <v>0.3325</v>
+        <v>0.3436</v>
       </c>
       <c r="J295" t="n">
-        <v>8.3125</v>
+        <v>8.59</v>
       </c>
     </row>
     <row r="296">
@@ -14189,10 +14189,10 @@
         <v>1.04</v>
       </c>
       <c r="I296" t="n">
-        <v>0.09279999999999999</v>
+        <v>0.1193</v>
       </c>
       <c r="J296" t="n">
-        <v>2.32</v>
+        <v>2.9825</v>
       </c>
     </row>
     <row r="297">
@@ -14229,10 +14229,10 @@
         <v>1.14</v>
       </c>
       <c r="I297" t="n">
-        <v>0.4101</v>
+        <v>0.3901</v>
       </c>
       <c r="J297" t="n">
-        <v>10.2525</v>
+        <v>9.7525</v>
       </c>
     </row>
     <row r="298">
@@ -14269,10 +14269,10 @@
         <v>0.93</v>
       </c>
       <c r="I298" t="n">
-        <v>-0.0747</v>
+        <v>-0.0921</v>
       </c>
       <c r="J298" t="n">
-        <v>-1.8675</v>
+        <v>-2.3025</v>
       </c>
     </row>
     <row r="299">
@@ -14309,10 +14309,10 @@
         <v>0.68</v>
       </c>
       <c r="I299" t="n">
-        <v>-0.3289</v>
+        <v>-0.3454</v>
       </c>
       <c r="J299" t="n">
-        <v>-8.2225</v>
+        <v>-8.635</v>
       </c>
     </row>
     <row r="300">
@@ -14349,10 +14349,10 @@
         <v>0.67</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.3384</v>
+        <v>-0.3545</v>
       </c>
       <c r="J300" t="n">
-        <v>-8.460000000000001</v>
+        <v>-8.862500000000001</v>
       </c>
     </row>
     <row r="301">
@@ -14389,10 +14389,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.4414</v>
+        <v>-0.4528</v>
       </c>
       <c r="J301" t="n">
-        <v>-11.035</v>
+        <v>-11.32</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/3515/event_3515_evp_summary.xlsx
+++ b/database/event/3515/event_3515_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.7761</v>
+        <v>6.6406</v>
       </c>
       <c r="C2" t="n">
-        <v>2.927</v>
+        <v>2.8685</v>
       </c>
       <c r="D2" t="n">
-        <v>2.4604</v>
+        <v>2.4193</v>
       </c>
       <c r="E2" t="n">
-        <v>6.7761</v>
+        <v>6.6406</v>
       </c>
       <c r="F2" t="n">
-        <v>4.1844</v>
+        <v>4.0208</v>
       </c>
       <c r="G2" t="n">
-        <v>2.5917</v>
+        <v>2.6198</v>
       </c>
       <c r="H2" t="n">
-        <v>8.9116</v>
+        <v>8.653</v>
       </c>
       <c r="I2" t="n">
-        <v>4.8122</v>
+        <v>4.8584</v>
       </c>
       <c r="J2" t="n">
-        <v>2.5917</v>
+        <v>2.6198</v>
       </c>
       <c r="K2" t="n">
         <v>110</v>
@@ -529,7 +529,7 @@
         <v>102</v>
       </c>
       <c r="M2" t="n">
-        <v>7.4039</v>
+        <v>7.478199999999999</v>
       </c>
       <c r="N2" t="n">
         <v>212</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.0577</v>
+        <v>4.8152</v>
       </c>
       <c r="C3" t="n">
-        <v>2.1847</v>
+        <v>2.08</v>
       </c>
       <c r="D3" t="n">
-        <v>1.6782</v>
+        <v>1.5878</v>
       </c>
       <c r="E3" t="n">
-        <v>5.0577</v>
+        <v>4.8152</v>
       </c>
       <c r="F3" t="n">
-        <v>4.1048</v>
+        <v>3.8676</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9529</v>
+        <v>0.9476</v>
       </c>
       <c r="H3" t="n">
-        <v>8.648999999999999</v>
+        <v>8.0779</v>
       </c>
       <c r="I3" t="n">
-        <v>4.6704</v>
+        <v>4.5355</v>
       </c>
       <c r="J3" t="n">
-        <v>0.9529</v>
+        <v>0.9476</v>
       </c>
       <c r="K3" t="n">
         <v>152</v>
@@ -575,7 +575,7 @@
         <v>103</v>
       </c>
       <c r="M3" t="n">
-        <v>5.6233</v>
+        <v>5.4831</v>
       </c>
       <c r="N3" t="n">
         <v>255</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.4884</v>
+        <v>4.5943</v>
       </c>
       <c r="C4" t="n">
-        <v>1.9388</v>
+        <v>1.9846</v>
       </c>
       <c r="D4" t="n">
-        <v>1.419</v>
+        <v>1.4871</v>
       </c>
       <c r="E4" t="n">
-        <v>4.4884</v>
+        <v>4.5943</v>
       </c>
       <c r="F4" t="n">
-        <v>2.2286</v>
+        <v>2.3289</v>
       </c>
       <c r="G4" t="n">
-        <v>2.2598</v>
+        <v>2.2654</v>
       </c>
       <c r="H4" t="n">
-        <v>2.4589</v>
+        <v>2.3289</v>
       </c>
       <c r="I4" t="n">
-        <v>1.3278</v>
+        <v>1.3076</v>
       </c>
       <c r="J4" t="n">
-        <v>2.2598</v>
+        <v>2.2654</v>
       </c>
       <c r="K4" t="n">
         <v>110</v>
@@ -621,7 +621,7 @@
         <v>102</v>
       </c>
       <c r="M4" t="n">
-        <v>3.5876</v>
+        <v>3.573</v>
       </c>
       <c r="N4" t="n">
         <v>212</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.353</v>
+        <v>4.261</v>
       </c>
       <c r="C5" t="n">
-        <v>1.8803</v>
+        <v>1.8406</v>
       </c>
       <c r="D5" t="n">
-        <v>1.3574</v>
+        <v>1.3353</v>
       </c>
       <c r="E5" t="n">
-        <v>4.353</v>
+        <v>4.261</v>
       </c>
       <c r="F5" t="n">
-        <v>4.029</v>
+        <v>3.8908</v>
       </c>
       <c r="G5" t="n">
-        <v>0.324</v>
+        <v>0.3702</v>
       </c>
       <c r="H5" t="n">
-        <v>8.398999999999999</v>
+        <v>8.164999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>4.5354</v>
+        <v>4.5844</v>
       </c>
       <c r="J5" t="n">
-        <v>0.324</v>
+        <v>0.3702</v>
       </c>
       <c r="K5" t="n">
         <v>152</v>
@@ -667,7 +667,7 @@
         <v>103</v>
       </c>
       <c r="M5" t="n">
-        <v>4.8594</v>
+        <v>4.954599999999999</v>
       </c>
       <c r="N5" t="n">
         <v>255</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.0201</v>
+        <v>3.9039</v>
       </c>
       <c r="C6" t="n">
-        <v>1.7365</v>
+        <v>1.6863</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2058</v>
+        <v>1.1726</v>
       </c>
       <c r="E6" t="n">
-        <v>4.0201</v>
+        <v>3.9039</v>
       </c>
       <c r="F6" t="n">
-        <v>2.7201</v>
+        <v>2.7343</v>
       </c>
       <c r="G6" t="n">
-        <v>1.3</v>
+        <v>1.1696</v>
       </c>
       <c r="H6" t="n">
-        <v>4.0804</v>
+        <v>3.823</v>
       </c>
       <c r="I6" t="n">
-        <v>2.2034</v>
+        <v>2.1465</v>
       </c>
       <c r="J6" t="n">
-        <v>1.3</v>
+        <v>1.1696</v>
       </c>
       <c r="K6" t="n">
         <v>110</v>
@@ -713,7 +713,7 @@
         <v>102</v>
       </c>
       <c r="M6" t="n">
-        <v>3.5034</v>
+        <v>3.3161</v>
       </c>
       <c r="N6" t="n">
         <v>212</v>
@@ -722,93 +722,93 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Magisk</t>
+          <t>nitr0</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.8229</v>
+        <v>3.8231</v>
       </c>
       <c r="C7" t="n">
         <v>1.6514</v>
       </c>
       <c r="D7" t="n">
-        <v>1.1161</v>
+        <v>1.1358</v>
       </c>
       <c r="E7" t="n">
-        <v>3.8229</v>
+        <v>3.8231</v>
       </c>
       <c r="F7" t="n">
-        <v>1.3985</v>
+        <v>2.7173</v>
       </c>
       <c r="G7" t="n">
-        <v>2.4244</v>
+        <v>1.1058</v>
       </c>
       <c r="H7" t="n">
-        <v>1.3985</v>
+        <v>3.7592</v>
       </c>
       <c r="I7" t="n">
-        <v>0.7552</v>
+        <v>2.1107</v>
       </c>
       <c r="J7" t="n">
-        <v>2.4244</v>
+        <v>1.1058</v>
       </c>
       <c r="K7" t="n">
-        <v>110</v>
+        <v>152</v>
       </c>
       <c r="L7" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="M7" t="n">
-        <v>3.1796</v>
+        <v>3.2165</v>
       </c>
       <c r="N7" t="n">
-        <v>212</v>
+        <v>255</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>nitr0</t>
+          <t>Magisk</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.8075</v>
+        <v>3.6141</v>
       </c>
       <c r="C8" t="n">
-        <v>1.6447</v>
+        <v>1.5612</v>
       </c>
       <c r="D8" t="n">
-        <v>1.109</v>
+        <v>1.0406</v>
       </c>
       <c r="E8" t="n">
-        <v>3.8075</v>
+        <v>3.6141</v>
       </c>
       <c r="F8" t="n">
-        <v>2.7098</v>
+        <v>1.2282</v>
       </c>
       <c r="G8" t="n">
-        <v>1.0977</v>
+        <v>2.3859</v>
       </c>
       <c r="H8" t="n">
-        <v>4.0464</v>
+        <v>1.2282</v>
       </c>
       <c r="I8" t="n">
-        <v>2.185</v>
+        <v>0.6896</v>
       </c>
       <c r="J8" t="n">
-        <v>1.0977</v>
+        <v>2.3859</v>
       </c>
       <c r="K8" t="n">
-        <v>152</v>
+        <v>110</v>
       </c>
       <c r="L8" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="M8" t="n">
-        <v>3.2827</v>
+        <v>3.0755</v>
       </c>
       <c r="N8" t="n">
-        <v>255</v>
+        <v>212</v>
       </c>
     </row>
     <row r="9">
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.6688</v>
+        <v>3.5371</v>
       </c>
       <c r="C9" t="n">
-        <v>1.5848</v>
+        <v>1.5279</v>
       </c>
       <c r="D9" t="n">
-        <v>1.0459</v>
+        <v>1.0055</v>
       </c>
       <c r="E9" t="n">
-        <v>3.6688</v>
+        <v>3.5371</v>
       </c>
       <c r="F9" t="n">
-        <v>3.5117</v>
+        <v>3.4145</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1571</v>
+        <v>0.1226</v>
       </c>
       <c r="H9" t="n">
-        <v>6.6923</v>
+        <v>6.3768</v>
       </c>
       <c r="I9" t="n">
-        <v>3.6138</v>
+        <v>3.5804</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1571</v>
+        <v>0.1226</v>
       </c>
       <c r="K9" t="n">
         <v>160</v>
@@ -851,7 +851,7 @@
         <v>54</v>
       </c>
       <c r="M9" t="n">
-        <v>3.7709</v>
+        <v>3.703</v>
       </c>
       <c r="N9" t="n">
         <v>214</v>
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.3461</v>
+        <v>3.3139</v>
       </c>
       <c r="C10" t="n">
-        <v>1.4454</v>
+        <v>1.4315</v>
       </c>
       <c r="D10" t="n">
-        <v>0.899</v>
+        <v>0.9039</v>
       </c>
       <c r="E10" t="n">
-        <v>3.3461</v>
+        <v>3.3139</v>
       </c>
       <c r="F10" t="n">
-        <v>3.0753</v>
+        <v>3.0538</v>
       </c>
       <c r="G10" t="n">
-        <v>0.2708</v>
+        <v>0.2601</v>
       </c>
       <c r="H10" t="n">
-        <v>5.2525</v>
+        <v>5.0225</v>
       </c>
       <c r="I10" t="n">
-        <v>2.8363</v>
+        <v>2.82</v>
       </c>
       <c r="J10" t="n">
-        <v>0.2708</v>
+        <v>0.2601</v>
       </c>
       <c r="K10" t="n">
         <v>160</v>
@@ -897,7 +897,7 @@
         <v>54</v>
       </c>
       <c r="M10" t="n">
-        <v>3.1071</v>
+        <v>3.0801</v>
       </c>
       <c r="N10" t="n">
         <v>214</v>
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.0082</v>
+        <v>3.047</v>
       </c>
       <c r="C11" t="n">
-        <v>1.2994</v>
+        <v>1.3162</v>
       </c>
       <c r="D11" t="n">
-        <v>0.7452</v>
+        <v>0.7823</v>
       </c>
       <c r="E11" t="n">
-        <v>3.0082</v>
+        <v>3.047</v>
       </c>
       <c r="F11" t="n">
-        <v>2.7291</v>
+        <v>2.8052</v>
       </c>
       <c r="G11" t="n">
-        <v>0.2791</v>
+        <v>0.2418</v>
       </c>
       <c r="H11" t="n">
-        <v>4.1102</v>
+        <v>4.0893</v>
       </c>
       <c r="I11" t="n">
-        <v>2.2195</v>
+        <v>2.296</v>
       </c>
       <c r="J11" t="n">
-        <v>0.2791</v>
+        <v>0.2418</v>
       </c>
       <c r="K11" t="n">
         <v>160</v>
@@ -943,7 +943,7 @@
         <v>54</v>
       </c>
       <c r="M11" t="n">
-        <v>2.4986</v>
+        <v>2.5378</v>
       </c>
       <c r="N11" t="n">
         <v>214</v>
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.9213</v>
+        <v>2.9669</v>
       </c>
       <c r="C12" t="n">
-        <v>1.2619</v>
+        <v>1.2816</v>
       </c>
       <c r="D12" t="n">
-        <v>0.7056</v>
+        <v>0.7458</v>
       </c>
       <c r="E12" t="n">
-        <v>2.9213</v>
+        <v>2.9669</v>
       </c>
       <c r="F12" t="n">
-        <v>2.2705</v>
+        <v>2.3626</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6508</v>
+        <v>0.6042999999999999</v>
       </c>
       <c r="H12" t="n">
-        <v>2.5969</v>
+        <v>2.4277</v>
       </c>
       <c r="I12" t="n">
-        <v>1.4023</v>
+        <v>1.3631</v>
       </c>
       <c r="J12" t="n">
-        <v>0.6508</v>
+        <v>0.6042999999999999</v>
       </c>
       <c r="K12" t="n">
         <v>248</v>
@@ -989,7 +989,7 @@
         <v>53</v>
       </c>
       <c r="M12" t="n">
-        <v>2.0531</v>
+        <v>1.9674</v>
       </c>
       <c r="N12" t="n">
         <v>301</v>
@@ -1002,31 +1002,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.8717</v>
+        <v>2.7637</v>
       </c>
       <c r="C13" t="n">
-        <v>1.2405</v>
+        <v>1.1938</v>
       </c>
       <c r="D13" t="n">
-        <v>0.6831</v>
+        <v>0.6532</v>
       </c>
       <c r="E13" t="n">
-        <v>2.8717</v>
+        <v>2.7637</v>
       </c>
       <c r="F13" t="n">
-        <v>3.3416</v>
+        <v>3.205</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.4699</v>
+        <v>-0.4413</v>
       </c>
       <c r="H13" t="n">
-        <v>6.1308</v>
+        <v>5.5903</v>
       </c>
       <c r="I13" t="n">
-        <v>3.3106</v>
+        <v>3.1388</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.4699</v>
+        <v>-0.4413</v>
       </c>
       <c r="K13" t="n">
         <v>248</v>
@@ -1035,7 +1035,7 @@
         <v>53</v>
       </c>
       <c r="M13" t="n">
-        <v>2.8407</v>
+        <v>2.6975</v>
       </c>
       <c r="N13" t="n">
         <v>301</v>
@@ -1044,93 +1044,93 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>NiKo</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.5262</v>
+        <v>2.4484</v>
       </c>
       <c r="C14" t="n">
-        <v>1.0912</v>
+        <v>1.0576</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5258</v>
+        <v>0.5096000000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>2.5262</v>
+        <v>2.4484</v>
       </c>
       <c r="F14" t="n">
-        <v>2.5262</v>
+        <v>2.9023</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>-0.4539</v>
       </c>
       <c r="H14" t="n">
-        <v>2.8042</v>
+        <v>4.4539</v>
       </c>
       <c r="I14" t="n">
-        <v>2.8042</v>
+        <v>2.5007</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>-0.4539</v>
       </c>
       <c r="K14" t="n">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="M14" t="n">
-        <v>2.8042</v>
+        <v>2.0468</v>
       </c>
       <c r="N14" t="n">
-        <v>148</v>
+        <v>255</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>NiKo</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.4808</v>
+        <v>2.4185</v>
       </c>
       <c r="C15" t="n">
-        <v>1.0716</v>
+        <v>1.0447</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5051</v>
+        <v>0.496</v>
       </c>
       <c r="E15" t="n">
-        <v>2.4808</v>
+        <v>2.4185</v>
       </c>
       <c r="F15" t="n">
-        <v>2.9594</v>
+        <v>2.4185</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.4786</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>4.8701</v>
+        <v>2.5924</v>
       </c>
       <c r="I15" t="n">
-        <v>2.6298</v>
+        <v>2.5924</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.4786</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="L15" t="n">
-        <v>103</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>2.1512</v>
+        <v>2.5924</v>
       </c>
       <c r="N15" t="n">
-        <v>255</v>
+        <v>148</v>
       </c>
     </row>
     <row r="16">
@@ -1140,31 +1140,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.2489</v>
+        <v>2.3001</v>
       </c>
       <c r="C16" t="n">
-        <v>0.9714</v>
+        <v>0.9936</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3995</v>
+        <v>0.442</v>
       </c>
       <c r="E16" t="n">
-        <v>2.2489</v>
+        <v>2.3001</v>
       </c>
       <c r="F16" t="n">
-        <v>2.7426</v>
+        <v>2.7798</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.4937</v>
+        <v>-0.4797</v>
       </c>
       <c r="H16" t="n">
-        <v>4.1547</v>
+        <v>3.994</v>
       </c>
       <c r="I16" t="n">
-        <v>2.2435</v>
+        <v>2.2425</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.4937</v>
+        <v>-0.4797</v>
       </c>
       <c r="K16" t="n">
         <v>248</v>
@@ -1173,7 +1173,7 @@
         <v>53</v>
       </c>
       <c r="M16" t="n">
-        <v>1.7498</v>
+        <v>1.7628</v>
       </c>
       <c r="N16" t="n">
         <v>301</v>
@@ -1182,93 +1182,93 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>olofmeister</t>
+          <t>Edward</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.6245</v>
+        <v>1.5571</v>
       </c>
       <c r="C17" t="n">
-        <v>0.7017</v>
+        <v>0.6726</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1153</v>
+        <v>0.1035</v>
       </c>
       <c r="E17" t="n">
-        <v>1.6245</v>
+        <v>1.5571</v>
       </c>
       <c r="F17" t="n">
-        <v>1.6245</v>
+        <v>1.9381</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>-0.381</v>
       </c>
       <c r="H17" t="n">
-        <v>1.6245</v>
+        <v>1.9381</v>
       </c>
       <c r="I17" t="n">
-        <v>1.6245</v>
+        <v>1.0882</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>-0.381</v>
       </c>
       <c r="K17" t="n">
-        <v>148</v>
+        <v>160</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="M17" t="n">
-        <v>1.6245</v>
+        <v>0.7072000000000001</v>
       </c>
       <c r="N17" t="n">
-        <v>148</v>
+        <v>214</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Edward</t>
+          <t>fer</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.6158</v>
+        <v>1.491</v>
       </c>
       <c r="C18" t="n">
-        <v>0.698</v>
+        <v>0.6441</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1113</v>
+        <v>0.07340000000000001</v>
       </c>
       <c r="E18" t="n">
-        <v>1.6158</v>
+        <v>1.491</v>
       </c>
       <c r="F18" t="n">
-        <v>2.0319</v>
+        <v>1.491</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.4161</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>2.0319</v>
+        <v>1.491</v>
       </c>
       <c r="I18" t="n">
-        <v>1.0972</v>
+        <v>1.491</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.4161</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="L18" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>0.6810999999999999</v>
+        <v>1.491</v>
       </c>
       <c r="N18" t="n">
-        <v>214</v>
+        <v>158</v>
       </c>
     </row>
     <row r="19">
@@ -1278,28 +1278,28 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.5992</v>
+        <v>1.4827</v>
       </c>
       <c r="C19" t="n">
-        <v>0.6908</v>
+        <v>0.6405</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1038</v>
+        <v>0.0697</v>
       </c>
       <c r="E19" t="n">
-        <v>1.5992</v>
+        <v>1.4827</v>
       </c>
       <c r="F19" t="n">
-        <v>1.5992</v>
+        <v>1.4827</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>1.5992</v>
+        <v>1.4827</v>
       </c>
       <c r="I19" t="n">
-        <v>1.5992</v>
+        <v>1.4827</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1311,7 +1311,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1.5992</v>
+        <v>1.4827</v>
       </c>
       <c r="N19" t="n">
         <v>228</v>
@@ -1320,47 +1320,47 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>fer</t>
+          <t>olofmeister</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.5188</v>
+        <v>1.4054</v>
       </c>
       <c r="C20" t="n">
-        <v>0.6561</v>
+        <v>0.6071</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0672</v>
+        <v>0.0344</v>
       </c>
       <c r="E20" t="n">
-        <v>1.5188</v>
+        <v>1.4054</v>
       </c>
       <c r="F20" t="n">
-        <v>1.5188</v>
+        <v>1.4054</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>1.5188</v>
+        <v>1.4054</v>
       </c>
       <c r="I20" t="n">
-        <v>1.5188</v>
+        <v>1.4054</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1.5188</v>
+        <v>1.4054</v>
       </c>
       <c r="N20" t="n">
-        <v>158</v>
+        <v>148</v>
       </c>
     </row>
     <row r="21">
@@ -1370,28 +1370,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.2352</v>
+        <v>1.2214</v>
       </c>
       <c r="C21" t="n">
-        <v>0.5336</v>
+        <v>0.5276</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.0619</v>
+        <v>-0.0494</v>
       </c>
       <c r="E21" t="n">
-        <v>1.2352</v>
+        <v>1.2214</v>
       </c>
       <c r="F21" t="n">
-        <v>1.2352</v>
+        <v>1.2214</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>1.2352</v>
+        <v>1.2214</v>
       </c>
       <c r="I21" t="n">
-        <v>1.2352</v>
+        <v>1.2214</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1.2352</v>
+        <v>1.2214</v>
       </c>
       <c r="N21" t="n">
         <v>158</v>
@@ -1416,28 +1416,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.0486</v>
+        <v>1.0272</v>
       </c>
       <c r="C22" t="n">
-        <v>0.453</v>
+        <v>0.4437</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1469</v>
+        <v>-0.1378</v>
       </c>
       <c r="E22" t="n">
-        <v>1.0486</v>
+        <v>1.0272</v>
       </c>
       <c r="F22" t="n">
-        <v>1.0486</v>
+        <v>1.0272</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>1.0486</v>
+        <v>1.0272</v>
       </c>
       <c r="I22" t="n">
-        <v>1.0486</v>
+        <v>1.0272</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1.0486</v>
+        <v>1.0272</v>
       </c>
       <c r="N22" t="n">
         <v>158</v>
@@ -1462,28 +1462,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.9233</v>
+        <v>0.8183</v>
       </c>
       <c r="C23" t="n">
-        <v>0.3988</v>
+        <v>0.3535</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.2039</v>
+        <v>-0.233</v>
       </c>
       <c r="E23" t="n">
-        <v>0.9233</v>
+        <v>0.8183</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9233</v>
+        <v>0.8183</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.9233</v>
+        <v>0.8183</v>
       </c>
       <c r="I23" t="n">
-        <v>0.9233</v>
+        <v>0.8183</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.9233</v>
+        <v>0.8183</v>
       </c>
       <c r="N23" t="n">
         <v>116</v>
@@ -1508,28 +1508,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.6078</v>
+        <v>0.5279</v>
       </c>
       <c r="C24" t="n">
-        <v>0.2625</v>
+        <v>0.228</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.3475</v>
+        <v>-0.3653</v>
       </c>
       <c r="E24" t="n">
-        <v>0.6078</v>
+        <v>0.5279</v>
       </c>
       <c r="F24" t="n">
-        <v>0.6078</v>
+        <v>0.5279</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.6078</v>
+        <v>0.5279</v>
       </c>
       <c r="I24" t="n">
-        <v>0.6078</v>
+        <v>0.5279</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.6078</v>
+        <v>0.5279</v>
       </c>
       <c r="N24" t="n">
         <v>228</v>
@@ -1550,47 +1550,47 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>flusha</t>
+          <t>Stewie2K</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.2101</v>
+        <v>0.1824</v>
       </c>
       <c r="C25" t="n">
-        <v>0.09080000000000001</v>
+        <v>0.0788</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.5286</v>
+        <v>-0.5227000000000001</v>
       </c>
       <c r="E25" t="n">
-        <v>0.2101</v>
+        <v>0.1824</v>
       </c>
       <c r="F25" t="n">
-        <v>0.2101</v>
+        <v>0.1824</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.2101</v>
+        <v>0.1824</v>
       </c>
       <c r="I25" t="n">
-        <v>0.2101</v>
+        <v>0.1824</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>228</v>
+        <v>158</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.2101</v>
+        <v>0.1824</v>
       </c>
       <c r="N25" t="n">
-        <v>228</v>
+        <v>158</v>
       </c>
     </row>
     <row r="26">
@@ -1600,28 +1600,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.21</v>
+        <v>0.1399</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0907</v>
+        <v>0.0604</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.5286</v>
+        <v>-0.5421</v>
       </c>
       <c r="E26" t="n">
-        <v>0.21</v>
+        <v>0.1399</v>
       </c>
       <c r="F26" t="n">
-        <v>0.21</v>
+        <v>0.1399</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.21</v>
+        <v>0.1399</v>
       </c>
       <c r="I26" t="n">
-        <v>0.21</v>
+        <v>0.1399</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.21</v>
+        <v>0.1399</v>
       </c>
       <c r="N26" t="n">
         <v>228</v>
@@ -1642,47 +1642,47 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Stewie2K</t>
+          <t>flusha</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.1396</v>
+        <v>0.1383</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0603</v>
+        <v>0.0597</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.5607</v>
+        <v>-0.5427999999999999</v>
       </c>
       <c r="E27" t="n">
-        <v>0.1396</v>
+        <v>0.1383</v>
       </c>
       <c r="F27" t="n">
-        <v>0.1396</v>
+        <v>0.1383</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.1396</v>
+        <v>0.1383</v>
       </c>
       <c r="I27" t="n">
-        <v>0.1396</v>
+        <v>0.1383</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>158</v>
+        <v>228</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.1396</v>
+        <v>0.1383</v>
       </c>
       <c r="N27" t="n">
-        <v>158</v>
+        <v>228</v>
       </c>
     </row>
     <row r="28">
@@ -1692,28 +1692,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.0011</v>
+        <v>-0.0456</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.0005</v>
+        <v>-0.0197</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.6247</v>
+        <v>-0.6266</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.0011</v>
+        <v>-0.0456</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.0011</v>
+        <v>-0.0456</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.0011</v>
+        <v>-0.0456</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.0011</v>
+        <v>-0.0456</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.0011</v>
+        <v>-0.0456</v>
       </c>
       <c r="N28" t="n">
         <v>148</v>
@@ -1738,31 +1738,31 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.1124</v>
+        <v>-0.1795</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.0486</v>
+        <v>-0.0775</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.6754</v>
+        <v>-0.6876</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.1124</v>
+        <v>-0.1795</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.1539</v>
+        <v>-0.184</v>
       </c>
       <c r="G29" t="n">
-        <v>0.0415</v>
+        <v>0.0045</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.1539</v>
+        <v>-0.184</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.08309999999999999</v>
+        <v>-0.1033</v>
       </c>
       <c r="J29" t="n">
-        <v>0.0415</v>
+        <v>0.0045</v>
       </c>
       <c r="K29" t="n">
         <v>160</v>
@@ -1771,7 +1771,7 @@
         <v>54</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.04159999999999999</v>
+        <v>-0.0988</v>
       </c>
       <c r="N29" t="n">
         <v>214</v>
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.2495</v>
+        <v>-0.2592</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.1078</v>
+        <v>-0.112</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.7378</v>
+        <v>-0.7239</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.2495</v>
+        <v>-0.2592</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.2495</v>
+        <v>-0.2592</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.2495</v>
+        <v>-0.2592</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.2495</v>
+        <v>-0.2592</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.2495</v>
+        <v>-0.2592</v>
       </c>
       <c r="N30" t="n">
         <v>116</v>
@@ -1830,31 +1830,31 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.2945</v>
+        <v>-0.4151</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.1272</v>
+        <v>-0.1793</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.7583</v>
+        <v>-0.7949000000000001</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.2945</v>
+        <v>-0.4151</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.1887</v>
+        <v>-0.3046</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.1058</v>
+        <v>-0.1105</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.1887</v>
+        <v>-0.3046</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.1019</v>
+        <v>-0.171</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.1058</v>
+        <v>-0.1105</v>
       </c>
       <c r="K31" t="n">
         <v>248</v>
@@ -1863,7 +1863,7 @@
         <v>53</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.2077</v>
+        <v>-0.2815</v>
       </c>
       <c r="N31" t="n">
         <v>301</v>
@@ -1872,185 +1872,185 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>RUSH</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.4468</v>
+        <v>-0.4823</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.193</v>
+        <v>-0.2083</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.8276</v>
+        <v>-0.8255</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.4468</v>
+        <v>-0.4823</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.4468</v>
+        <v>-0.4823</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.4468</v>
+        <v>-0.4823</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.4468</v>
+        <v>-0.4823</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>116</v>
+        <v>148</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.4468</v>
+        <v>-0.4823</v>
       </c>
       <c r="N32" t="n">
-        <v>116</v>
+        <v>148</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>chrisJ</t>
+          <t>RUSH</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.4918</v>
+        <v>-0.5341</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.2124</v>
+        <v>-0.2307</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.8481</v>
+        <v>-0.8491</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.4918</v>
+        <v>-0.5341</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.2878</v>
+        <v>-0.5341</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.204</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.2878</v>
+        <v>-0.5341</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.1554</v>
+        <v>-0.5341</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.204</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>248</v>
+        <v>116</v>
       </c>
       <c r="L33" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.3594</v>
+        <v>-0.5341</v>
       </c>
       <c r="N33" t="n">
-        <v>301</v>
+        <v>116</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>Xizt</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.5117</v>
+        <v>-0.6136</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.221</v>
+        <v>-0.2651</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.8571</v>
+        <v>-0.8853</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.5117</v>
+        <v>-0.6136</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.5117</v>
+        <v>-0.6136</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.5117</v>
+        <v>-0.6136</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.5117</v>
+        <v>-0.6136</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>148</v>
+        <v>228</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.5117</v>
+        <v>-0.6136</v>
       </c>
       <c r="N34" t="n">
-        <v>148</v>
+        <v>228</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Xizt</t>
+          <t>chrisJ</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.613</v>
+        <v>-0.621</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.2648</v>
+        <v>-0.2682</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.9033</v>
+        <v>-0.8887</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.613</v>
+        <v>-0.621</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.613</v>
+        <v>-0.446</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>-0.175</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.613</v>
+        <v>-0.446</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.613</v>
+        <v>-0.2504</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>-0.175</v>
       </c>
       <c r="K35" t="n">
-        <v>228</v>
+        <v>248</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.613</v>
+        <v>-0.4254</v>
       </c>
       <c r="N35" t="n">
-        <v>228</v>
+        <v>301</v>
       </c>
     </row>
     <row r="36">
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.8216</v>
+        <v>-0.7822</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.3549</v>
+        <v>-0.3379</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9982</v>
+        <v>-0.9621</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.8216</v>
+        <v>-0.7822</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.8216</v>
+        <v>-0.7822</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.8216</v>
+        <v>-0.7822</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.8216</v>
+        <v>-0.7822</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.8216</v>
+        <v>-0.7822</v>
       </c>
       <c r="N36" t="n">
         <v>158</v>
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.8538</v>
+        <v>-0.7955</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.3688</v>
+        <v>-0.3436</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.0129</v>
+        <v>-0.9681999999999999</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.8538</v>
+        <v>-0.7955</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.8538</v>
+        <v>-0.7955</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.8538</v>
+        <v>-0.7955</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.8538</v>
+        <v>-0.7955</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.8538</v>
+        <v>-0.7955</v>
       </c>
       <c r="N37" t="n">
         <v>148</v>
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.0668</v>
+        <v>-1.0203</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.4608</v>
+        <v>-0.4407</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.1098</v>
+        <v>-1.0706</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.0668</v>
+        <v>-1.0203</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.0668</v>
+        <v>-1.0203</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.0668</v>
+        <v>-1.0203</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.0668</v>
+        <v>-1.0203</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.0668</v>
+        <v>-1.0203</v>
       </c>
       <c r="N38" t="n">
         <v>116</v>
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.1675</v>
+        <v>-1.115</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.5043</v>
+        <v>-0.4816</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.1557</v>
+        <v>-1.1137</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.1675</v>
+        <v>-1.115</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.1675</v>
+        <v>-1.115</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.1675</v>
+        <v>-1.115</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.1675</v>
+        <v>-1.115</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.1675</v>
+        <v>-1.115</v>
       </c>
       <c r="N39" t="n">
         <v>116</v>
@@ -2244,31 +2244,31 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.6795</v>
+        <v>-1.5601</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.7255</v>
+        <v>-0.6739000000000001</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.3887</v>
+        <v>-1.3165</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.6795</v>
+        <v>-1.5601</v>
       </c>
       <c r="F40" t="n">
-        <v>-0.8069</v>
+        <v>-0.7457</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.8726</v>
+        <v>-0.8144</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.8069</v>
+        <v>-0.7457</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.4357</v>
+        <v>-0.4187</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.8726</v>
+        <v>-0.8144</v>
       </c>
       <c r="K40" t="n">
         <v>110</v>
@@ -2277,7 +2277,7 @@
         <v>102</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.3083</v>
+        <v>-1.2331</v>
       </c>
       <c r="N40" t="n">
         <v>212</v>
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-3.7721</v>
+        <v>-3.7355</v>
       </c>
       <c r="C41" t="n">
-        <v>-1.6294</v>
+        <v>-1.6136</v>
       </c>
       <c r="D41" t="n">
-        <v>-2.3413</v>
+        <v>-2.3075</v>
       </c>
       <c r="E41" t="n">
-        <v>-3.7721</v>
+        <v>-3.7355</v>
       </c>
       <c r="F41" t="n">
-        <v>-3.2886</v>
+        <v>-3.2921</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.4835</v>
+        <v>-0.4434</v>
       </c>
       <c r="H41" t="n">
-        <v>-3.2886</v>
+        <v>-3.2921</v>
       </c>
       <c r="I41" t="n">
-        <v>-1.7758</v>
+        <v>-1.8484</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.4835</v>
+        <v>-0.4434</v>
       </c>
       <c r="K41" t="n">
         <v>152</v>
@@ -2323,7 +2323,7 @@
         <v>103</v>
       </c>
       <c r="M41" t="n">
-        <v>-2.2593</v>
+        <v>-2.2918</v>
       </c>
       <c r="N41" t="n">
         <v>255</v>
@@ -2429,10 +2429,10 @@
         <v>1.8</v>
       </c>
       <c r="I2" t="n">
-        <v>1.5857</v>
+        <v>1.6132</v>
       </c>
       <c r="J2" t="n">
-        <v>33.2997</v>
+        <v>33.8772</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.78</v>
       </c>
       <c r="I3" t="n">
-        <v>1.5584</v>
+        <v>1.5872</v>
       </c>
       <c r="J3" t="n">
-        <v>32.7264</v>
+        <v>33.3312</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>1.29</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7065</v>
+        <v>0.6866</v>
       </c>
       <c r="J4" t="n">
-        <v>14.8365</v>
+        <v>14.4186</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>1.18</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4718</v>
+        <v>0.4417</v>
       </c>
       <c r="J5" t="n">
-        <v>9.9078</v>
+        <v>9.275700000000001</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.98</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1681</v>
+        <v>-0.1449</v>
       </c>
       <c r="J6" t="n">
-        <v>-3.5301</v>
+        <v>-3.0429</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>0.85</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1495</v>
+        <v>-0.1306</v>
       </c>
       <c r="J7" t="n">
-        <v>-3.1395</v>
+        <v>-2.7426</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>0.64</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3622</v>
+        <v>-0.3526</v>
       </c>
       <c r="J8" t="n">
-        <v>-7.6062</v>
+        <v>-7.4046</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>0.6</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3958</v>
+        <v>-0.3869</v>
       </c>
       <c r="J9" t="n">
-        <v>-8.3118</v>
+        <v>-8.1249</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.4304</v>
+        <v>-0.4229</v>
       </c>
       <c r="J10" t="n">
-        <v>-9.038399999999999</v>
+        <v>-8.8809</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.45</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.5271</v>
+        <v>-0.5283</v>
       </c>
       <c r="J11" t="n">
-        <v>-11.0691</v>
+        <v>-11.0943</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.42</v>
       </c>
       <c r="I12" t="n">
-        <v>1.0164</v>
+        <v>1.0102</v>
       </c>
       <c r="J12" t="n">
-        <v>28.4592</v>
+        <v>28.2856</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.07</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2439</v>
+        <v>0.2112</v>
       </c>
       <c r="J13" t="n">
-        <v>6.8292</v>
+        <v>5.9136</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>1.05</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1854</v>
+        <v>0.1568</v>
       </c>
       <c r="J14" t="n">
-        <v>5.1912</v>
+        <v>4.3904</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>1.05</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1854</v>
+        <v>0.1568</v>
       </c>
       <c r="J15" t="n">
-        <v>5.1912</v>
+        <v>4.3904</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.2505</v>
+        <v>-0.2117</v>
       </c>
       <c r="J16" t="n">
-        <v>-7.014</v>
+        <v>-5.9276</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1</v>
       </c>
       <c r="I17" t="n">
-        <v>0.0081</v>
+        <v>0.0049</v>
       </c>
       <c r="J17" t="n">
-        <v>0.2268</v>
+        <v>0.1372</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>0.99</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.021</v>
+        <v>-0.0156</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.588</v>
+        <v>-0.4368</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>0.96</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.0687</v>
+        <v>-0.0562</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.9236</v>
+        <v>-1.5736</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.95</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.0822</v>
+        <v>-0.0682</v>
       </c>
       <c r="J20" t="n">
-        <v>-2.3016</v>
+        <v>-1.9096</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.78</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.2661</v>
+        <v>-0.2466</v>
       </c>
       <c r="J21" t="n">
-        <v>-7.4508</v>
+        <v>-6.9048</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.29</v>
       </c>
       <c r="I22" t="n">
-        <v>0.5304</v>
+        <v>0.5006</v>
       </c>
       <c r="J22" t="n">
-        <v>15.3816</v>
+        <v>14.5174</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.17</v>
       </c>
       <c r="I23" t="n">
-        <v>0.3674</v>
+        <v>0.3137</v>
       </c>
       <c r="J23" t="n">
-        <v>10.6546</v>
+        <v>9.097300000000001</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>1.17</v>
       </c>
       <c r="I24" t="n">
-        <v>0.3674</v>
+        <v>0.3137</v>
       </c>
       <c r="J24" t="n">
-        <v>10.6546</v>
+        <v>9.097300000000001</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.97</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.064</v>
+        <v>-0.0501</v>
       </c>
       <c r="J25" t="n">
-        <v>-1.856</v>
+        <v>-1.4529</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.78</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.2787</v>
+        <v>-0.2602</v>
       </c>
       <c r="J26" t="n">
-        <v>-8.0823</v>
+        <v>-7.5458</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.34</v>
       </c>
       <c r="I27" t="n">
-        <v>0.7492</v>
+        <v>0.7332</v>
       </c>
       <c r="J27" t="n">
-        <v>21.7268</v>
+        <v>21.2628</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.27</v>
       </c>
       <c r="I28" t="n">
-        <v>0.6417</v>
+        <v>0.6277</v>
       </c>
       <c r="J28" t="n">
-        <v>18.6093</v>
+        <v>18.2033</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.2</v>
       </c>
       <c r="I29" t="n">
-        <v>0.529</v>
+        <v>0.5171</v>
       </c>
       <c r="J29" t="n">
-        <v>15.341</v>
+        <v>14.9959</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.91</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.3348</v>
+        <v>-0.2927</v>
       </c>
       <c r="J30" t="n">
-        <v>-9.709199999999999</v>
+        <v>-8.488300000000001</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.78</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.6532</v>
+        <v>-0.6186</v>
       </c>
       <c r="J31" t="n">
-        <v>-18.9428</v>
+        <v>-17.9394</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.13</v>
       </c>
       <c r="I32" t="n">
-        <v>0.3431</v>
+        <v>0.2919</v>
       </c>
       <c r="J32" t="n">
-        <v>8.577500000000001</v>
+        <v>7.2975</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>0.9</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.1374</v>
+        <v>-0.1208</v>
       </c>
       <c r="J33" t="n">
-        <v>-3.435</v>
+        <v>-3.02</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>0.83</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.2103</v>
+        <v>-0.1911</v>
       </c>
       <c r="J34" t="n">
-        <v>-5.2575</v>
+        <v>-4.7775</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.78</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.2596</v>
+        <v>-0.2405</v>
       </c>
       <c r="J35" t="n">
-        <v>-6.49</v>
+        <v>-6.0125</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.71</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.3259</v>
+        <v>-0.3092</v>
       </c>
       <c r="J36" t="n">
-        <v>-8.147500000000001</v>
+        <v>-7.73</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.58</v>
       </c>
       <c r="I37" t="n">
-        <v>1.042</v>
+        <v>1.0311</v>
       </c>
       <c r="J37" t="n">
-        <v>26.05</v>
+        <v>25.7775</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.52</v>
       </c>
       <c r="I38" t="n">
-        <v>0.9629</v>
+        <v>0.9500999999999999</v>
       </c>
       <c r="J38" t="n">
-        <v>24.0725</v>
+        <v>23.7525</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.34</v>
       </c>
       <c r="I39" t="n">
-        <v>0.7163</v>
+        <v>0.7055</v>
       </c>
       <c r="J39" t="n">
-        <v>17.9075</v>
+        <v>17.6375</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>1.31</v>
       </c>
       <c r="I40" t="n">
-        <v>0.6742</v>
+        <v>0.6649</v>
       </c>
       <c r="J40" t="n">
-        <v>16.855</v>
+        <v>16.6225</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.6199</v>
+        <v>-0.589</v>
       </c>
       <c r="J41" t="n">
-        <v>-15.4975</v>
+        <v>-14.725</v>
       </c>
     </row>
     <row r="42">
@@ -4069,10 +4069,10 @@
         <v>1.08</v>
       </c>
       <c r="I43" t="n">
-        <v>0.2746</v>
+        <v>0.2387</v>
       </c>
       <c r="J43" t="n">
-        <v>7.4142</v>
+        <v>6.4449</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.02</v>
       </c>
       <c r="I44" t="n">
-        <v>0.0893</v>
+        <v>0.0706</v>
       </c>
       <c r="J44" t="n">
-        <v>2.4111</v>
+        <v>1.9062</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.96</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.1826</v>
+        <v>-0.1485</v>
       </c>
       <c r="J45" t="n">
-        <v>-4.9302</v>
+        <v>-4.0095</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.7</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.8239</v>
+        <v>-0.8025</v>
       </c>
       <c r="J46" t="n">
-        <v>-22.2453</v>
+        <v>-21.6675</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.02</v>
       </c>
       <c r="I47" t="n">
-        <v>0.083</v>
+        <v>0.0592</v>
       </c>
       <c r="J47" t="n">
-        <v>2.241</v>
+        <v>1.5984</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>0.98</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.0388</v>
+        <v>-0.0302</v>
       </c>
       <c r="J48" t="n">
-        <v>-1.0476</v>
+        <v>-0.8154</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.0949</v>
+        <v>-0.0796</v>
       </c>
       <c r="J49" t="n">
-        <v>-2.5623</v>
+        <v>-2.1492</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.89</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.1528</v>
+        <v>-0.1338</v>
       </c>
       <c r="J50" t="n">
-        <v>-4.1256</v>
+        <v>-3.6126</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.85</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.1957</v>
+        <v>-0.1755</v>
       </c>
       <c r="J51" t="n">
-        <v>-5.2839</v>
+        <v>-4.7385</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.41</v>
       </c>
       <c r="I52" t="n">
-        <v>0.8408</v>
+        <v>0.8249</v>
       </c>
       <c r="J52" t="n">
-        <v>21.8608</v>
+        <v>21.4474</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.28</v>
       </c>
       <c r="I53" t="n">
-        <v>0.648</v>
+        <v>0.6347</v>
       </c>
       <c r="J53" t="n">
-        <v>16.848</v>
+        <v>16.5022</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>1.19</v>
       </c>
       <c r="I54" t="n">
-        <v>0.5054999999999999</v>
+        <v>0.4909</v>
       </c>
       <c r="J54" t="n">
-        <v>13.143</v>
+        <v>12.7634</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>1.12</v>
       </c>
       <c r="I55" t="n">
-        <v>0.3682</v>
+        <v>0.3324</v>
       </c>
       <c r="J55" t="n">
-        <v>9.5732</v>
+        <v>8.6424</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.76</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.7073</v>
+        <v>-0.6778</v>
       </c>
       <c r="J56" t="n">
-        <v>-18.3898</v>
+        <v>-17.6228</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.29</v>
       </c>
       <c r="I57" t="n">
-        <v>0.5678</v>
+        <v>0.5451</v>
       </c>
       <c r="J57" t="n">
-        <v>14.7628</v>
+        <v>14.1726</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.02</v>
       </c>
       <c r="I58" t="n">
-        <v>0.08989999999999999</v>
+        <v>0.065</v>
       </c>
       <c r="J58" t="n">
-        <v>2.3374</v>
+        <v>1.69</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>0.97</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.0512</v>
+        <v>-0.0412</v>
       </c>
       <c r="J59" t="n">
-        <v>-1.3312</v>
+        <v>-1.0712</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.66</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.375</v>
+        <v>-0.3617</v>
       </c>
       <c r="J60" t="n">
-        <v>-9.75</v>
+        <v>-9.404199999999999</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.57</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.4549</v>
+        <v>-0.4495</v>
       </c>
       <c r="J61" t="n">
-        <v>-11.8274</v>
+        <v>-11.687</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.45</v>
       </c>
       <c r="I62" t="n">
-        <v>0.6232</v>
+        <v>0.6511</v>
       </c>
       <c r="J62" t="n">
-        <v>18.0728</v>
+        <v>18.8819</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.34</v>
       </c>
       <c r="I63" t="n">
-        <v>0.4969</v>
+        <v>0.5053</v>
       </c>
       <c r="J63" t="n">
-        <v>14.4101</v>
+        <v>14.6537</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.09</v>
       </c>
       <c r="I64" t="n">
-        <v>0.1729</v>
+        <v>0.1586</v>
       </c>
       <c r="J64" t="n">
-        <v>5.0141</v>
+        <v>4.5994</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>0.95</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.0939</v>
+        <v>-0.0771</v>
       </c>
       <c r="J65" t="n">
-        <v>-2.7231</v>
+        <v>-2.2359</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.66</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.3919</v>
+        <v>-0.382</v>
       </c>
       <c r="J66" t="n">
-        <v>-11.3651</v>
+        <v>-11.078</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.14</v>
       </c>
       <c r="I67" t="n">
-        <v>0.2408</v>
+        <v>0.1913</v>
       </c>
       <c r="J67" t="n">
-        <v>6.9832</v>
+        <v>5.5477</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.11</v>
       </c>
       <c r="I68" t="n">
-        <v>0.1994</v>
+        <v>0.1552</v>
       </c>
       <c r="J68" t="n">
-        <v>5.7826</v>
+        <v>4.5008</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>1.07</v>
       </c>
       <c r="I69" t="n">
-        <v>0.1401</v>
+        <v>0.1051</v>
       </c>
       <c r="J69" t="n">
-        <v>4.0629</v>
+        <v>3.0479</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.92</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.1253</v>
+        <v>-0.1065</v>
       </c>
       <c r="J70" t="n">
-        <v>-3.6337</v>
+        <v>-3.0885</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.86</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.1927</v>
+        <v>-0.172</v>
       </c>
       <c r="J71" t="n">
-        <v>-5.5883</v>
+        <v>-4.988</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.38</v>
       </c>
       <c r="I72" t="n">
-        <v>0.9223</v>
+        <v>0.9068000000000001</v>
       </c>
       <c r="J72" t="n">
-        <v>27.669</v>
+        <v>27.204</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.37</v>
       </c>
       <c r="I73" t="n">
-        <v>0.9029</v>
+        <v>0.8853</v>
       </c>
       <c r="J73" t="n">
-        <v>27.087</v>
+        <v>26.559</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1.22</v>
       </c>
       <c r="I74" t="n">
-        <v>0.594</v>
+        <v>0.5585</v>
       </c>
       <c r="J74" t="n">
-        <v>17.82</v>
+        <v>16.755</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>1.13</v>
       </c>
       <c r="I75" t="n">
-        <v>0.3921</v>
+        <v>0.3559</v>
       </c>
       <c r="J75" t="n">
-        <v>11.763</v>
+        <v>10.677</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.68</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.88</v>
+        <v>-0.8665</v>
       </c>
       <c r="J76" t="n">
-        <v>-26.4</v>
+        <v>-25.995</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.05</v>
       </c>
       <c r="I77" t="n">
-        <v>0.1707</v>
+        <v>0.1333</v>
       </c>
       <c r="J77" t="n">
-        <v>5.121</v>
+        <v>3.999</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>0.91</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.1273</v>
+        <v>-0.1109</v>
       </c>
       <c r="J78" t="n">
-        <v>-3.819</v>
+        <v>-3.327</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>0.88</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.16</v>
+        <v>-0.1419</v>
       </c>
       <c r="J79" t="n">
-        <v>-4.8</v>
+        <v>-4.257</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.84</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.2015</v>
+        <v>-0.1821</v>
       </c>
       <c r="J80" t="n">
-        <v>-6.045</v>
+        <v>-5.463</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.75</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.29</v>
+        <v>-0.2716</v>
       </c>
       <c r="J81" t="n">
-        <v>-8.699999999999999</v>
+        <v>-8.148</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.7</v>
       </c>
       <c r="I82" t="n">
-        <v>1.3758</v>
+        <v>1.402</v>
       </c>
       <c r="J82" t="n">
-        <v>34.395</v>
+        <v>35.05</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.28</v>
       </c>
       <c r="I83" t="n">
-        <v>0.7151999999999999</v>
+        <v>0.6855</v>
       </c>
       <c r="J83" t="n">
-        <v>17.88</v>
+        <v>17.1375</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.16</v>
       </c>
       <c r="I84" t="n">
-        <v>0.4589</v>
+        <v>0.4234</v>
       </c>
       <c r="J84" t="n">
-        <v>11.4725</v>
+        <v>10.585</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>1.06</v>
       </c>
       <c r="I85" t="n">
-        <v>0.2024</v>
+        <v>0.174</v>
       </c>
       <c r="J85" t="n">
-        <v>5.06</v>
+        <v>4.35</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.72</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.7998</v>
+        <v>-0.779</v>
       </c>
       <c r="J86" t="n">
-        <v>-19.995</v>
+        <v>-19.475</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.16</v>
       </c>
       <c r="I87" t="n">
-        <v>0.3938</v>
+        <v>0.3399</v>
       </c>
       <c r="J87" t="n">
-        <v>9.845000000000001</v>
+        <v>8.4975</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.12</v>
       </c>
       <c r="I88" t="n">
-        <v>0.3181</v>
+        <v>0.2675</v>
       </c>
       <c r="J88" t="n">
-        <v>7.9525</v>
+        <v>6.6875</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>0.89</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.1496</v>
+        <v>-0.1319</v>
       </c>
       <c r="J89" t="n">
-        <v>-3.74</v>
+        <v>-3.2975</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.67</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.3645</v>
+        <v>-0.3503</v>
       </c>
       <c r="J90" t="n">
-        <v>-9.112500000000001</v>
+        <v>-8.7575</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.6</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.4272</v>
+        <v>-0.4186</v>
       </c>
       <c r="J91" t="n">
-        <v>-10.68</v>
+        <v>-10.465</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.43</v>
       </c>
       <c r="I92" t="n">
-        <v>0.9953</v>
+        <v>0.9919</v>
       </c>
       <c r="J92" t="n">
-        <v>25.8778</v>
+        <v>25.7894</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.38</v>
       </c>
       <c r="I93" t="n">
-        <v>0.9056</v>
+        <v>0.8898</v>
       </c>
       <c r="J93" t="n">
-        <v>23.5456</v>
+        <v>23.1348</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.22</v>
       </c>
       <c r="I94" t="n">
-        <v>0.5852000000000001</v>
+        <v>0.5531</v>
       </c>
       <c r="J94" t="n">
-        <v>15.2152</v>
+        <v>14.3806</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>1.2</v>
       </c>
       <c r="I95" t="n">
-        <v>0.5427</v>
+        <v>0.5099</v>
       </c>
       <c r="J95" t="n">
-        <v>14.1102</v>
+        <v>13.2574</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.9</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.3846</v>
+        <v>-0.3442</v>
       </c>
       <c r="J96" t="n">
-        <v>-9.999599999999999</v>
+        <v>-8.949199999999999</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.18</v>
       </c>
       <c r="I97" t="n">
-        <v>0.4515</v>
+        <v>0.4003</v>
       </c>
       <c r="J97" t="n">
-        <v>11.739</v>
+        <v>10.4078</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>0.98</v>
       </c>
       <c r="I98" t="n">
-        <v>-0.0257</v>
+        <v>-0.0185</v>
       </c>
       <c r="J98" t="n">
-        <v>-0.6682</v>
+        <v>-0.481</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>0.75</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.2842</v>
+        <v>-0.2662</v>
       </c>
       <c r="J99" t="n">
-        <v>-7.3892</v>
+        <v>-6.9212</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.65</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.3765</v>
+        <v>-0.3631</v>
       </c>
       <c r="J100" t="n">
-        <v>-9.789</v>
+        <v>-9.4406</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.59</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.4301</v>
+        <v>-0.4214</v>
       </c>
       <c r="J101" t="n">
-        <v>-11.1826</v>
+        <v>-10.9564</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.55</v>
       </c>
       <c r="I102" t="n">
-        <v>1.1534</v>
+        <v>1.1669</v>
       </c>
       <c r="J102" t="n">
-        <v>29.9884</v>
+        <v>30.3394</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.38</v>
       </c>
       <c r="I103" t="n">
-        <v>0.893</v>
+        <v>0.8788</v>
       </c>
       <c r="J103" t="n">
-        <v>23.218</v>
+        <v>22.8488</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.31</v>
       </c>
       <c r="I104" t="n">
-        <v>0.7588</v>
+        <v>0.7365</v>
       </c>
       <c r="J104" t="n">
-        <v>19.7288</v>
+        <v>19.149</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>1.27</v>
       </c>
       <c r="I105" t="n">
-        <v>0.6808999999999999</v>
+        <v>0.6551</v>
       </c>
       <c r="J105" t="n">
-        <v>17.7034</v>
+        <v>17.0326</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.95</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.2529</v>
+        <v>-0.218</v>
       </c>
       <c r="J106" t="n">
-        <v>-6.5754</v>
+        <v>-5.668</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.03</v>
       </c>
       <c r="I107" t="n">
-        <v>0.1346</v>
+        <v>0.1042</v>
       </c>
       <c r="J107" t="n">
-        <v>3.4996</v>
+        <v>2.7092</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>0.98</v>
       </c>
       <c r="I108" t="n">
-        <v>-0.0267</v>
+        <v>-0.0195</v>
       </c>
       <c r="J108" t="n">
-        <v>-0.6942</v>
+        <v>-0.507</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.2272</v>
+        <v>-0.2087</v>
       </c>
       <c r="J109" t="n">
-        <v>-5.9072</v>
+        <v>-5.4262</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.79</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.2466</v>
+        <v>-0.228</v>
       </c>
       <c r="J110" t="n">
-        <v>-6.4116</v>
+        <v>-5.928</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.57</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.4483</v>
+        <v>-0.4416</v>
       </c>
       <c r="J111" t="n">
-        <v>-11.6558</v>
+        <v>-11.4816</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.44</v>
       </c>
       <c r="I112" t="n">
-        <v>1.0269</v>
+        <v>1.0285</v>
       </c>
       <c r="J112" t="n">
-        <v>34.9146</v>
+        <v>34.969</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.16</v>
       </c>
       <c r="I113" t="n">
-        <v>0.4614</v>
+        <v>0.4246</v>
       </c>
       <c r="J113" t="n">
-        <v>15.6876</v>
+        <v>14.4364</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>1.15</v>
       </c>
       <c r="I114" t="n">
-        <v>0.4389</v>
+        <v>0.4021</v>
       </c>
       <c r="J114" t="n">
-        <v>14.9226</v>
+        <v>13.6714</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>1.13</v>
       </c>
       <c r="I115" t="n">
-        <v>0.3918</v>
+        <v>0.3557</v>
       </c>
       <c r="J115" t="n">
-        <v>13.3212</v>
+        <v>12.0938</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.91</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.3456</v>
+        <v>-0.3041</v>
       </c>
       <c r="J116" t="n">
-        <v>-11.7504</v>
+        <v>-10.3394</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.11</v>
       </c>
       <c r="I117" t="n">
-        <v>0.2818</v>
+        <v>0.2325</v>
       </c>
       <c r="J117" t="n">
-        <v>9.581200000000001</v>
+        <v>7.905</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.08</v>
       </c>
       <c r="I118" t="n">
-        <v>0.2215</v>
+        <v>0.1776</v>
       </c>
       <c r="J118" t="n">
-        <v>7.531</v>
+        <v>6.0384</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>0.9</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.1429</v>
+        <v>-0.124</v>
       </c>
       <c r="J119" t="n">
-        <v>-4.8586</v>
+        <v>-4.216</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.86</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.1866</v>
+        <v>-0.1664</v>
       </c>
       <c r="J120" t="n">
-        <v>-6.3444</v>
+        <v>-5.6576</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.238</v>
+        <v>-0.2178</v>
       </c>
       <c r="J121" t="n">
-        <v>-8.092000000000001</v>
+        <v>-7.4052</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.26</v>
       </c>
       <c r="I122" t="n">
-        <v>0.7252999999999999</v>
+        <v>0.6941000000000001</v>
       </c>
       <c r="J122" t="n">
-        <v>21.759</v>
+        <v>20.823</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.18</v>
       </c>
       <c r="I123" t="n">
-        <v>0.5433</v>
+        <v>0.5023</v>
       </c>
       <c r="J123" t="n">
-        <v>16.299</v>
+        <v>15.069</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>0.9</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.3404</v>
+        <v>-0.2987</v>
       </c>
       <c r="J124" t="n">
-        <v>-10.212</v>
+        <v>-8.961</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.82</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.5391</v>
+        <v>-0.498</v>
       </c>
       <c r="J125" t="n">
-        <v>-16.173</v>
+        <v>-14.94</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.8</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.5857</v>
+        <v>-0.5463</v>
       </c>
       <c r="J126" t="n">
-        <v>-17.571</v>
+        <v>-16.389</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.64</v>
       </c>
       <c r="I127" t="n">
-        <v>1.0219</v>
+        <v>0.9886</v>
       </c>
       <c r="J127" t="n">
-        <v>30.657</v>
+        <v>29.658</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.21</v>
       </c>
       <c r="I128" t="n">
-        <v>0.4191</v>
+        <v>0.366</v>
       </c>
       <c r="J128" t="n">
-        <v>12.573</v>
+        <v>10.98</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>1.11</v>
       </c>
       <c r="I129" t="n">
-        <v>0.2495</v>
+        <v>0.2087</v>
       </c>
       <c r="J129" t="n">
-        <v>7.485</v>
+        <v>6.261</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>1.01</v>
       </c>
       <c r="I130" t="n">
-        <v>0.0209</v>
+        <v>0.0127</v>
       </c>
       <c r="J130" t="n">
-        <v>0.627</v>
+        <v>0.381</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.97</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.0728</v>
+        <v>-0.0585</v>
       </c>
       <c r="J131" t="n">
-        <v>-2.184</v>
+        <v>-1.755</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>0.97</v>
       </c>
       <c r="I132" t="n">
-        <v>0.0064</v>
+        <v>0.0363</v>
       </c>
       <c r="J132" t="n">
-        <v>0.1344</v>
+        <v>0.7623</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I133" t="n">
-        <v>-0.3195</v>
+        <v>-0.3082</v>
       </c>
       <c r="J133" t="n">
-        <v>-6.7095</v>
+        <v>-6.4722</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>0.6</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.3979</v>
+        <v>-0.3884</v>
       </c>
       <c r="J134" t="n">
-        <v>-8.3559</v>
+        <v>-8.1564</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.52</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.4681</v>
+        <v>-0.463</v>
       </c>
       <c r="J135" t="n">
-        <v>-9.8301</v>
+        <v>-9.723000000000001</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.41</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.5647</v>
+        <v>-0.5711000000000001</v>
       </c>
       <c r="J136" t="n">
-        <v>-11.8587</v>
+        <v>-11.9931</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.71</v>
       </c>
       <c r="I137" t="n">
-        <v>1.3278</v>
+        <v>1.3498</v>
       </c>
       <c r="J137" t="n">
-        <v>27.8838</v>
+        <v>28.3458</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.66</v>
       </c>
       <c r="I138" t="n">
-        <v>1.2661</v>
+        <v>1.2859</v>
       </c>
       <c r="J138" t="n">
-        <v>26.5881</v>
+        <v>27.0039</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>1.51</v>
       </c>
       <c r="I139" t="n">
-        <v>1.0772</v>
+        <v>1.0927</v>
       </c>
       <c r="J139" t="n">
-        <v>22.6212</v>
+        <v>22.9467</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>1.51</v>
       </c>
       <c r="I140" t="n">
-        <v>1.0772</v>
+        <v>1.0927</v>
       </c>
       <c r="J140" t="n">
-        <v>22.6212</v>
+        <v>22.9467</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.97</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.214</v>
+        <v>-0.1888</v>
       </c>
       <c r="J141" t="n">
-        <v>-4.494</v>
+        <v>-3.9648</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.22</v>
       </c>
       <c r="I142" t="n">
-        <v>0.4597</v>
+        <v>0.4013</v>
       </c>
       <c r="J142" t="n">
-        <v>16.5492</v>
+        <v>14.4468</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.21</v>
       </c>
       <c r="I143" t="n">
-        <v>0.443</v>
+        <v>0.3852</v>
       </c>
       <c r="J143" t="n">
-        <v>15.948</v>
+        <v>13.8672</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>0.95</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.0887</v>
+        <v>-0.0725</v>
       </c>
       <c r="J144" t="n">
-        <v>-3.1932</v>
+        <v>-2.61</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.1018</v>
+        <v>-0.0844</v>
       </c>
       <c r="J145" t="n">
-        <v>-3.6648</v>
+        <v>-3.0384</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.85</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.2045</v>
+        <v>-0.1838</v>
       </c>
       <c r="J146" t="n">
-        <v>-7.362</v>
+        <v>-6.6168</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.19</v>
       </c>
       <c r="I147" t="n">
-        <v>0.5364</v>
+        <v>0.4976</v>
       </c>
       <c r="J147" t="n">
-        <v>19.3104</v>
+        <v>17.9136</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.1</v>
       </c>
       <c r="I148" t="n">
-        <v>0.3234</v>
+        <v>0.2869</v>
       </c>
       <c r="J148" t="n">
-        <v>11.6424</v>
+        <v>10.3284</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.1</v>
       </c>
       <c r="I149" t="n">
-        <v>0.3234</v>
+        <v>0.2869</v>
       </c>
       <c r="J149" t="n">
-        <v>11.6424</v>
+        <v>10.3284</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>1.09</v>
       </c>
       <c r="I150" t="n">
-        <v>0.2976</v>
+        <v>0.2622</v>
       </c>
       <c r="J150" t="n">
-        <v>10.7136</v>
+        <v>9.4392</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>1.07</v>
       </c>
       <c r="I151" t="n">
-        <v>0.2433</v>
+        <v>0.2108</v>
       </c>
       <c r="J151" t="n">
-        <v>8.758800000000001</v>
+        <v>7.5888</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.08</v>
       </c>
       <c r="I152" t="n">
-        <v>0.181</v>
+        <v>0.1641</v>
       </c>
       <c r="J152" t="n">
-        <v>5.43</v>
+        <v>4.923</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.07</v>
       </c>
       <c r="I153" t="n">
-        <v>0.1643</v>
+        <v>0.1472</v>
       </c>
       <c r="J153" t="n">
-        <v>4.929</v>
+        <v>4.416</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>1.03</v>
       </c>
       <c r="I154" t="n">
-        <v>0.0905</v>
+        <v>0.0755</v>
       </c>
       <c r="J154" t="n">
-        <v>2.715</v>
+        <v>2.265</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.71</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.33</v>
+        <v>-0.3135</v>
       </c>
       <c r="J155" t="n">
-        <v>-9.9</v>
+        <v>-9.404999999999999</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.66</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.3758</v>
+        <v>-0.3626</v>
       </c>
       <c r="J156" t="n">
-        <v>-11.274</v>
+        <v>-10.878</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.5</v>
       </c>
       <c r="I157" t="n">
-        <v>0.6345</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="J157" t="n">
-        <v>19.035</v>
+        <v>16.89</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.22</v>
       </c>
       <c r="I158" t="n">
-        <v>0.3269</v>
+        <v>0.2702</v>
       </c>
       <c r="J158" t="n">
-        <v>9.807</v>
+        <v>8.106</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.08</v>
       </c>
       <c r="I159" t="n">
-        <v>0.1457</v>
+        <v>0.1125</v>
       </c>
       <c r="J159" t="n">
-        <v>4.371</v>
+        <v>3.375</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>1.07</v>
       </c>
       <c r="I160" t="n">
-        <v>0.1304</v>
+        <v>0.0997</v>
       </c>
       <c r="J160" t="n">
-        <v>3.912</v>
+        <v>2.991</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.86</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.2033</v>
+        <v>-0.1832</v>
       </c>
       <c r="J161" t="n">
-        <v>-6.099</v>
+        <v>-5.496</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.67</v>
       </c>
       <c r="I162" t="n">
-        <v>1.3028</v>
+        <v>1.3222</v>
       </c>
       <c r="J162" t="n">
-        <v>29.9644</v>
+        <v>30.4106</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.53</v>
       </c>
       <c r="I163" t="n">
-        <v>1.1212</v>
+        <v>1.1344</v>
       </c>
       <c r="J163" t="n">
-        <v>25.7876</v>
+        <v>26.0912</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>1.24</v>
       </c>
       <c r="I164" t="n">
-        <v>0.6148</v>
+        <v>0.5881</v>
       </c>
       <c r="J164" t="n">
-        <v>14.1404</v>
+        <v>13.5263</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>1.16</v>
       </c>
       <c r="I165" t="n">
-        <v>0.4378</v>
+        <v>0.4064</v>
       </c>
       <c r="J165" t="n">
-        <v>10.0694</v>
+        <v>9.347200000000001</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>1.03</v>
       </c>
       <c r="I166" t="n">
-        <v>0.08309999999999999</v>
+        <v>0.0619</v>
       </c>
       <c r="J166" t="n">
-        <v>1.9113</v>
+        <v>1.4237</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>0.88</v>
       </c>
       <c r="I167" t="n">
-        <v>-0.1425</v>
+        <v>-0.127</v>
       </c>
       <c r="J167" t="n">
-        <v>-3.2775</v>
+        <v>-2.921</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>0.86</v>
       </c>
       <c r="I168" t="n">
-        <v>-0.1651</v>
+        <v>-0.1495</v>
       </c>
       <c r="J168" t="n">
-        <v>-3.7973</v>
+        <v>-3.4385</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>0.85</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.176</v>
+        <v>-0.1604</v>
       </c>
       <c r="J169" t="n">
-        <v>-4.048</v>
+        <v>-3.6892</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.67</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.3479</v>
+        <v>-0.3337</v>
       </c>
       <c r="J170" t="n">
-        <v>-8.0017</v>
+        <v>-7.6751</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.43</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.5594</v>
+        <v>-0.5661</v>
       </c>
       <c r="J171" t="n">
-        <v>-12.8662</v>
+        <v>-13.0203</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.6</v>
       </c>
       <c r="I172" t="n">
-        <v>1.2545</v>
+        <v>1.2736</v>
       </c>
       <c r="J172" t="n">
-        <v>33.8715</v>
+        <v>34.3872</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.08</v>
       </c>
       <c r="I173" t="n">
-        <v>0.2658</v>
+        <v>0.2333</v>
       </c>
       <c r="J173" t="n">
-        <v>7.1766</v>
+        <v>6.2991</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>1.06</v>
       </c>
       <c r="I174" t="n">
-        <v>0.2091</v>
+        <v>0.1798</v>
       </c>
       <c r="J174" t="n">
-        <v>5.6457</v>
+        <v>4.8546</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>1.02</v>
       </c>
       <c r="I175" t="n">
-        <v>0.0775</v>
+        <v>0.0608</v>
       </c>
       <c r="J175" t="n">
-        <v>2.0925</v>
+        <v>1.6416</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.96</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.1953</v>
+        <v>-0.1606</v>
       </c>
       <c r="J176" t="n">
-        <v>-5.2731</v>
+        <v>-4.3362</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.22</v>
       </c>
       <c r="I177" t="n">
-        <v>0.4747</v>
+        <v>0.4165</v>
       </c>
       <c r="J177" t="n">
-        <v>12.8169</v>
+        <v>11.2455</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.2</v>
       </c>
       <c r="I178" t="n">
-        <v>0.4406</v>
+        <v>0.3831</v>
       </c>
       <c r="J178" t="n">
-        <v>11.8962</v>
+        <v>10.3437</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.12</v>
       </c>
       <c r="I179" t="n">
-        <v>0.2966</v>
+        <v>0.2461</v>
       </c>
       <c r="J179" t="n">
-        <v>8.0082</v>
+        <v>6.6447</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>0.75</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.2984</v>
+        <v>-0.2803</v>
       </c>
       <c r="J180" t="n">
-        <v>-8.056800000000001</v>
+        <v>-7.5681</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.57</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.461</v>
+        <v>-0.4572</v>
       </c>
       <c r="J181" t="n">
-        <v>-12.447</v>
+        <v>-12.3444</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.22</v>
       </c>
       <c r="I182" t="n">
-        <v>0.6147</v>
+        <v>0.5768</v>
       </c>
       <c r="J182" t="n">
-        <v>17.2116</v>
+        <v>16.1504</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.07</v>
       </c>
       <c r="I183" t="n">
-        <v>0.2489</v>
+        <v>0.2137</v>
       </c>
       <c r="J183" t="n">
-        <v>6.9692</v>
+        <v>5.9836</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>1.06</v>
       </c>
       <c r="I184" t="n">
-        <v>0.221</v>
+        <v>0.1878</v>
       </c>
       <c r="J184" t="n">
-        <v>6.188</v>
+        <v>5.2584</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>1.03</v>
       </c>
       <c r="I185" t="n">
-        <v>0.1276</v>
+        <v>0.1035</v>
       </c>
       <c r="J185" t="n">
-        <v>3.5728</v>
+        <v>2.898</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.93</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.2714</v>
+        <v>-0.2314</v>
       </c>
       <c r="J186" t="n">
-        <v>-7.5992</v>
+        <v>-6.4792</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.33</v>
       </c>
       <c r="I187" t="n">
-        <v>0.6312</v>
+        <v>0.5719</v>
       </c>
       <c r="J187" t="n">
-        <v>17.6736</v>
+        <v>16.0132</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.17</v>
       </c>
       <c r="I188" t="n">
-        <v>0.3722</v>
+        <v>0.3176</v>
       </c>
       <c r="J188" t="n">
-        <v>10.4216</v>
+        <v>8.892799999999999</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>1.14</v>
       </c>
       <c r="I189" t="n">
-        <v>0.3192</v>
+        <v>0.268</v>
       </c>
       <c r="J189" t="n">
-        <v>8.9376</v>
+        <v>7.504</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.83</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.2265</v>
+        <v>-0.2061</v>
       </c>
       <c r="J190" t="n">
-        <v>-6.342</v>
+        <v>-5.7708</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.77</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.286</v>
+        <v>-0.2677</v>
       </c>
       <c r="J191" t="n">
-        <v>-8.007999999999999</v>
+        <v>-7.4956</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.82</v>
       </c>
       <c r="I192" t="n">
-        <v>1.4958</v>
+        <v>1.5281</v>
       </c>
       <c r="J192" t="n">
-        <v>34.4034</v>
+        <v>35.1463</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.64</v>
       </c>
       <c r="I193" t="n">
-        <v>1.2683</v>
+        <v>1.2861</v>
       </c>
       <c r="J193" t="n">
-        <v>29.1709</v>
+        <v>29.5803</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.41</v>
       </c>
       <c r="I194" t="n">
-        <v>0.9458</v>
+        <v>0.9375</v>
       </c>
       <c r="J194" t="n">
-        <v>21.7534</v>
+        <v>21.5625</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>0.83</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.5723</v>
+        <v>-0.5386</v>
       </c>
       <c r="J195" t="n">
-        <v>-13.1629</v>
+        <v>-12.3878</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.83</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.5723</v>
+        <v>-0.5386</v>
       </c>
       <c r="J196" t="n">
-        <v>-13.1629</v>
+        <v>-12.3878</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.31</v>
       </c>
       <c r="I197" t="n">
-        <v>0.6688</v>
+        <v>0.6217</v>
       </c>
       <c r="J197" t="n">
-        <v>15.3824</v>
+        <v>14.2991</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.09</v>
       </c>
       <c r="I198" t="n">
-        <v>0.2699</v>
+        <v>0.2242</v>
       </c>
       <c r="J198" t="n">
-        <v>6.2077</v>
+        <v>5.1566</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>1.01</v>
       </c>
       <c r="I199" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.0527</v>
       </c>
       <c r="J199" t="n">
-        <v>1.656</v>
+        <v>1.2121</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.49</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.5189</v>
+        <v>-0.5212</v>
       </c>
       <c r="J200" t="n">
-        <v>-11.9347</v>
+        <v>-11.9876</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.34</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.6453</v>
+        <v>-0.6686</v>
       </c>
       <c r="J201" t="n">
-        <v>-14.8419</v>
+        <v>-15.3778</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.38</v>
       </c>
       <c r="I202" t="n">
-        <v>0.5106000000000001</v>
+        <v>0.4417</v>
       </c>
       <c r="J202" t="n">
-        <v>13.7862</v>
+        <v>11.9259</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.3</v>
       </c>
       <c r="I203" t="n">
-        <v>0.4218</v>
+        <v>0.3574</v>
       </c>
       <c r="J203" t="n">
-        <v>11.3886</v>
+        <v>9.649800000000001</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>1.13</v>
       </c>
       <c r="I204" t="n">
-        <v>0.2166</v>
+        <v>0.1724</v>
       </c>
       <c r="J204" t="n">
-        <v>5.8482</v>
+        <v>4.6548</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>1</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.0089</v>
+        <v>-0.0066</v>
       </c>
       <c r="J205" t="n">
-        <v>-0.2403</v>
+        <v>-0.1782</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.83</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.2331</v>
+        <v>-0.2134</v>
       </c>
       <c r="J206" t="n">
-        <v>-6.2937</v>
+        <v>-5.7618</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.17</v>
       </c>
       <c r="I207" t="n">
-        <v>0.3053</v>
+        <v>0.2937</v>
       </c>
       <c r="J207" t="n">
-        <v>8.2431</v>
+        <v>7.9299</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.03</v>
       </c>
       <c r="I208" t="n">
-        <v>0.0822</v>
+        <v>0.0678</v>
       </c>
       <c r="J208" t="n">
-        <v>2.2194</v>
+        <v>1.8306</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>0.93</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.1089</v>
+        <v>-0.09180000000000001</v>
       </c>
       <c r="J209" t="n">
-        <v>-2.9403</v>
+        <v>-2.4786</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>0.91</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.1326</v>
+        <v>-0.114</v>
       </c>
       <c r="J210" t="n">
-        <v>-3.5802</v>
+        <v>-3.078</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.79</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.2591</v>
+        <v>-0.2394</v>
       </c>
       <c r="J211" t="n">
-        <v>-6.9957</v>
+        <v>-6.4638</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.32</v>
       </c>
       <c r="I212" t="n">
-        <v>0.6361</v>
+        <v>0.5787</v>
       </c>
       <c r="J212" t="n">
-        <v>17.8108</v>
+        <v>16.2036</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.29</v>
       </c>
       <c r="I213" t="n">
-        <v>0.5885</v>
+        <v>0.5301</v>
       </c>
       <c r="J213" t="n">
-        <v>16.478</v>
+        <v>14.8428</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>0.83</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.22</v>
+        <v>-0.1995</v>
       </c>
       <c r="J214" t="n">
-        <v>-6.16</v>
+        <v>-5.586</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>0.78</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.2699</v>
+        <v>-0.2505</v>
       </c>
       <c r="J215" t="n">
-        <v>-7.5572</v>
+        <v>-7.014</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.66</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.3819</v>
+        <v>-0.3698</v>
       </c>
       <c r="J216" t="n">
-        <v>-10.6932</v>
+        <v>-10.3544</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.39</v>
       </c>
       <c r="I217" t="n">
-        <v>0.9597</v>
+        <v>0.9497</v>
       </c>
       <c r="J217" t="n">
-        <v>26.8716</v>
+        <v>26.5916</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.39</v>
       </c>
       <c r="I218" t="n">
-        <v>0.9597</v>
+        <v>0.9497</v>
       </c>
       <c r="J218" t="n">
-        <v>26.8716</v>
+        <v>26.5916</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>1.01</v>
       </c>
       <c r="I219" t="n">
-        <v>0.0454</v>
+        <v>0.034</v>
       </c>
       <c r="J219" t="n">
-        <v>1.2712</v>
+        <v>0.952</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>0.97</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.1518</v>
+        <v>-0.1208</v>
       </c>
       <c r="J220" t="n">
-        <v>-4.2504</v>
+        <v>-3.3824</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.7</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.8268</v>
+        <v>-0.8061</v>
       </c>
       <c r="J221" t="n">
-        <v>-23.1504</v>
+        <v>-22.5708</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.42</v>
       </c>
       <c r="I222" t="n">
-        <v>0.7785</v>
+        <v>0.7254</v>
       </c>
       <c r="J222" t="n">
-        <v>22.5765</v>
+        <v>21.0366</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>0.96</v>
       </c>
       <c r="I223" t="n">
-        <v>-0.0731</v>
+        <v>-0.0586</v>
       </c>
       <c r="J223" t="n">
-        <v>-2.1199</v>
+        <v>-1.6994</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>0.95</v>
       </c>
       <c r="I224" t="n">
-        <v>-0.0867</v>
+        <v>-0.0708</v>
       </c>
       <c r="J224" t="n">
-        <v>-2.5143</v>
+        <v>-2.0532</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>0.9</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.1476</v>
+        <v>-0.1279</v>
       </c>
       <c r="J225" t="n">
-        <v>-4.2804</v>
+        <v>-3.7091</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.2432</v>
+        <v>-0.2231</v>
       </c>
       <c r="J226" t="n">
-        <v>-7.0528</v>
+        <v>-6.4699</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.3</v>
       </c>
       <c r="I227" t="n">
-        <v>0.7839</v>
+        <v>0.756</v>
       </c>
       <c r="J227" t="n">
-        <v>22.7331</v>
+        <v>21.924</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>1.1</v>
       </c>
       <c r="I228" t="n">
-        <v>0.3273</v>
+        <v>0.2887</v>
       </c>
       <c r="J228" t="n">
-        <v>9.4917</v>
+        <v>8.372299999999999</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>1.04</v>
       </c>
       <c r="I229" t="n">
-        <v>0.159</v>
+        <v>0.1318</v>
       </c>
       <c r="J229" t="n">
-        <v>4.611</v>
+        <v>3.8222</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>1.03</v>
       </c>
       <c r="I230" t="n">
-        <v>0.1257</v>
+        <v>0.1022</v>
       </c>
       <c r="J230" t="n">
-        <v>3.6453</v>
+        <v>2.9638</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.9</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.3567</v>
+        <v>-0.314</v>
       </c>
       <c r="J231" t="n">
-        <v>-10.3443</v>
+        <v>-9.106</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.52</v>
       </c>
       <c r="I232" t="n">
-        <v>1.1325</v>
+        <v>1.1451</v>
       </c>
       <c r="J232" t="n">
-        <v>32.8425</v>
+        <v>33.2079</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1.45</v>
       </c>
       <c r="I233" t="n">
-        <v>1.0336</v>
+        <v>1.0364</v>
       </c>
       <c r="J233" t="n">
-        <v>29.9744</v>
+        <v>30.0556</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>1.09</v>
       </c>
       <c r="I234" t="n">
-        <v>0.2845</v>
+        <v>0.2524</v>
       </c>
       <c r="J234" t="n">
-        <v>8.250500000000001</v>
+        <v>7.3196</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>0.98</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.1342</v>
+        <v>-0.107</v>
       </c>
       <c r="J235" t="n">
-        <v>-3.8918</v>
+        <v>-3.103</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.2671</v>
+        <v>-0.2288</v>
       </c>
       <c r="J236" t="n">
-        <v>-7.7459</v>
+        <v>-6.6352</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.15</v>
       </c>
       <c r="I237" t="n">
-        <v>0.3663</v>
+        <v>0.3124</v>
       </c>
       <c r="J237" t="n">
-        <v>10.6227</v>
+        <v>9.0596</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>1.01</v>
       </c>
       <c r="I238" t="n">
-        <v>0.0557</v>
+        <v>0.0379</v>
       </c>
       <c r="J238" t="n">
-        <v>1.6153</v>
+        <v>1.0991</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>0.9</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.1403</v>
+        <v>-0.1223</v>
       </c>
       <c r="J239" t="n">
-        <v>-4.0687</v>
+        <v>-3.5467</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>0.82</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.2247</v>
+        <v>-0.2047</v>
       </c>
       <c r="J240" t="n">
-        <v>-6.5163</v>
+        <v>-5.9363</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.71</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.3307</v>
+        <v>-0.3143</v>
       </c>
       <c r="J241" t="n">
-        <v>-9.590299999999999</v>
+        <v>-9.114699999999999</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1.1</v>
       </c>
       <c r="I242" t="n">
-        <v>0.2251</v>
+        <v>0.2109</v>
       </c>
       <c r="J242" t="n">
-        <v>6.0777</v>
+        <v>5.6943</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>0.99</v>
       </c>
       <c r="I243" t="n">
-        <v>-0.0118</v>
+        <v>-0.0074</v>
       </c>
       <c r="J243" t="n">
-        <v>-0.3186</v>
+        <v>-0.1998</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>0.82</v>
       </c>
       <c r="I244" t="n">
-        <v>-0.2192</v>
+        <v>-0.2002</v>
       </c>
       <c r="J244" t="n">
-        <v>-5.9184</v>
+        <v>-5.4054</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>0.76</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.2776</v>
+        <v>-0.259</v>
       </c>
       <c r="J245" t="n">
-        <v>-7.4952</v>
+        <v>-6.993</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>0.62</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.4064</v>
+        <v>-0.3956</v>
       </c>
       <c r="J246" t="n">
-        <v>-10.9728</v>
+        <v>-10.6812</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>2.09</v>
       </c>
       <c r="I247" t="n">
-        <v>1.1262</v>
+        <v>1.0958</v>
       </c>
       <c r="J247" t="n">
-        <v>30.4074</v>
+        <v>29.5866</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>1.13</v>
       </c>
       <c r="I248" t="n">
-        <v>0.2063</v>
+        <v>0.1658</v>
       </c>
       <c r="J248" t="n">
-        <v>5.5701</v>
+        <v>4.4766</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>1.11</v>
       </c>
       <c r="I249" t="n">
-        <v>0.1788</v>
+        <v>0.1418</v>
       </c>
       <c r="J249" t="n">
-        <v>4.8276</v>
+        <v>3.8286</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>1.06</v>
       </c>
       <c r="I250" t="n">
-        <v>0.1038</v>
+        <v>0.0779</v>
       </c>
       <c r="J250" t="n">
-        <v>2.8026</v>
+        <v>2.1033</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.92</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.1444</v>
+        <v>-0.1261</v>
       </c>
       <c r="J251" t="n">
-        <v>-3.8988</v>
+        <v>-3.4047</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>1.66</v>
       </c>
       <c r="I252" t="n">
-        <v>1.2908</v>
+        <v>1.3096</v>
       </c>
       <c r="J252" t="n">
-        <v>30.9792</v>
+        <v>31.4304</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>1.43</v>
       </c>
       <c r="I253" t="n">
-        <v>0.9777</v>
+        <v>0.9745</v>
       </c>
       <c r="J253" t="n">
-        <v>23.4648</v>
+        <v>23.388</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>1.41</v>
       </c>
       <c r="I254" t="n">
-        <v>0.9433</v>
+        <v>0.9353</v>
       </c>
       <c r="J254" t="n">
-        <v>22.6392</v>
+        <v>22.4472</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>1.13</v>
       </c>
       <c r="I255" t="n">
-        <v>0.3665</v>
+        <v>0.3345</v>
       </c>
       <c r="J255" t="n">
-        <v>8.795999999999999</v>
+        <v>8.028</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>0.98</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.1553</v>
+        <v>-0.13</v>
       </c>
       <c r="J256" t="n">
-        <v>-3.7272</v>
+        <v>-3.12</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>1.31</v>
       </c>
       <c r="I257" t="n">
-        <v>0.6697</v>
+        <v>0.6229</v>
       </c>
       <c r="J257" t="n">
-        <v>16.0728</v>
+        <v>14.9496</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>1.02</v>
       </c>
       <c r="I258" t="n">
-        <v>0.1039</v>
+        <v>0.07820000000000001</v>
       </c>
       <c r="J258" t="n">
-        <v>2.4936</v>
+        <v>1.8768</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>0.85</v>
       </c>
       <c r="I259" t="n">
-        <v>-0.1887</v>
+        <v>-0.1707</v>
       </c>
       <c r="J259" t="n">
-        <v>-4.5288</v>
+        <v>-4.0968</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>0.7</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.3326</v>
+        <v>-0.3163</v>
       </c>
       <c r="J260" t="n">
-        <v>-7.9824</v>
+        <v>-7.5912</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>0.35</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.6368</v>
+        <v>-0.6585</v>
       </c>
       <c r="J261" t="n">
-        <v>-15.2832</v>
+        <v>-15.804</v>
       </c>
     </row>
     <row r="262">
@@ -12829,10 +12829,10 @@
         <v>1.71</v>
       </c>
       <c r="I262" t="n">
-        <v>1.3553</v>
+        <v>1.3775</v>
       </c>
       <c r="J262" t="n">
-        <v>32.5272</v>
+        <v>33.06</v>
       </c>
     </row>
     <row r="263">
@@ -12869,10 +12869,10 @@
         <v>1.57</v>
       </c>
       <c r="I263" t="n">
-        <v>1.1751</v>
+        <v>1.1895</v>
       </c>
       <c r="J263" t="n">
-        <v>28.2024</v>
+        <v>28.548</v>
       </c>
     </row>
     <row r="264">
@@ -12909,10 +12909,10 @@
         <v>1.29</v>
       </c>
       <c r="I264" t="n">
-        <v>0.7178</v>
+        <v>0.6949</v>
       </c>
       <c r="J264" t="n">
-        <v>17.2272</v>
+        <v>16.6776</v>
       </c>
     </row>
     <row r="265">
@@ -12949,10 +12949,10 @@
         <v>1.24</v>
       </c>
       <c r="I265" t="n">
-        <v>0.6159</v>
+        <v>0.589</v>
       </c>
       <c r="J265" t="n">
-        <v>14.7816</v>
+        <v>14.136</v>
       </c>
     </row>
     <row r="266">
@@ -12989,10 +12989,10 @@
         <v>0.78</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.6889999999999999</v>
+        <v>-0.6627999999999999</v>
       </c>
       <c r="J266" t="n">
-        <v>-16.536</v>
+        <v>-15.9072</v>
       </c>
     </row>
     <row r="267">
@@ -13029,10 +13029,10 @@
         <v>0.99</v>
       </c>
       <c r="I267" t="n">
-        <v>-0.0058</v>
+        <v>-0.0014</v>
       </c>
       <c r="J267" t="n">
-        <v>-0.1392</v>
+        <v>-0.0336</v>
       </c>
     </row>
     <row r="268">
@@ -13069,10 +13069,10 @@
         <v>0.95</v>
       </c>
       <c r="I268" t="n">
-        <v>-0.0693</v>
+        <v>-0.0575</v>
       </c>
       <c r="J268" t="n">
-        <v>-1.6632</v>
+        <v>-1.38</v>
       </c>
     </row>
     <row r="269">
@@ -13109,10 +13109,10 @@
         <v>0.78</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.2547</v>
+        <v>-0.2366</v>
       </c>
       <c r="J269" t="n">
-        <v>-6.1128</v>
+        <v>-5.6784</v>
       </c>
     </row>
     <row r="270">
@@ -13149,10 +13149,10 @@
         <v>0.71</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.3205</v>
+        <v>-0.3039</v>
       </c>
       <c r="J270" t="n">
-        <v>-7.692</v>
+        <v>-7.2936</v>
       </c>
     </row>
     <row r="271">
@@ -13189,10 +13189,10 @@
         <v>0.67</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.3572</v>
+        <v>-0.3426</v>
       </c>
       <c r="J271" t="n">
-        <v>-8.572800000000001</v>
+        <v>-8.2224</v>
       </c>
     </row>
     <row r="272">
@@ -13229,10 +13229,10 @@
         <v>1.8</v>
       </c>
       <c r="I272" t="n">
-        <v>1.48</v>
+        <v>1.5119</v>
       </c>
       <c r="J272" t="n">
-        <v>37</v>
+        <v>37.7975</v>
       </c>
     </row>
     <row r="273">
@@ -13269,10 +13269,10 @@
         <v>1.71</v>
       </c>
       <c r="I273" t="n">
-        <v>1.3661</v>
+        <v>1.3895</v>
       </c>
       <c r="J273" t="n">
-        <v>34.1525</v>
+        <v>34.7375</v>
       </c>
     </row>
     <row r="274">
@@ -13309,10 +13309,10 @@
         <v>1.18</v>
       </c>
       <c r="I274" t="n">
-        <v>0.4924</v>
+        <v>0.4606</v>
       </c>
       <c r="J274" t="n">
-        <v>12.31</v>
+        <v>11.515</v>
       </c>
     </row>
     <row r="275">
@@ -13349,10 +13349,10 @@
         <v>1.17</v>
       </c>
       <c r="I275" t="n">
-        <v>0.4696</v>
+        <v>0.4376</v>
       </c>
       <c r="J275" t="n">
-        <v>11.74</v>
+        <v>10.94</v>
       </c>
     </row>
     <row r="276">
@@ -13389,10 +13389,10 @@
         <v>0.49</v>
       </c>
       <c r="I276" t="n">
-        <v>-1.2724</v>
+        <v>-1.3171</v>
       </c>
       <c r="J276" t="n">
-        <v>-31.81</v>
+        <v>-32.9275</v>
       </c>
     </row>
     <row r="277">
@@ -13429,10 +13429,10 @@
         <v>1.13</v>
       </c>
       <c r="I277" t="n">
-        <v>0.3477</v>
+        <v>0.2971</v>
       </c>
       <c r="J277" t="n">
-        <v>8.692500000000001</v>
+        <v>7.4275</v>
       </c>
     </row>
     <row r="278">
@@ -13469,10 +13469,10 @@
         <v>0.86</v>
       </c>
       <c r="I278" t="n">
-        <v>-0.1792</v>
+        <v>-0.1611</v>
       </c>
       <c r="J278" t="n">
-        <v>-4.48</v>
+        <v>-4.0275</v>
       </c>
     </row>
     <row r="279">
@@ -13509,10 +13509,10 @@
         <v>0.82</v>
       </c>
       <c r="I279" t="n">
-        <v>-0.2191</v>
+        <v>-0.2001</v>
       </c>
       <c r="J279" t="n">
-        <v>-5.4775</v>
+        <v>-5.0025</v>
       </c>
     </row>
     <row r="280">
@@ -13549,10 +13549,10 @@
         <v>0.79</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.2485</v>
+        <v>-0.2295</v>
       </c>
       <c r="J280" t="n">
-        <v>-6.2125</v>
+        <v>-5.7375</v>
       </c>
     </row>
     <row r="281">
@@ -13589,10 +13589,10 @@
         <v>0.68</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.352</v>
+        <v>-0.3369</v>
       </c>
       <c r="J281" t="n">
-        <v>-8.800000000000001</v>
+        <v>-8.422499999999999</v>
       </c>
     </row>
     <row r="282">
@@ -13629,10 +13629,10 @@
         <v>1.63</v>
       </c>
       <c r="I282" t="n">
-        <v>1.2874</v>
+        <v>1.3079</v>
       </c>
       <c r="J282" t="n">
-        <v>43.7716</v>
+        <v>44.4686</v>
       </c>
     </row>
     <row r="283">
@@ -13669,10 +13669,10 @@
         <v>1.17</v>
       </c>
       <c r="I283" t="n">
-        <v>0.4827</v>
+        <v>0.4465</v>
       </c>
       <c r="J283" t="n">
-        <v>16.4118</v>
+        <v>15.181</v>
       </c>
     </row>
     <row r="284">
@@ -13709,10 +13709,10 @@
         <v>1.09</v>
       </c>
       <c r="I284" t="n">
-        <v>0.2887</v>
+        <v>0.2559</v>
       </c>
       <c r="J284" t="n">
-        <v>9.815799999999999</v>
+        <v>8.7006</v>
       </c>
     </row>
     <row r="285">
@@ -13749,10 +13749,10 @@
         <v>1.04</v>
       </c>
       <c r="I285" t="n">
-        <v>0.143</v>
+        <v>0.119</v>
       </c>
       <c r="J285" t="n">
-        <v>4.862</v>
+        <v>4.046</v>
       </c>
     </row>
     <row r="286">
@@ -13789,10 +13789,10 @@
         <v>0.92</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.3202</v>
+        <v>-0.2794</v>
       </c>
       <c r="J286" t="n">
-        <v>-10.8868</v>
+        <v>-9.499599999999999</v>
       </c>
     </row>
     <row r="287">
@@ -13829,10 +13829,10 @@
         <v>1.35</v>
       </c>
       <c r="I287" t="n">
-        <v>0.6983</v>
+        <v>0.6454</v>
       </c>
       <c r="J287" t="n">
-        <v>23.7422</v>
+        <v>21.9436</v>
       </c>
     </row>
     <row r="288">
@@ -13869,10 +13869,10 @@
         <v>1.03</v>
       </c>
       <c r="I288" t="n">
-        <v>0.111</v>
+        <v>0.082</v>
       </c>
       <c r="J288" t="n">
-        <v>3.774</v>
+        <v>2.788</v>
       </c>
     </row>
     <row r="289">
@@ -13909,10 +13909,10 @@
         <v>1.02</v>
       </c>
       <c r="I289" t="n">
-        <v>0.0838</v>
+        <v>0.0598</v>
       </c>
       <c r="J289" t="n">
-        <v>2.8492</v>
+        <v>2.0332</v>
       </c>
     </row>
     <row r="290">
@@ -13949,10 +13949,10 @@
         <v>0.63</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.4048</v>
+        <v>-0.3944</v>
       </c>
       <c r="J290" t="n">
-        <v>-13.7632</v>
+        <v>-13.4096</v>
       </c>
     </row>
     <row r="291">
@@ -13989,10 +13989,10 @@
         <v>0.63</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.4048</v>
+        <v>-0.3944</v>
       </c>
       <c r="J291" t="n">
-        <v>-13.7632</v>
+        <v>-13.4096</v>
       </c>
     </row>
     <row r="292">
@@ -14029,10 +14029,10 @@
         <v>1.94</v>
       </c>
       <c r="I292" t="n">
-        <v>1.6418</v>
+        <v>1.6876</v>
       </c>
       <c r="J292" t="n">
-        <v>41.045</v>
+        <v>42.19</v>
       </c>
     </row>
     <row r="293">
@@ -14069,10 +14069,10 @@
         <v>1.23</v>
       </c>
       <c r="I293" t="n">
-        <v>0.5959</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="J293" t="n">
-        <v>14.8975</v>
+        <v>14.2</v>
       </c>
     </row>
     <row r="294">
@@ -14109,10 +14109,10 @@
         <v>1.22</v>
       </c>
       <c r="I294" t="n">
-        <v>0.5746</v>
+        <v>0.546</v>
       </c>
       <c r="J294" t="n">
-        <v>14.365</v>
+        <v>13.65</v>
       </c>
     </row>
     <row r="295">
@@ -14149,10 +14149,10 @@
         <v>1.12</v>
       </c>
       <c r="I295" t="n">
-        <v>0.3436</v>
+        <v>0.3116</v>
       </c>
       <c r="J295" t="n">
-        <v>8.59</v>
+        <v>7.79</v>
       </c>
     </row>
     <row r="296">
@@ -14189,10 +14189,10 @@
         <v>1.04</v>
       </c>
       <c r="I296" t="n">
-        <v>0.1193</v>
+        <v>0.0954</v>
       </c>
       <c r="J296" t="n">
-        <v>2.9825</v>
+        <v>2.385</v>
       </c>
     </row>
     <row r="297">
@@ -14229,10 +14229,10 @@
         <v>1.14</v>
       </c>
       <c r="I297" t="n">
-        <v>0.3901</v>
+        <v>0.3427</v>
       </c>
       <c r="J297" t="n">
-        <v>9.7525</v>
+        <v>8.567500000000001</v>
       </c>
     </row>
     <row r="298">
@@ -14269,10 +14269,10 @@
         <v>0.93</v>
       </c>
       <c r="I298" t="n">
-        <v>-0.0921</v>
+        <v>-0.0785</v>
       </c>
       <c r="J298" t="n">
-        <v>-2.3025</v>
+        <v>-1.9625</v>
       </c>
     </row>
     <row r="299">
@@ -14309,10 +14309,10 @@
         <v>0.68</v>
       </c>
       <c r="I299" t="n">
-        <v>-0.3454</v>
+        <v>-0.3302</v>
       </c>
       <c r="J299" t="n">
-        <v>-8.635</v>
+        <v>-8.255000000000001</v>
       </c>
     </row>
     <row r="300">
@@ -14349,10 +14349,10 @@
         <v>0.67</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.3545</v>
+        <v>-0.3399</v>
       </c>
       <c r="J300" t="n">
-        <v>-8.862500000000001</v>
+        <v>-8.4975</v>
       </c>
     </row>
     <row r="301">
@@ -14389,10 +14389,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.4528</v>
+        <v>-0.4463</v>
       </c>
       <c r="J301" t="n">
-        <v>-11.32</v>
+        <v>-11.1575</v>
       </c>
     </row>
   </sheetData>
